--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB77E01F-E3CE-4171-A517-1254FC8EBEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8BF0AE-C848-477A-89B2-2C7774795181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>49.05</v>
+        <v>50.7</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>12415.00297365</v>
+        <v>12832.633043100001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
+      <c r="B12" s="336" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="C12" s="336"/>
+      <c r="D12" s="336"/>
+      <c r="E12" s="336"/>
+      <c r="F12" s="336"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7610000000000001</v>
+        <v>7.7594000000000003</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1151268191287802</v>
+        <v>0.10282033117906053</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
+      <c r="B25" s="336" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="C25" s="336"/>
+      <c r="D25" s="336"/>
+      <c r="E25" s="336"/>
+      <c r="F25" s="336"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
+      <c r="B26" s="338" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="C26" s="338"/>
+      <c r="D26" s="338"/>
+      <c r="E26" s="338"/>
+      <c r="F26" s="338"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="337" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="337"/>
+      <c r="D29" s="337"/>
+      <c r="E29" s="337"/>
+      <c r="F29" s="337"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="337" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="337"/>
+      <c r="D32" s="337"/>
+      <c r="E32" s="337"/>
+      <c r="F32" s="337"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="337" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="337"/>
+      <c r="D36" s="337"/>
+      <c r="E36" s="337"/>
+      <c r="F36" s="337"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="337" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="337"/>
+      <c r="D39" s="337"/>
+      <c r="E39" s="337"/>
+      <c r="F39" s="337"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="337" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="337"/>
+      <c r="D47" s="337"/>
+      <c r="E47" s="337"/>
+      <c r="F47" s="337"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
+      <c r="B50" s="337" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
+      <c r="B53" s="336" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="C53" s="336"/>
+      <c r="D53" s="336"/>
+      <c r="E53" s="336"/>
+      <c r="F53" s="336"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
+      <c r="B54" s="336" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="C54" s="336"/>
+      <c r="D54" s="336"/>
+      <c r="E54" s="336"/>
+      <c r="F54" s="336"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10720319069009697</v>
+        <v>0.10369294781216104</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
+      <c r="B63" s="336" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="C63" s="336"/>
+      <c r="D63" s="336"/>
+      <c r="E63" s="336"/>
+      <c r="F63" s="336"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="338" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="338"/>
+      <c r="D64" s="338"/>
+      <c r="E64" s="338"/>
+      <c r="F64" s="338"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
+      <c r="B73" s="336" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="C73" s="336"/>
+      <c r="D73" s="336"/>
+      <c r="E73" s="336"/>
+      <c r="F73" s="336"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
+      <c r="B74" s="336" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="C74" s="336"/>
+      <c r="D74" s="336"/>
+      <c r="E74" s="336"/>
+      <c r="F74" s="336"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>65.7289562918657</v>
+        <v>65.715405675957058</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
+      <c r="B81" s="336" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="C81" s="336"/>
+      <c r="D81" s="336"/>
+      <c r="E81" s="336"/>
+      <c r="F81" s="336"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
+      <c r="B85" s="336" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="C85" s="336"/>
+      <c r="D85" s="336"/>
+      <c r="E85" s="336"/>
+      <c r="F85" s="336"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>4.7619115348160905</v>
+        <v>4.7609298238953706</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>-0.68958712231633723</v>
+        <v>-0.68944495772469871</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.1958438496962494E-2</v>
+        <v>1.1955973157238857E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
+      <c r="B98" s="336" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="C98" s="336"/>
+      <c r="D98" s="336"/>
+      <c r="E98" s="336"/>
+      <c r="F98" s="336"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
+      <c r="B104" s="337" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="C104" s="337"/>
+      <c r="D104" s="337"/>
+      <c r="E104" s="337"/>
+      <c r="F104" s="337"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>95.81 HKD</v>
+        <v>95.79 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>71.71 HKD</v>
+        <v>71.7 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.81 HKD</v>
+        <v>66.8 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>62.36 HKD</v>
+        <v>62.35 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>60.29 HKD</v>
+        <v>60.28 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>68.016110669918646</v>
+        <v>68.002088536550289</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
+      <c r="B115" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="C115" s="341"/>
+      <c r="D115" s="341"/>
+      <c r="E115" s="341"/>
+      <c r="F115" s="341"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
+      <c r="B119" s="339" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="C119" s="339"/>
+      <c r="D119" s="339"/>
+      <c r="E119" s="339"/>
+      <c r="F119" s="339"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
+      <c r="B120" s="336" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="C120" s="336"/>
+      <c r="D120" s="336"/>
+      <c r="E120" s="336"/>
+      <c r="F120" s="336"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+      <c r="B134" s="343" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
+      <c r="C134" s="336"/>
+      <c r="D134" s="336"/>
+      <c r="E134" s="336"/>
+      <c r="F134" s="336"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
+      <c r="B143" s="337" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
+      <c r="B146" s="342" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
+      <c r="C146" s="342"/>
+      <c r="D146" s="342"/>
+      <c r="E146" s="342"/>
+      <c r="F146" s="342"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
+      <c r="B147" s="342" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
+      <c r="C147" s="342"/>
+      <c r="D147" s="342"/>
+      <c r="E147" s="342"/>
+      <c r="F147" s="342"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,6 +5203,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5219,17 +5230,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.225489583578156</v>
+        <v>19.221526075868621</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.644501354283415</v>
+        <v>-2.6439561665283766</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9006,11 +9006,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1205.2833000000001</v>
+        <v>-1205.0348200000001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-4.7619115348160905</v>
+        <v>-4.7609298238953706</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9023,11 +9023,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-174.54079865745305</v>
+        <v>-174.50481550092013</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>-0.68958712231633723</v>
+        <v>-0.6894449577246986</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9040,11 +9040,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0267900000000001</v>
+        <v>3.0261660000000004</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.1958438496962494E-2</v>
+        <v>1.1955973157238859E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9057,11 +9057,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-1376.7973086574532</v>
+        <v>-1376.5134695009201</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-5.4395402186354653</v>
+        <v>-5.4384188084628304</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -13882,46 +13882,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2583165033492563</v>
+        <v>5.2572324540765649</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1233337637010532</v>
+        <v>6.1220713833348741</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5162130400091032</v>
+        <v>5.5150758230442776</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1539964265137694</v>
+        <v>6.1527277247636833</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2635876280292138</v>
+        <v>8.2618840150663431</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3651716076163867</v>
+        <v>7.3636532112019832</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0992008257560624</v>
+        <v>5.0981495796123681</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2061229532954059</v>
+        <v>6.2048435051926774</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4855503771963896</v>
+        <v>5.4844194816154701</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5376769039780163</v>
+        <v>5.5365352620444552</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13939,46 +13939,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10720319069009697</v>
+        <v>0.10369294781216104</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12483860884201944</v>
+        <v>0.12075091485867601</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11246102018367184</v>
+        <v>0.10877861583913762</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.12546373958233986</v>
+        <v>0.12135557642531919</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1684727345163958</v>
+        <v>0.16295629221038152</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.15015640382500278</v>
+        <v>0.14523970830773142</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10395924211531218</v>
+        <v>0.10055521853278832</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.12652646184088495</v>
+        <v>0.12238350108861296</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.11183588944335147</v>
+        <v>0.10817395427249447</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.11289861170189636</v>
+        <v>0.10920187893578806</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -13996,39 +13996,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.341924769197375E-2</v>
+        <v>1.2982526613240876E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2017717620903262E-2</v>
+        <v>1.1626608467560256E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.391058869390076E-2</v>
+        <v>1.3457877227531207E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8598465138515839E-2</v>
+        <v>1.7993189645842247E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.536044738811161E-2</v>
+        <v>1.4860551171338745E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3797821906573249E-2</v>
+        <v>1.3348780365235065E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6616991589761012E-2</v>
+        <v>1.607620192263861E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4418039236874557E-2</v>
+        <v>1.3948813107863845E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4611353729436003E-2</v>
+        <v>1.4135836300371518E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7610000000000001</v>
+        <v>7.7594000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>68.015846213324608</v>
+        <v>68.001824134476351</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15897,23 +15897,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15924,23 +15924,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>60.289416073230228</v>
+        <v>60.276986867494216</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>61.342027566061752</v>
+        <v>61.329381354992854</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>63.49420262093485</v>
+        <v>63.481112719608539</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>65.711276456808733</v>
+        <v>65.697729485757208</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>69.164787365785372</v>
+        <v>69.150528422377917</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15951,23 +15951,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>60.289416073230228</v>
+        <v>60.276986867494216</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>62.360962315350591</v>
+        <v>62.348106041712583</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>66.811063418731948</v>
+        <v>66.797289716700007</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>71.711247730313843</v>
+        <v>71.696463811183776</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>80.02446731049173</v>
+        <v>80.007969546325157</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15978,23 +15978,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>60.289416073230228</v>
+        <v>60.276986867494216</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.590824964965655</v>
+        <v>63.577715144073515</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>71.023370436075268</v>
+        <v>71.008728329040395</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>79.74401529561581</v>
+        <v>79.727575349156211</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>95.813356238445664</v>
+        <v>95.793603452724554</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16005,23 +16005,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>60.289416073230214</v>
+        <v>60.276986867494209</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>64.811530456755406</v>
+        <v>64.798168976439626</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>75.432583368360312</v>
+        <v>75.417032262395949</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.641395769535904</v>
+        <v>88.623121548014041</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>114.95698197506579</v>
+        <v>114.93328255860398</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16032,23 +16032,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>60.289416073230214</v>
+        <v>60.276986867494209</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>65.916769494108806</v>
+        <v>65.903180158818174</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>79.650336323462795</v>
+        <v>79.633915689766425</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>97.676515034920328</v>
+        <v>97.656378142244662</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>136.38378521413472</v>
+        <v>136.3556684693412</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16058,23 +16058,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>60.289416073230214</v>
+        <v>60.276986867494209</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>66.86528877012627</v>
+        <v>66.851503889050093</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>83.480994057086562</v>
+        <v>83.463783698821999</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>106.41388993894219</v>
+        <v>106.39195175779255</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>159.36448069721581</v>
+        <v>159.33162627521921</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>95.813356238445664</v>
+        <v>95.793603452724554</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>71.711247730313843</v>
+        <v>71.696463811183776</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.811063418731948</v>
+        <v>66.797289716700007</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>62.360962315350591</v>
+        <v>62.348106041712583</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>60.289416073230228</v>
+        <v>60.276986867494216</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-49.05</v>
+        <v>-50.7</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>68.016110669918646</v>
+        <v>68.002088536550289</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>49.05</v>
+        <v>50.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>60.289416073230242</v>
+        <v>60.27698686749423</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.811063418731948</v>
+        <v>66.797289716700007</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>62.360962315350591</v>
+        <v>62.348106041712583</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16719,7 +16719,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>71.711247730313843</v>
+        <v>71.696463811183776</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.901080060372067</v>
+        <v>66.887287800599282</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>60.289416073230228</v>
+        <v>60.276986867494216</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>95.813356238445664</v>
+        <v>95.793603452724554</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>68.016110669918646</v>
+        <v>68.002088536550289</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16966,7 +16966,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>68.015846213324608</v>
+        <v>68.001824134476351</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-7.9974290871077408E-2</v>
+        <v>-7.9974290871077394E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.82424866299835</v>
+        <v>34.81706933071375</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>49.05</v>
+        <v>50.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1151268191287802</v>
+        <v>0.10282033117906053</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8BF0AE-C848-477A-89B2-2C7774795181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639CFD96-CA3F-4F8B-B2C4-60F92E239883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3701,29 +3701,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4079,7 +4079,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="50">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>41</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>12832.633043100001</v>
+        <v>13212.2967426</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4134,13 +4134,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="336" t="s">
+      <c r="B12" s="338" t="s">
         <v>375</v>
       </c>
-      <c r="C12" s="336"/>
-      <c r="D12" s="336"/>
-      <c r="E12" s="336"/>
-      <c r="F12" s="336"/>
+      <c r="C12" s="338"/>
+      <c r="D12" s="338"/>
+      <c r="E12" s="338"/>
+      <c r="F12" s="338"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
@@ -4174,7 +4174,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7594000000000003</v>
+        <v>7.7579000000000002</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="C20" s="252">
         <f>C129</f>
-        <v>34.81706933071375</v>
+        <v>34.810338706696939</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>319</v>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.10282033117906053</v>
+        <v>9.2083708290373378E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4242,22 +4242,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="336" t="s">
+      <c r="B25" s="338" t="s">
         <v>376</v>
       </c>
-      <c r="C25" s="336"/>
-      <c r="D25" s="336"/>
-      <c r="E25" s="336"/>
-      <c r="F25" s="336"/>
+      <c r="C25" s="338"/>
+      <c r="D25" s="338"/>
+      <c r="E25" s="338"/>
+      <c r="F25" s="338"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="338" t="s">
+      <c r="B26" s="341" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="338"/>
-      <c r="D26" s="338"/>
-      <c r="E26" s="338"/>
-      <c r="F26" s="338"/>
+      <c r="C26" s="341"/>
+      <c r="D26" s="341"/>
+      <c r="E26" s="341"/>
+      <c r="F26" s="341"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4269,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="337" t="s">
+      <c r="B29" s="339" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="337"/>
-      <c r="D29" s="337"/>
-      <c r="E29" s="337"/>
-      <c r="F29" s="337"/>
+      <c r="C29" s="339"/>
+      <c r="D29" s="339"/>
+      <c r="E29" s="339"/>
+      <c r="F29" s="339"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4295,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="337" t="s">
+      <c r="B32" s="339" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="337"/>
-      <c r="D32" s="337"/>
-      <c r="E32" s="337"/>
-      <c r="F32" s="337"/>
+      <c r="C32" s="339"/>
+      <c r="D32" s="339"/>
+      <c r="E32" s="339"/>
+      <c r="F32" s="339"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="337" t="s">
+      <c r="B36" s="339" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="337"/>
-      <c r="D36" s="337"/>
-      <c r="E36" s="337"/>
-      <c r="F36" s="337"/>
+      <c r="C36" s="339"/>
+      <c r="D36" s="339"/>
+      <c r="E36" s="339"/>
+      <c r="F36" s="339"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,13 +4352,13 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="337" t="s">
+      <c r="B39" s="339" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="337"/>
-      <c r="D39" s="337"/>
-      <c r="E39" s="337"/>
-      <c r="F39" s="337"/>
+      <c r="C39" s="339"/>
+      <c r="D39" s="339"/>
+      <c r="E39" s="339"/>
+      <c r="F39" s="339"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
@@ -4422,13 +4422,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="337" t="s">
+      <c r="B47" s="339" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="337"/>
-      <c r="D47" s="337"/>
-      <c r="E47" s="337"/>
-      <c r="F47" s="337"/>
+      <c r="C47" s="339"/>
+      <c r="D47" s="339"/>
+      <c r="E47" s="339"/>
+      <c r="F47" s="339"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,7 +4444,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="337" t="s">
+      <c r="B50" s="339" t="s">
         <v>351</v>
       </c>
       <c r="C50" s="340"/>
@@ -4466,22 +4466,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="336" t="s">
+      <c r="B53" s="338" t="s">
         <v>356</v>
       </c>
-      <c r="C53" s="336"/>
-      <c r="D53" s="336"/>
-      <c r="E53" s="336"/>
-      <c r="F53" s="336"/>
+      <c r="C53" s="338"/>
+      <c r="D53" s="338"/>
+      <c r="E53" s="338"/>
+      <c r="F53" s="338"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="336" t="s">
+      <c r="B54" s="338" t="s">
         <v>377</v>
       </c>
-      <c r="C54" s="336"/>
-      <c r="D54" s="336"/>
-      <c r="E54" s="336"/>
-      <c r="F54" s="336"/>
+      <c r="C54" s="338"/>
+      <c r="D54" s="338"/>
+      <c r="E54" s="338"/>
+      <c r="F54" s="338"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10369294781216104</v>
+        <v>0.10069379612803481</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
@@ -4542,22 +4542,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="336" t="s">
+      <c r="B63" s="338" t="s">
         <v>378</v>
       </c>
-      <c r="C63" s="336"/>
-      <c r="D63" s="336"/>
-      <c r="E63" s="336"/>
-      <c r="F63" s="336"/>
+      <c r="C63" s="338"/>
+      <c r="D63" s="338"/>
+      <c r="E63" s="338"/>
+      <c r="F63" s="338"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="338" t="s">
+      <c r="B64" s="341" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="338"/>
-      <c r="D64" s="338"/>
-      <c r="E64" s="338"/>
-      <c r="F64" s="338"/>
+      <c r="C64" s="341"/>
+      <c r="D64" s="341"/>
+      <c r="E64" s="341"/>
+      <c r="F64" s="341"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4615,22 +4615,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="336" t="s">
+      <c r="B73" s="338" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="336"/>
-      <c r="D73" s="336"/>
-      <c r="E73" s="336"/>
-      <c r="F73" s="336"/>
+      <c r="C73" s="338"/>
+      <c r="D73" s="338"/>
+      <c r="E73" s="338"/>
+      <c r="F73" s="338"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="336" t="s">
+      <c r="B74" s="338" t="s">
         <v>380</v>
       </c>
-      <c r="C74" s="336"/>
-      <c r="D74" s="336"/>
-      <c r="E74" s="336"/>
-      <c r="F74" s="336"/>
+      <c r="C74" s="338"/>
+      <c r="D74" s="338"/>
+      <c r="E74" s="338"/>
+      <c r="F74" s="338"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
-        <v>65.715405675957058</v>
+        <v>65.702701973542702</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4667,13 +4667,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="336" t="s">
+      <c r="B81" s="338" t="s">
         <v>381</v>
       </c>
-      <c r="C81" s="336"/>
-      <c r="D81" s="336"/>
-      <c r="E81" s="336"/>
-      <c r="F81" s="336"/>
+      <c r="C81" s="338"/>
+      <c r="D81" s="338"/>
+      <c r="E81" s="338"/>
+      <c r="F81" s="338"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="336" t="s">
+      <c r="B85" s="338" t="s">
         <v>357</v>
       </c>
-      <c r="C85" s="336"/>
-      <c r="D85" s="336"/>
-      <c r="E85" s="336"/>
-      <c r="F85" s="336"/>
+      <c r="C85" s="338"/>
+      <c r="D85" s="338"/>
+      <c r="E85" s="338"/>
+      <c r="F85" s="338"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
-        <v>4.7609298238953706</v>
+        <v>4.760009469907196</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
-        <v>-0.68944495772469871</v>
+        <v>-0.6893116784200376</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
-        <v>1.1955973157238857E-2</v>
+        <v>1.1953661901247949E-2</v>
       </c>
       <c r="D96" s="1" t="str">
         <f>Market_currency</f>
@@ -4796,13 +4796,13 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="336" t="s">
+      <c r="B98" s="338" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="336"/>
-      <c r="D98" s="336"/>
-      <c r="E98" s="336"/>
-      <c r="F98" s="336"/>
+      <c r="C98" s="338"/>
+      <c r="D98" s="338"/>
+      <c r="E98" s="338"/>
+      <c r="F98" s="338"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4828,13 +4828,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="337" t="s">
+      <c r="B104" s="339" t="s">
         <v>383</v>
       </c>
-      <c r="C104" s="337"/>
-      <c r="D104" s="337"/>
-      <c r="E104" s="337"/>
-      <c r="F104" s="337"/>
+      <c r="C104" s="339"/>
+      <c r="D104" s="339"/>
+      <c r="E104" s="339"/>
+      <c r="F104" s="339"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E107" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>95.79 HKD</v>
+        <v>95.78 HKD</v>
       </c>
       <c r="F107" s="259">
         <f>Valuation_Model!F74</f>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="E108" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>71.7 HKD</v>
+        <v>71.68 HKD</v>
       </c>
       <c r="F108" s="246">
         <f>Valuation_Model!F75</f>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="E109" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.8 HKD</v>
+        <v>66.78 HKD</v>
       </c>
       <c r="F109" s="246">
         <f>Valuation_Model!F76</f>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="E110" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>62.35 HKD</v>
+        <v>62.34 HKD</v>
       </c>
       <c r="F110" s="246">
         <f>Valuation_Model!F77</f>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E111" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>60.28 HKD</v>
+        <v>60.27 HKD</v>
       </c>
       <c r="F111" s="246">
         <f>Valuation_Model!F78</f>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="C113" s="241">
         <f>Scenarios!C60</f>
-        <v>68.002088536550289</v>
+        <v>67.988942786517455</v>
       </c>
       <c r="D113" s="236" t="str">
         <f>Market_currency</f>
@@ -4977,13 +4977,13 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="341" t="s">
+      <c r="B115" s="342" t="s">
         <v>386</v>
       </c>
-      <c r="C115" s="341"/>
-      <c r="D115" s="341"/>
-      <c r="E115" s="341"/>
-      <c r="F115" s="341"/>
+      <c r="C115" s="342"/>
+      <c r="D115" s="342"/>
+      <c r="E115" s="342"/>
+      <c r="F115" s="342"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
@@ -4996,22 +4996,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="339" t="s">
+      <c r="B119" s="343" t="s">
         <v>384</v>
       </c>
-      <c r="C119" s="339"/>
-      <c r="D119" s="339"/>
-      <c r="E119" s="339"/>
-      <c r="F119" s="339"/>
+      <c r="C119" s="343"/>
+      <c r="D119" s="343"/>
+      <c r="E119" s="343"/>
+      <c r="F119" s="343"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="336" t="s">
+      <c r="B120" s="338" t="s">
         <v>385</v>
       </c>
-      <c r="C120" s="336"/>
-      <c r="D120" s="336"/>
-      <c r="E120" s="336"/>
-      <c r="F120" s="336"/>
+      <c r="C120" s="338"/>
+      <c r="D120" s="338"/>
+      <c r="E120" s="338"/>
+      <c r="F120" s="338"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="C128" s="240">
         <f>Scenarios!C82</f>
-        <v>34.81706933071375</v>
+        <v>34.810338706696939</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.35">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="C129" s="239">
         <f>Scenarios!C83</f>
-        <v>34.81706933071375</v>
+        <v>34.810338706696939</v>
       </c>
       <c r="D129" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5107,13 +5107,13 @@
       <c r="F132" s="36"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="343" t="s">
+      <c r="B134" s="337" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="336"/>
-      <c r="D134" s="336"/>
-      <c r="E134" s="336"/>
-      <c r="F134" s="336"/>
+      <c r="C134" s="338"/>
+      <c r="D134" s="338"/>
+      <c r="E134" s="338"/>
+      <c r="F134" s="338"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B136" s="234" t="s">
@@ -5150,13 +5150,13 @@
       </c>
     </row>
     <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="337" t="s">
+      <c r="B143" s="339" t="s">
         <v>397</v>
       </c>
-      <c r="C143" s="337"/>
-      <c r="D143" s="337"/>
-      <c r="E143" s="337"/>
-      <c r="F143" s="337"/>
+      <c r="C143" s="339"/>
+      <c r="D143" s="339"/>
+      <c r="E143" s="339"/>
+      <c r="F143" s="339"/>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B145" s="1" t="s">
@@ -5164,22 +5164,22 @@
       </c>
     </row>
     <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="342" t="s">
+      <c r="B146" s="336" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="342"/>
-      <c r="D146" s="342"/>
-      <c r="E146" s="342"/>
-      <c r="F146" s="342"/>
+      <c r="C146" s="336"/>
+      <c r="D146" s="336"/>
+      <c r="E146" s="336"/>
+      <c r="F146" s="336"/>
     </row>
     <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="342" t="s">
+      <c r="B147" s="336" t="s">
         <v>399</v>
       </c>
-      <c r="C147" s="342"/>
-      <c r="D147" s="342"/>
-      <c r="E147" s="342"/>
-      <c r="F147" s="342"/>
+      <c r="C147" s="336"/>
+      <c r="D147" s="336"/>
+      <c r="E147" s="336"/>
+      <c r="F147" s="336"/>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B149" s="1" t="s">
@@ -5203,17 +5203,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5230,6 +5219,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B146:F146"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8596,11 +8596,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.221526075868621</v>
+        <v>19.217810287390929</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6439561665283766</v>
+        <v>-2.643445053008028</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9006,11 +9006,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1205.0348200000001</v>
+        <v>-1204.8018700000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*$H$1/Common_Shares</f>
-        <v>-4.7609298238953706</v>
+        <v>-4.7600094699071969</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9023,11 +9023,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-174.50481550092013</v>
+        <v>-174.47108129167054</v>
       </c>
       <c r="D87" s="248">
         <f>C87*$H$1/Common_Shares</f>
-        <v>-0.6894449577246986</v>
+        <v>-0.6893116784200376</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9040,11 +9040,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0261660000000004</v>
+        <v>3.0255810000000003</v>
       </c>
       <c r="D88" s="248">
         <f>C88*$H$1/Common_Shares</f>
-        <v>1.1955973157238859E-2</v>
+        <v>1.195366190124795E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9057,11 +9057,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-1376.5134695009201</v>
+        <v>-1376.2473702916707</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-5.4384188084628304</v>
+        <v>-5.4373674864259867</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -13882,46 +13882,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2572324540765649</v>
+        <v>5.2562161578834168</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1220713833348741</v>
+        <v>6.1208879017415807</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5150758230442776</v>
+        <v>5.5140096821397533</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1527277247636833</v>
+        <v>6.1515383168729771</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2618840150663431</v>
+        <v>8.26028687791365</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3636532112019832</v>
+        <v>7.3622297145634796</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0981495796123681</v>
+        <v>5.0971640363526554</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2048435051926774</v>
+        <v>6.2036440225963698</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4844194816154701</v>
+        <v>5.4833592670083586</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5365352620444552</v>
+        <v>5.5354649727317424</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -13939,46 +13939,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10369294781216104</v>
+        <v>0.10069379612803481</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.12075091485867601</v>
+        <v>0.1172583889222525</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10877861583913762</v>
+        <v>0.10563236938965044</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.12135557642531919</v>
+        <v>0.1178455616259191</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16295629221038152</v>
+        <v>0.15824304363819253</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14523970830773142</v>
+        <v>0.14103888342075629</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.10055521853278832</v>
+        <v>9.7646820619782665E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.12238350108861296</v>
+        <v>0.11884375522215267</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10817395427249447</v>
+        <v>0.10504519668598387</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10920187893578806</v>
+        <v>0.10604339028221728</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -13996,39 +13996,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2982526613240876E-2</v>
+        <v>1.2609465503664988E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1626608467560256E-2</v>
+        <v>1.1292510523090134E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3457877227531207E-2</v>
+        <v>1.3071156617544679E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7993189645842247E-2</v>
+        <v>1.747614396636402E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4860551171338745E-2</v>
+        <v>1.4433523838829012E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3348780365235065E-2</v>
+        <v>1.2965194722555898E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.607620192263861E-2</v>
+        <v>1.5614242097275433E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3948813107863845E-2</v>
+        <v>1.3547985144994196E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4135836300371518E-2</v>
+        <v>1.3729634107832107E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -14894,7 +14894,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7594000000000003</v>
+        <v>7.7579000000000002</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*C3)/Common_Shares*C11</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -14961,7 +14961,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
-        <v>68.001824134476351</v>
+        <v>67.988678435556125</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15897,23 +15897,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -15924,23 +15924,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>60.276986867494216</v>
+        <v>60.265334487116711</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>61.329381354992854</v>
+        <v>61.317525532115766</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>63.481112719608539</v>
+        <v>63.468840937115125</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>65.697729485757208</v>
+        <v>65.6850292003964</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>69.150528422377917</v>
+        <v>69.137160662933425</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -15951,23 +15951,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>60.276986867494216</v>
+        <v>60.265334487116711</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>62.348106041712583</v>
+        <v>62.336053285176952</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>66.797289716700007</v>
+        <v>66.784376871045055</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>71.696463811183776</v>
+        <v>71.682603886999331</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>80.007969546325157</v>
+        <v>79.992502892418983</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -15978,23 +15978,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>60.276986867494216</v>
+        <v>60.265334487116711</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.577715144073515</v>
+        <v>63.565424686987129</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>71.008728329040395</v>
+        <v>70.995001353695187</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>79.727575349156211</v>
+        <v>79.712162899350332</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>95.793603452724554</v>
+        <v>95.775085216111023</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16005,23 +16005,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>60.276986867494209</v>
+        <v>60.265334487116696</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>64.798168976439626</v>
+        <v>64.785642588643583</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>75.417032262395949</v>
+        <v>75.402453100554368</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.623121548014041</v>
+        <v>88.605989465337288</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>114.93328255860398</v>
+        <v>114.91106435567103</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16032,23 +16032,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>60.276986867494209</v>
+        <v>60.265334487116696</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>65.903180158818174</v>
+        <v>65.890440156983203</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>79.633915689766425</v>
+        <v>79.618521345676072</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>97.656378142244662</v>
+        <v>97.637499805361216</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>136.3556684693412</v>
+        <v>136.32930902109723</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16058,23 +16058,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>60.276986867494209</v>
+        <v>60.265334487116696</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>66.851503889050093</v>
+        <v>66.838580563041177</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>83.463783698821999</v>
+        <v>83.447648987948966</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>106.39195175779255</v>
+        <v>106.37138471296478</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>159.33162627521921</v>
+        <v>159.30082525459741</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>95.793603452724554</v>
+        <v>95.775085216111023</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16131,7 +16131,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>71.696463811183776</v>
+        <v>71.682603886999331</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16154,7 +16154,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.797289716700007</v>
+        <v>66.784376871045055</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>62.348106041712583</v>
+        <v>62.336053285176952</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>60.276986867494216</v>
+        <v>60.265334487116711</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-50.7</v>
+        <v>-52.2</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
@@ -16350,7 +16350,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>68.002088536550289</v>
+        <v>67.988942786517455</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16556,7 +16556,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>60.27698686749423</v>
+        <v>60.265334487116725</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16603,7 +16603,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.797289716700007</v>
+        <v>66.784376871045055</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>62.348106041712583</v>
+        <v>62.336053285176952</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16719,7 +16719,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>71.696463811183776</v>
+        <v>71.682603886999331</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16746,7 +16746,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.887287800599282</v>
+        <v>66.874357557062297</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16820,7 +16820,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>60.276986867494216</v>
+        <v>60.265334487116711</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -16878,7 +16878,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>95.793603452724554</v>
+        <v>95.775085216111023</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>68.002088536550289</v>
+        <v>67.988942786517455</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -16966,7 +16966,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>68.001824134476351</v>
+        <v>67.988678435556125</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17029,7 +17029,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-7.9974290871077394E-2</v>
+        <v>-7.9974290871077408E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>34.81706933071375</v>
+        <v>34.810338706696939</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.81706933071375</v>
+        <v>34.810338706696939</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.10282033117906053</v>
+        <v>9.2083708290373378E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639CFD96-CA3F-4F8B-B2C4-60F92E239883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F410062-E922-4DA6-B885-0374C76748F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1321,10 +1321,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">Expected Holding period = </t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -1825,14 +1821,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision (Calculating Target Buy Price)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Implied Market Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2318,6 +2306,45 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>in contrast to a cash yield of</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Sell Price Output</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Cash Yield</t>
+    <phoneticPr fontId="28" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>偉易達</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2330,11 +2357,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>CNS_02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>CNS_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3008,7 +3035,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="349">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3701,6 +3728,9 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4013,7 +4043,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J152"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4033,15 +4063,15 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A2" s="247" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4065,13 +4095,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4098,7 +4128,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4108,7 +4138,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4134,24 +4164,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="338" t="s">
-        <v>375</v>
-      </c>
-      <c r="C12" s="338"/>
-      <c r="D12" s="338"/>
-      <c r="E12" s="338"/>
-      <c r="F12" s="338"/>
+      <c r="B12" s="339" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="339"/>
+      <c r="D12" s="339"/>
+      <c r="E12" s="339"/>
+      <c r="F12" s="339"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4161,10 +4191,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4187,18 +4217,23 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="D19" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E19" s="336">
+        <v>3.4500000000000003E-2</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" s="2" t="str">
@@ -4210,7 +4245,7 @@
         <v>34.810338706696939</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4218,7 +4253,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>374</v>
+        <v>414</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4233,7 +4268,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4242,22 +4277,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="338" t="s">
-        <v>376</v>
-      </c>
-      <c r="C25" s="338"/>
-      <c r="D25" s="338"/>
-      <c r="E25" s="338"/>
-      <c r="F25" s="338"/>
+      <c r="B25" s="339" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="339"/>
+      <c r="D25" s="339"/>
+      <c r="E25" s="339"/>
+      <c r="F25" s="339"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="341" t="s">
-        <v>352</v>
-      </c>
-      <c r="C26" s="341"/>
-      <c r="D26" s="341"/>
-      <c r="E26" s="341"/>
-      <c r="F26" s="341"/>
+      <c r="B26" s="342" t="s">
+        <v>351</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4269,13 +4304,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="339" t="s">
+      <c r="B29" s="340" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="339"/>
-      <c r="D29" s="339"/>
-      <c r="E29" s="339"/>
-      <c r="F29" s="339"/>
+      <c r="C29" s="340"/>
+      <c r="D29" s="340"/>
+      <c r="E29" s="340"/>
+      <c r="F29" s="340"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4295,13 +4330,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="339" t="s">
+      <c r="B32" s="340" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="339"/>
-      <c r="D32" s="339"/>
-      <c r="E32" s="339"/>
-      <c r="F32" s="339"/>
+      <c r="C32" s="340"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="340"/>
+      <c r="F32" s="340"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4330,13 +4365,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="339" t="s">
+      <c r="B36" s="340" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="339"/>
-      <c r="D36" s="339"/>
-      <c r="E36" s="339"/>
-      <c r="F36" s="339"/>
+      <c r="C36" s="340"/>
+      <c r="D36" s="340"/>
+      <c r="E36" s="340"/>
+      <c r="F36" s="340"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4352,17 +4387,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="339" t="s">
+      <c r="B39" s="340" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="339"/>
-      <c r="D39" s="339"/>
-      <c r="E39" s="339"/>
-      <c r="F39" s="339"/>
+      <c r="C39" s="340"/>
+      <c r="D39" s="340"/>
+      <c r="E39" s="340"/>
+      <c r="F39" s="340"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4377,7 +4412,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4410,7 +4445,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B45" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4422,13 +4457,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="339" t="s">
+      <c r="B47" s="340" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="339"/>
-      <c r="D47" s="339"/>
-      <c r="E47" s="339"/>
-      <c r="F47" s="339"/>
+      <c r="C47" s="340"/>
+      <c r="D47" s="340"/>
+      <c r="E47" s="340"/>
+      <c r="F47" s="340"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4444,13 +4479,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="339" t="s">
-        <v>351</v>
-      </c>
-      <c r="C50" s="340"/>
-      <c r="D50" s="340"/>
-      <c r="E50" s="340"/>
-      <c r="F50" s="340"/>
+      <c r="B50" s="340" t="s">
+        <v>350</v>
+      </c>
+      <c r="C50" s="341"/>
+      <c r="D50" s="341"/>
+      <c r="E50" s="341"/>
+      <c r="F50" s="341"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4466,26 +4501,26 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="338" t="s">
-        <v>356</v>
-      </c>
-      <c r="C53" s="338"/>
-      <c r="D53" s="338"/>
-      <c r="E53" s="338"/>
-      <c r="F53" s="338"/>
+      <c r="B53" s="339" t="s">
+        <v>355</v>
+      </c>
+      <c r="C53" s="339"/>
+      <c r="D53" s="339"/>
+      <c r="E53" s="339"/>
+      <c r="F53" s="339"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="338" t="s">
-        <v>377</v>
-      </c>
-      <c r="C54" s="338"/>
-      <c r="D54" s="338"/>
-      <c r="E54" s="338"/>
-      <c r="F54" s="338"/>
+      <c r="B54" s="339" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="339"/>
+      <c r="D54" s="339"/>
+      <c r="E54" s="339"/>
+      <c r="F54" s="339"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4511,7 +4546,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4520,7 +4555,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4529,7 +4564,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4542,22 +4577,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="338" t="s">
-        <v>378</v>
-      </c>
-      <c r="C63" s="338"/>
-      <c r="D63" s="338"/>
-      <c r="E63" s="338"/>
-      <c r="F63" s="338"/>
+      <c r="B63" s="339" t="s">
+        <v>375</v>
+      </c>
+      <c r="C63" s="339"/>
+      <c r="D63" s="339"/>
+      <c r="E63" s="339"/>
+      <c r="F63" s="339"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="341" t="s">
+      <c r="B64" s="342" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="341"/>
-      <c r="D64" s="341"/>
-      <c r="E64" s="341"/>
-      <c r="F64" s="341"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4566,7 +4601,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4574,26 +4609,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4610,27 +4645,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="338" t="s">
-        <v>379</v>
-      </c>
-      <c r="C73" s="338"/>
-      <c r="D73" s="338"/>
-      <c r="E73" s="338"/>
-      <c r="F73" s="338"/>
+      <c r="B73" s="339" t="s">
+        <v>376</v>
+      </c>
+      <c r="C73" s="339"/>
+      <c r="D73" s="339"/>
+      <c r="E73" s="339"/>
+      <c r="F73" s="339"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="338" t="s">
-        <v>380</v>
-      </c>
-      <c r="C74" s="338"/>
-      <c r="D74" s="338"/>
-      <c r="E74" s="338"/>
-      <c r="F74" s="338"/>
+      <c r="B74" s="339" t="s">
+        <v>377</v>
+      </c>
+      <c r="C74" s="339"/>
+      <c r="D74" s="339"/>
+      <c r="E74" s="339"/>
+      <c r="F74" s="339"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4642,7 +4677,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4655,7 +4690,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4667,13 +4702,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="338" t="s">
-        <v>381</v>
-      </c>
-      <c r="C81" s="338"/>
-      <c r="D81" s="338"/>
-      <c r="E81" s="338"/>
-      <c r="F81" s="338"/>
+      <c r="B81" s="339" t="s">
+        <v>378</v>
+      </c>
+      <c r="C81" s="339"/>
+      <c r="D81" s="339"/>
+      <c r="E81" s="339"/>
+      <c r="F81" s="339"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4686,13 +4721,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="338" t="s">
-        <v>357</v>
-      </c>
-      <c r="C85" s="338"/>
-      <c r="D85" s="338"/>
-      <c r="E85" s="338"/>
-      <c r="F85" s="338"/>
+      <c r="B85" s="339" t="s">
+        <v>356</v>
+      </c>
+      <c r="C85" s="339"/>
+      <c r="D85" s="339"/>
+      <c r="E85" s="339"/>
+      <c r="F85" s="339"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4709,7 +4744,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4727,7 +4762,7 @@
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B90" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C90" s="188">
         <f>BS!C66</f>
@@ -4740,7 +4775,7 @@
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B91" s="47" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C91" s="188">
         <f>Valuation_Model!C8</f>
@@ -4753,7 +4788,7 @@
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B92" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C92" s="248">
         <f>C91*C28*Exchange_Rate/Common_Shares</f>
@@ -4784,7 +4819,7 @@
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B96" s="47" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C96" s="248">
         <f>C95*C28*Exchange_Rate/Common_Shares</f>
@@ -4796,17 +4831,17 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="338" t="s">
-        <v>382</v>
-      </c>
-      <c r="C98" s="338"/>
-      <c r="D98" s="338"/>
-      <c r="E98" s="338"/>
-      <c r="F98" s="338"/>
+      <c r="B98" s="339" t="s">
+        <v>379</v>
+      </c>
+      <c r="C98" s="339"/>
+      <c r="D98" s="339"/>
+      <c r="E98" s="339"/>
+      <c r="F98" s="339"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B100" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C100" s="248">
         <f>Valuation_Model!C12</f>
@@ -4819,7 +4854,7 @@
     </row>
     <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A102" s="247" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B102" s="36"/>
       <c r="C102" s="36"/>
@@ -4828,13 +4863,13 @@
       <c r="F102" s="36"/>
     </row>
     <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="339" t="s">
-        <v>383</v>
-      </c>
-      <c r="C104" s="339"/>
-      <c r="D104" s="339"/>
-      <c r="E104" s="339"/>
-      <c r="F104" s="339"/>
+      <c r="B104" s="340" t="s">
+        <v>380</v>
+      </c>
+      <c r="C104" s="340"/>
+      <c r="D104" s="340"/>
+      <c r="E104" s="340"/>
+      <c r="F104" s="340"/>
     </row>
     <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B106" s="260" t="s">
@@ -4977,17 +5012,17 @@
       </c>
     </row>
     <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="342" t="s">
-        <v>386</v>
-      </c>
-      <c r="C115" s="342"/>
-      <c r="D115" s="342"/>
-      <c r="E115" s="342"/>
-      <c r="F115" s="342"/>
+      <c r="B115" s="343" t="s">
+        <v>383</v>
+      </c>
+      <c r="C115" s="343"/>
+      <c r="D115" s="343"/>
+      <c r="E115" s="343"/>
+      <c r="F115" s="343"/>
     </row>
     <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A117" s="247" t="s">
-        <v>373</v>
+        <v>418</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -4996,22 +5031,22 @@
       <c r="F117" s="36"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="343" t="s">
-        <v>384</v>
-      </c>
-      <c r="C119" s="343"/>
-      <c r="D119" s="343"/>
-      <c r="E119" s="343"/>
-      <c r="F119" s="343"/>
+      <c r="B119" s="344" t="s">
+        <v>381</v>
+      </c>
+      <c r="C119" s="344"/>
+      <c r="D119" s="344"/>
+      <c r="E119" s="344"/>
+      <c r="F119" s="344"/>
     </row>
     <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="338" t="s">
-        <v>385</v>
-      </c>
-      <c r="C120" s="338"/>
-      <c r="D120" s="338"/>
-      <c r="E120" s="338"/>
-      <c r="F120" s="338"/>
+      <c r="B120" s="339" t="s">
+        <v>382</v>
+      </c>
+      <c r="C120" s="339"/>
+      <c r="D120" s="339"/>
+      <c r="E120" s="339"/>
+      <c r="F120" s="339"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B121" s="234" t="s">
@@ -5020,7 +5055,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B122" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C122" s="251">
         <f>E20</f>
@@ -5029,7 +5064,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B123" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C123" s="250">
         <f>C19</f>
@@ -5051,7 +5086,7 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B126" s="234" t="s">
-        <v>265</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.35">
@@ -5096,109 +5131,156 @@
         <v>0.48799999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A132" s="247" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="234" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="236" t="str">
+        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C133" s="240">
+        <f>Scenarios!C91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C134" s="240">
+        <f>Scenarios!C92</f>
+        <v>61.41108960250569</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B135" s="80" t="s">
+        <v>417</v>
+      </c>
+      <c r="C135" s="239">
+        <f>Scenarios!C93</f>
+        <v>61.41108960250569</v>
+      </c>
+      <c r="D135" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="238" t="s">
+        <v>264</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!F93</f>
+        <v>9.6748867013066508E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A138" s="247" t="s">
+        <v>387</v>
+      </c>
+      <c r="B138" s="36"/>
+      <c r="C138" s="36"/>
+      <c r="D138" s="36"/>
+      <c r="E138" s="36"/>
+      <c r="F138" s="36"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="338" t="s">
+        <v>389</v>
+      </c>
+      <c r="C140" s="339"/>
+      <c r="D140" s="339"/>
+      <c r="E140" s="339"/>
+      <c r="F140" s="339"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B142" s="234" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B143" s="341" t="s">
+        <v>393</v>
+      </c>
+      <c r="C143" s="341"/>
+      <c r="D143" s="341"/>
+      <c r="E143" s="341"/>
+      <c r="F143" s="341"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="B132" s="36"/>
-      <c r="C132" s="36"/>
-      <c r="D132" s="36"/>
-      <c r="E132" s="36"/>
-      <c r="F132" s="36"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="337" t="s">
+    </row>
+    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B145" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="238" t="s">
         <v>392</v>
       </c>
-      <c r="C134" s="338"/>
-      <c r="D134" s="338"/>
-      <c r="E134" s="338"/>
-      <c r="F134" s="338"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="234" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B137" s="340" t="s">
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B149" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="340"/>
+      <c r="D149" s="340"/>
+      <c r="E149" s="340"/>
+      <c r="F149" s="340"/>
+    </row>
+    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B151" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B152" s="337" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" s="337"/>
+      <c r="D152" s="337"/>
+      <c r="E152" s="337"/>
+      <c r="F152" s="337"/>
+    </row>
+    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="337" t="s">
         <v>396</v>
       </c>
-      <c r="C137" s="340"/>
-      <c r="D137" s="340"/>
-      <c r="E137" s="340"/>
-      <c r="F137" s="340"/>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B138" s="238" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B139" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="1" t="s">
+      <c r="C153" s="337"/>
+      <c r="D153" s="337"/>
+      <c r="E153" s="337"/>
+      <c r="F153" s="337"/>
+    </row>
+    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B155" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B156" s="238" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B157" s="238" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="339" t="s">
-        <v>397</v>
-      </c>
-      <c r="C143" s="339"/>
-      <c r="D143" s="339"/>
-      <c r="E143" s="339"/>
-      <c r="F143" s="339"/>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="1" t="s">
+    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B158" s="238" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="336" t="s">
-        <v>398</v>
-      </c>
-      <c r="C146" s="336"/>
-      <c r="D146" s="336"/>
-      <c r="E146" s="336"/>
-      <c r="F146" s="336"/>
-    </row>
-    <row r="147" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="336" t="s">
-        <v>399</v>
-      </c>
-      <c r="C147" s="336"/>
-      <c r="D147" s="336"/>
-      <c r="E147" s="336"/>
-      <c r="F147" s="336"/>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="238" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="238" t="s">
-        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -5225,14 +5307,14 @@
     <mergeCell ref="B115:F115"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B146:F146"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="B143:F143"/>
-    <mergeCell ref="B137:F137"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -5792,7 +5874,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C22" s="181">
         <v>355.2</v>
@@ -5826,7 +5908,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C23" s="181">
         <v>-54.4</v>
@@ -5860,7 +5942,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C24" s="181">
         <v>-171.1</v>
@@ -5914,7 +5996,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7193,7 +7275,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8563,13 +8645,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C45" s="261" t="s">
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8577,7 +8659,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8730,7 +8812,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8753,7 +8835,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8775,7 +8857,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8842,7 +8924,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8854,7 +8936,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8865,12 +8947,12 @@
         <v>-172.68947283306957</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8881,12 +8963,12 @@
         <v>0.86976928897797345</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8894,12 +8976,12 @@
         <v>172.68947283306957</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8907,7 +8989,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8983,7 +9065,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -8994,15 +9076,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>300</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9019,7 +9101,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9053,7 +9135,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9924,7 +10006,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -9949,7 +10031,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10277,7 +10359,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10337,7 +10419,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10461,7 +10543,7 @@
         <v>-78.45</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10519,7 +10601,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10827,7 +10909,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -10966,7 +11048,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11021,7 +11103,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11154,7 +11236,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11181,7 +11263,7 @@
         <v>3.1551835157759174E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11496,7 +11578,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12057,7 +12139,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12736,7 +12818,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13430,7 +13512,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13482,7 +13564,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13935,7 +14017,7 @@
     <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -13991,7 +14073,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14820,10 +14902,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="344" t="s">
+      <c r="E6" s="345" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="344"/>
+      <c r="F6" s="345"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14838,8 +14920,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="344"/>
-      <c r="F7" s="344"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14854,8 +14936,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="344"/>
-      <c r="F8" s="344"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14870,8 +14952,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="344"/>
-      <c r="F9" s="344"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16216,7 +16298,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16268,7 +16350,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I92"/>
+  <dimension ref="B2:I98"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16288,7 +16370,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16342,7 +16424,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16355,7 +16437,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16365,11 +16447,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="346" t="str">
+      <c r="E7" s="347" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="346"/>
+      <c r="F7" s="347"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16390,8 +16472,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="346"/>
-      <c r="F8" s="346"/>
+      <c r="E8" s="347"/>
+      <c r="F8" s="347"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16412,8 +16494,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="346"/>
-      <c r="F9" s="346"/>
+      <c r="E9" s="347"/>
+      <c r="F9" s="347"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16423,8 +16505,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="346"/>
-      <c r="F10" s="346"/>
+      <c r="E10" s="347"/>
+      <c r="F10" s="347"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16435,10 +16517,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>282</v>
-      </c>
-      <c r="E11" s="346"/>
-      <c r="F11" s="346"/>
+        <v>281</v>
+      </c>
+      <c r="E11" s="347"/>
+      <c r="F11" s="347"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16456,8 +16538,8 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="346"/>
-      <c r="F12" s="346"/>
+      <c r="E12" s="347"/>
+      <c r="F12" s="347"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16474,8 +16556,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="346"/>
-      <c r="F13" s="346"/>
+      <c r="E13" s="347"/>
+      <c r="F13" s="347"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16492,8 +16574,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="346"/>
-      <c r="F14" s="346"/>
+      <c r="E14" s="347"/>
+      <c r="F14" s="347"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16509,7 +16591,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16519,25 +16601,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="346" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="347"/>
+      <c r="E18" s="347" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="348"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="347"/>
-      <c r="F19" s="347"/>
+      <c r="E19" s="348"/>
+      <c r="F19" s="348"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="347"/>
-      <c r="F20" s="347"/>
+        <v>313</v>
+      </c>
+      <c r="E20" s="348"/>
+      <c r="F20" s="348"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16547,12 +16629,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="347"/>
-      <c r="F21" s="347"/>
+      <c r="E21" s="348"/>
+      <c r="F21" s="348"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16562,8 +16644,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="347"/>
-      <c r="F22" s="347"/>
+      <c r="E22" s="348"/>
+      <c r="F22" s="348"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16583,8 +16665,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="345"/>
-      <c r="F25" s="345"/>
+      <c r="E25" s="346"/>
+      <c r="F25" s="346"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16594,8 +16676,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="E26" s="346"/>
+      <c r="F26" s="346"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16609,8 +16691,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="345"/>
-      <c r="F27" s="345"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="346"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16620,8 +16702,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="345"/>
-      <c r="F28" s="345"/>
+      <c r="E28" s="346"/>
+      <c r="F28" s="346"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16641,8 +16723,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="E31" s="346"/>
+      <c r="F31" s="346"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16652,8 +16734,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="345"/>
-      <c r="F32" s="345"/>
+      <c r="E32" s="346"/>
+      <c r="F32" s="346"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16667,8 +16749,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="345"/>
-      <c r="F33" s="345"/>
+      <c r="E33" s="346"/>
+      <c r="F33" s="346"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16678,8 +16760,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="345"/>
-      <c r="F34" s="345"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16699,8 +16781,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="345"/>
-      <c r="F37" s="345"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16710,8 +16792,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="345"/>
-      <c r="F38" s="345"/>
+      <c r="E38" s="346"/>
+      <c r="F38" s="346"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16725,8 +16807,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="345"/>
-      <c r="F39" s="345"/>
+      <c r="E39" s="346"/>
+      <c r="F39" s="346"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16737,8 +16819,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="345"/>
-      <c r="F40" s="345"/>
+      <c r="E40" s="346"/>
+      <c r="F40" s="346"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16800,8 +16882,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="345"/>
-      <c r="F49" s="345"/>
+      <c r="E49" s="346"/>
+      <c r="F49" s="346"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16811,8 +16893,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="345"/>
-      <c r="F50" s="345"/>
+      <c r="E50" s="346"/>
+      <c r="F50" s="346"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16826,8 +16908,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="345"/>
-      <c r="F51" s="345"/>
+      <c r="E51" s="346"/>
+      <c r="F51" s="346"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16837,12 +16919,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="345"/>
-      <c r="F52" s="345"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16858,8 +16940,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="345"/>
-      <c r="F55" s="345"/>
+      <c r="E55" s="346"/>
+      <c r="F55" s="346"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16869,8 +16951,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="345"/>
-      <c r="F56" s="345"/>
+      <c r="E56" s="346"/>
+      <c r="F56" s="346"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16884,8 +16966,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="345"/>
-      <c r="F57" s="345"/>
+      <c r="E57" s="346"/>
+      <c r="F57" s="346"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16895,8 +16977,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="E58" s="346"/>
+      <c r="F58" s="346"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16911,7 +16993,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -16920,7 +17002,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -16929,10 +17011,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -16945,7 +17027,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -16957,7 +17039,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -16973,20 +17055,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -16996,19 +17078,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17018,14 +17100,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17048,7 +17130,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17071,12 +17153,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C123</f>
@@ -17130,12 +17212,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17148,7 +17230,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17158,43 +17240,99 @@
     <row r="88" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
-      <c r="E89" s="320" t="s">
+    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B89" s="109" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B90" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C90" s="135">
+        <f>Thesis!E19</f>
+        <v>3.4500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B91" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="117">
+        <f>PV(C90, C76, -C77, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="117"/>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B92" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="C92" s="117">
+        <f>C60/(1+C90)^C76</f>
+        <v>61.41108960250569</v>
+      </c>
+      <c r="D92" s="117"/>
+    </row>
+    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B93" s="111" t="s">
+        <v>413</v>
+      </c>
+      <c r="C93" s="112">
+        <f>C91+C92</f>
+        <v>61.41108960250569</v>
+      </c>
+      <c r="D93" t="s">
+        <v>410</v>
+      </c>
+      <c r="E93" s="147" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" s="329">
+        <f>(1-C93/C60)</f>
+        <v>9.6748867013066508E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B94" s="100"/>
+    </row>
+    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+      <c r="E95" s="320" t="s">
+        <v>336</v>
+      </c>
+      <c r="F95" s="317"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="316"/>
+    </row>
+    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E96" s="313" t="s">
         <v>337</v>
       </c>
-      <c r="F89" s="317"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="316"/>
-    </row>
-    <row r="90" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E90" s="313" t="s">
+      <c r="F96" s="318" t="s">
         <v>338</v>
       </c>
-      <c r="F90" s="318" t="s">
+      <c r="G96" s="2"/>
+      <c r="H96" s="316"/>
+    </row>
+    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E97" s="314" t="s">
+        <v>337</v>
+      </c>
+      <c r="F97" s="318" t="s">
         <v>339</v>
       </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="316"/>
-    </row>
-    <row r="91" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E91" s="314" t="s">
-        <v>338</v>
-      </c>
-      <c r="F91" s="318" t="s">
+      <c r="G97" s="2"/>
+      <c r="H97" s="316"/>
+    </row>
+    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="E98" s="315" t="s">
+        <v>337</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>340</v>
       </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="316"/>
-    </row>
-    <row r="92" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="E92" s="315" t="s">
-        <v>338</v>
-      </c>
-      <c r="F92" s="319" t="s">
-        <v>341</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="316"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="316"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F410062-E922-4DA6-B885-0374C76748F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE509B16-D88F-4A21-9E9E-32F47F329E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1357,10 +1357,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Stress Test</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Rough Estimate only</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2317,31 +2313,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>@Cash Yield</t>
+    <t>Sell Above</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Market Implied Annual Return:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Buy)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Result (Sell)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sell Above:</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Step 5: Determining the Investment Decision</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
   <si>
-    <t>Sell Above</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Implied Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Result (Sell)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sell Above:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 5: Determining the Investment Decision</t>
+    <t>Liabilities to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Debt to Equity Ratio =</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Est. Realizable Value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt to EBIT Ratio = </t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -3035,7 +3047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="349">
+  <cellXfs count="352">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3731,6 +3743,11 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4043,7 +4060,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J162"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4063,10 +4080,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
@@ -4095,13 +4112,13 @@
     </row>
     <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
@@ -4128,7 +4145,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B8" s="2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4164,24 +4181,24 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="339" t="s">
-        <v>372</v>
-      </c>
-      <c r="C12" s="339"/>
-      <c r="D12" s="339"/>
-      <c r="E12" s="339"/>
-      <c r="F12" s="339"/>
+      <c r="B12" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B14" s="45" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B15" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4191,10 +4208,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4217,19 +4234,19 @@
         <v>57</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
@@ -4241,11 +4258,11 @@
         <v>Target Buy Price (HKD):</v>
       </c>
       <c r="C20" s="252">
-        <f>C129</f>
+        <f>C133</f>
         <v>34.810338706696939</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
@@ -4253,7 +4270,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4268,7 +4285,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A23" s="247" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4277,22 +4294,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="339" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="339"/>
-      <c r="D25" s="339"/>
-      <c r="E25" s="339"/>
-      <c r="F25" s="339"/>
+      <c r="B25" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="B26" s="345" t="s">
+        <v>350</v>
+      </c>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" s="234" t="s">
@@ -4304,13 +4321,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="340" t="s">
+      <c r="B29" s="343" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="340"/>
-      <c r="D29" s="340"/>
-      <c r="E29" s="340"/>
-      <c r="F29" s="340"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" s="47" t="s">
@@ -4330,13 +4347,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="340" t="s">
+      <c r="B32" s="343" t="s">
         <v>235</v>
       </c>
-      <c r="C32" s="340"/>
-      <c r="D32" s="340"/>
-      <c r="E32" s="340"/>
-      <c r="F32" s="340"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="47" t="s">
@@ -4365,13 +4382,13 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="340" t="s">
+      <c r="B36" s="343" t="s">
         <v>238</v>
       </c>
-      <c r="C36" s="340"/>
-      <c r="D36" s="340"/>
-      <c r="E36" s="340"/>
-      <c r="F36" s="340"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B37" s="47" t="s">
@@ -4387,17 +4404,17 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="340" t="s">
+      <c r="B39" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C39" s="340"/>
-      <c r="D39" s="340"/>
-      <c r="E39" s="340"/>
-      <c r="F39" s="340"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="47" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4412,7 +4429,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B41" s="47" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4457,13 +4474,13 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="340" t="s">
+      <c r="B47" s="343" t="s">
         <v>243</v>
       </c>
-      <c r="C47" s="340"/>
-      <c r="D47" s="340"/>
-      <c r="E47" s="340"/>
-      <c r="F47" s="340"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B48" s="47" t="s">
@@ -4479,13 +4496,13 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="340" t="s">
-        <v>350</v>
-      </c>
-      <c r="C50" s="341"/>
-      <c r="D50" s="341"/>
-      <c r="E50" s="341"/>
-      <c r="F50" s="341"/>
+      <c r="B50" s="343" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="344"/>
+      <c r="D50" s="344"/>
+      <c r="E50" s="344"/>
+      <c r="F50" s="344"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B51" s="47" t="s">
@@ -4501,22 +4518,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="339" t="s">
-        <v>355</v>
-      </c>
-      <c r="C53" s="339"/>
-      <c r="D53" s="339"/>
-      <c r="E53" s="339"/>
-      <c r="F53" s="339"/>
+      <c r="B53" s="342" t="s">
+        <v>354</v>
+      </c>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="339" t="s">
-        <v>374</v>
-      </c>
-      <c r="C54" s="339"/>
-      <c r="D54" s="339"/>
-      <c r="E54" s="339"/>
-      <c r="F54" s="339"/>
+      <c r="B54" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B56" s="47" t="s">
@@ -4546,7 +4563,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B58" s="254" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4555,7 +4572,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B59" s="254" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
@@ -4564,7 +4581,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A61" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4577,22 +4594,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="17"/>
-      <c r="B63" s="339" t="s">
-        <v>375</v>
-      </c>
-      <c r="C63" s="339"/>
-      <c r="D63" s="339"/>
-      <c r="E63" s="339"/>
-      <c r="F63" s="339"/>
+      <c r="B63" s="342" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>254</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B66" s="234" t="s">
@@ -4601,7 +4618,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
@@ -4609,26 +4626,26 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
@@ -4645,27 +4662,27 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B72" s="332" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="339" t="s">
+      <c r="B73" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C73" s="339"/>
-      <c r="D73" s="339"/>
-      <c r="E73" s="339"/>
-      <c r="F73" s="339"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="339" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="339"/>
-      <c r="D74" s="339"/>
-      <c r="E74" s="339"/>
-      <c r="F74" s="339"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B76" s="47" t="s">
@@ -4677,7 +4694,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B77" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
@@ -4690,7 +4707,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="A79" s="247" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4702,13 +4719,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="339" t="s">
-        <v>378</v>
-      </c>
-      <c r="C81" s="339"/>
-      <c r="D81" s="339"/>
-      <c r="E81" s="339"/>
-      <c r="F81" s="339"/>
+      <c r="B81" s="342" t="s">
+        <v>377</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B82" s="1" t="s">
@@ -4721,13 +4738,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="339" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="339"/>
-      <c r="D85" s="339"/>
-      <c r="E85" s="339"/>
-      <c r="F85" s="339"/>
+      <c r="B85" s="342" t="s">
+        <v>355</v>
+      </c>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B86" s="47" t="s">
@@ -4744,7 +4761,7 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B87" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="248">
         <f>C86*C28*Exchange_Rate/Common_Shares</f>
@@ -4755,537 +4772,577 @@
         <v>HKD</v>
       </c>
     </row>
+    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B88" s="337" t="s">
+        <v>418</v>
+      </c>
+      <c r="C88" s="338">
+        <f>BS!G30/BS!G27</f>
+        <v>1.2907496012759174</v>
+      </c>
+    </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="337" t="s">
+        <v>419</v>
+      </c>
+      <c r="C89" s="338">
+        <f>BS!G31/BS!G27</f>
+        <v>0.24768740031897937</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B90" s="337" t="s">
+        <v>421</v>
+      </c>
+      <c r="C90" s="339">
+        <f>BS!C50</f>
+        <v>0.73855199466278643</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B92" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B90" s="47" t="s">
+    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B93" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C90" s="188">
+      <c r="C93" s="188">
         <f>BS!C66</f>
         <v>150.19999999999999</v>
       </c>
-      <c r="D90" s="1" t="str">
+      <c r="D93" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="91" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B91" s="47" t="s">
+    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B94" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
         <v>-22.489472833069584</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B92" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*C28*Exchange_Rate/Common_Shares</f>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B95" s="47" t="s">
+        <v>287</v>
+      </c>
+      <c r="C95" s="248">
+        <f>C94*C28*Exchange_Rate/Common_Shares</f>
         <v>-0.6893116784200376</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D95" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B94" s="1" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B97" s="1" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B95" s="47" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B98" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="C95" s="188">
+      <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
         <v>0.39</v>
       </c>
-      <c r="D95" s="1" t="str">
+      <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B96" s="47" t="s">
-        <v>289</v>
-      </c>
-      <c r="C96" s="248">
-        <f>C95*C28*Exchange_Rate/Common_Shares</f>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B99" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C99" s="248">
+        <f>C98*C28*Exchange_Rate/Common_Shares</f>
         <v>1.1953661901247949E-2</v>
       </c>
-      <c r="D96" s="1" t="str">
+      <c r="D99" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B98" s="339" t="s">
-        <v>379</v>
-      </c>
-      <c r="C98" s="339"/>
-      <c r="D98" s="339"/>
-      <c r="E98" s="339"/>
-      <c r="F98" s="339"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B100" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C100" s="248">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B101" s="342" t="s">
+        <v>378</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B103" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
         <v>60.265334487116725</v>
       </c>
-      <c r="D100" s="1" t="str">
+      <c r="D103" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A102" s="247" t="s">
-        <v>371</v>
-      </c>
-      <c r="B102" s="36"/>
-      <c r="C102" s="36"/>
-      <c r="D102" s="36"/>
-      <c r="E102" s="36"/>
-      <c r="F102" s="36"/>
-    </row>
-    <row r="104" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="340" t="s">
-        <v>380</v>
-      </c>
-      <c r="C104" s="340"/>
-      <c r="D104" s="340"/>
-      <c r="E104" s="340"/>
-      <c r="F104" s="340"/>
-    </row>
-    <row r="106" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
-      <c r="B106" s="260" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="337" t="s">
+        <v>420</v>
+      </c>
+      <c r="C104" s="248">
+        <f>BS!D47</f>
+        <v>-2.643445053008028</v>
+      </c>
+      <c r="D104" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A106" s="247" t="s">
+        <v>370</v>
+      </c>
+      <c r="B106" s="36"/>
+      <c r="C106" s="36"/>
+      <c r="D106" s="36"/>
+      <c r="E106" s="36"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B108" s="343" t="s">
+        <v>379</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+      <c r="B110" s="260" t="s">
         <v>119</v>
       </c>
-      <c r="C106" s="260" t="s">
+      <c r="C110" s="260" t="s">
         <v>134</v>
       </c>
-      <c r="D106" s="260" t="s">
+      <c r="D110" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="E106" s="260" t="s">
+      <c r="E110" s="260" t="s">
         <v>261</v>
       </c>
-      <c r="F106" s="260" t="s">
+      <c r="F110" s="260" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B107" s="255" t="str">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C107" s="256">
+      <c r="C111" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D107" s="257">
+      <c r="D111" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E107" s="258" t="str">
+      <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>95.78 HKD</v>
       </c>
-      <c r="F107" s="259">
+      <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B108" s="242" t="str">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C108" s="243">
+      <c r="C112" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D108" s="244">
+      <c r="D112" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E108" s="245" t="str">
+      <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>71.68 HKD</v>
       </c>
-      <c r="F108" s="246">
+      <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B109" s="242" t="str">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C109" s="243">
+      <c r="C113" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.03</v>
       </c>
-      <c r="D109" s="244">
+      <c r="D113" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E109" s="245" t="str">
+      <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>66.78 HKD</v>
       </c>
-      <c r="F109" s="246">
+      <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="242" t="str">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C110" s="243">
+      <c r="C114" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.01</v>
       </c>
-      <c r="D110" s="244">
+      <c r="D114" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E110" s="245" t="str">
+      <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>62.34 HKD</v>
       </c>
-      <c r="F110" s="246">
+      <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="242" t="str">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C111" s="243">
+      <c r="C115" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D111" s="244">
+      <c r="D115" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E111" s="245" t="str">
+      <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>60.27 HKD</v>
       </c>
-      <c r="F111" s="246">
+      <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B113" s="235" t="s">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B117" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="C113" s="241">
+      <c r="C117" s="241">
         <f>Scenarios!C60</f>
         <v>67.988942786517455</v>
       </c>
-      <c r="D113" s="236" t="str">
+      <c r="D117" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B115" s="343" t="s">
-        <v>383</v>
-      </c>
-      <c r="C115" s="343"/>
-      <c r="D115" s="343"/>
-      <c r="E115" s="343"/>
-      <c r="F115" s="343"/>
-    </row>
-    <row r="117" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A117" s="247" t="s">
-        <v>418</v>
-      </c>
-      <c r="B117" s="36"/>
-      <c r="C117" s="36"/>
-      <c r="D117" s="36"/>
-      <c r="E117" s="36"/>
-      <c r="F117" s="36"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B119" s="344" t="s">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B119" s="346" t="s">
+        <v>382</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A121" s="247" t="s">
+        <v>416</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B123" s="347" t="s">
+        <v>380</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B124" s="342" t="s">
         <v>381</v>
       </c>
-      <c r="C119" s="344"/>
-      <c r="D119" s="344"/>
-      <c r="E119" s="344"/>
-      <c r="F119" s="344"/>
-    </row>
-    <row r="120" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="339" t="s">
-        <v>382</v>
-      </c>
-      <c r="C120" s="339"/>
-      <c r="D120" s="339"/>
-      <c r="E120" s="339"/>
-      <c r="F120" s="339"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B121" s="234" t="s">
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B125" s="234" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B122" s="1" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B126" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="C122" s="251">
+      <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C123" s="250">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B127" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B124" s="236" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B128" s="236" t="s">
         <v>263</v>
       </c>
-      <c r="C124" s="237">
+      <c r="C128" s="237">
         <f>Scenarios!C77</f>
         <v>0</v>
       </c>
-      <c r="D124" s="236" t="str">
+      <c r="D128" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B126" s="234" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B127" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B130" s="234" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B131" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C127" s="240">
+      <c r="C131" s="240">
         <f>Scenarios!C81</f>
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B128" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B132" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C128" s="240">
+      <c r="C132" s="240">
         <f>Scenarios!C82</f>
         <v>34.810338706696939</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B129" s="80" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B133" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="C129" s="239">
+      <c r="C133" s="239">
         <f>Scenarios!C83</f>
         <v>34.810338706696939</v>
       </c>
-      <c r="D129" s="47" t="str">
+      <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B130" s="238" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B134" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C130" s="92">
+      <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.48799999999999999</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B132" s="234" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B133" s="236" t="str">
-        <f>"PV("&amp;C122&amp;" yrs of Dividends)"</f>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B136" s="234" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C133" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C91</f>
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B134" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C122&amp;")"</f>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C134" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>61.41108960250569</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B135" s="80" t="s">
-        <v>417</v>
-      </c>
-      <c r="C135" s="239">
+        <v>57.531434982190753</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B139" s="80" t="s">
+        <v>415</v>
+      </c>
+      <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>61.41108960250569</v>
-      </c>
-      <c r="D135" s="101" t="str">
+        <v>57.531434982190753</v>
+      </c>
+      <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B136" s="238" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B140" s="238" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="92">
+      <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>9.6748867013066508E-2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
-      <c r="A138" s="247" t="s">
+        <v>0.15381189022401565</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+      <c r="A142" s="247" t="s">
+        <v>386</v>
+      </c>
+      <c r="B142" s="36"/>
+      <c r="C142" s="36"/>
+      <c r="D142" s="36"/>
+      <c r="E142" s="36"/>
+      <c r="F142" s="36"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B144" s="341" t="s">
+        <v>388</v>
+      </c>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
+    </row>
+    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B146" s="234" t="s">
         <v>387</v>
       </c>
-      <c r="B138" s="36"/>
-      <c r="C138" s="36"/>
-      <c r="D138" s="36"/>
-      <c r="E138" s="36"/>
-      <c r="F138" s="36"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B140" s="338" t="s">
+    </row>
+    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B147" s="344" t="s">
+        <v>392</v>
+      </c>
+      <c r="C147" s="344"/>
+      <c r="D147" s="344"/>
+      <c r="E147" s="344"/>
+      <c r="F147" s="344"/>
+    </row>
+    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B148" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C140" s="339"/>
-      <c r="D140" s="339"/>
-      <c r="E140" s="339"/>
-      <c r="F140" s="339"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B142" s="234" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B143" s="341" t="s">
+    </row>
+    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B149" s="238" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B150" s="238" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B152" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B153" s="343" t="s">
         <v>393</v>
       </c>
-      <c r="C143" s="341"/>
-      <c r="D143" s="341"/>
-      <c r="E143" s="341"/>
-      <c r="F143" s="341"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="238" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="145" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B145" s="238" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="238" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B148" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="149" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B149" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C149" s="340"/>
-      <c r="D149" s="340"/>
-      <c r="E149" s="340"/>
-      <c r="F149" s="340"/>
-    </row>
-    <row r="151" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B151" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="152" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B152" s="337" t="s">
-        <v>395</v>
-      </c>
-      <c r="C152" s="337"/>
-      <c r="D152" s="337"/>
-      <c r="E152" s="337"/>
-      <c r="F152" s="337"/>
-    </row>
-    <row r="153" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="337" t="s">
-        <v>396</v>
-      </c>
-      <c r="C153" s="337"/>
-      <c r="D153" s="337"/>
-      <c r="E153" s="337"/>
-      <c r="F153" s="337"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B155" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B156" s="238" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B156" s="340" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B157" s="340" t="s">
+        <v>395</v>
+      </c>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
+    </row>
+    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B159" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B160" s="238" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B161" s="238" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="157" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B162" s="238" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="158" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B158" s="238" t="s">
-        <v>401</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B120:F120"/>
+    <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B25:F25"/>
@@ -5294,24 +5351,24 @@
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="B74:F74"/>
     <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B123:F123"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B115:F115"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5874,7 +5931,7 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B22" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C22" s="181">
         <v>355.2</v>
@@ -5908,7 +5965,7 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B23" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C23" s="181">
         <v>-54.4</v>
@@ -5942,7 +5999,7 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B24" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C24" s="181">
         <v>-171.1</v>
@@ -5996,7 +6053,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.35">
@@ -7275,7 +7332,7 @@
     </row>
     <row r="64" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B64" s="27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8651,7 +8708,7 @@
         <v>138</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>274</v>
+        <v>420</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>60</v>
@@ -8659,7 +8716,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8812,7 +8869,7 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="158" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C61" s="262" t="s">
         <v>139</v>
@@ -8835,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8857,7 +8914,7 @@
         <v>138</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F65" s="287" t="s">
         <v>60</v>
@@ -8924,7 +8981,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B72" s="285" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C72" s="261" t="s">
         <v>97</v>
@@ -8936,7 +8993,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -8947,12 +9004,12 @@
         <v>-172.68947283306957</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="288" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -8963,12 +9020,12 @@
         <v>0.86976928897797345</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -8976,12 +9033,12 @@
         <v>172.68947283306957</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="290" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -8989,7 +9046,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9065,7 +9122,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B84" s="79" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9076,15 +9133,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B85" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D85" s="270" t="s">
         <v>299</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B86" s="267" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9101,7 +9158,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B87" s="267" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9135,7 +9192,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B89" s="80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -10006,7 +10063,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10031,7 +10088,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10359,7 +10416,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10419,7 +10476,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10543,7 +10600,7 @@
         <v>-78.45</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10601,7 +10658,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10909,7 +10966,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11048,7 +11105,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11103,7 +11160,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11236,7 +11293,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11263,7 +11320,7 @@
         <v>3.1551835157759174E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11578,7 +11635,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12139,7 +12196,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12818,7 +12875,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -13512,7 +13569,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13564,7 +13621,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14073,7 +14130,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B126" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14902,10 +14959,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="345" t="s">
+      <c r="E6" s="348" t="s">
         <v>251</v>
       </c>
-      <c r="F6" s="345"/>
+      <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.35">
@@ -14920,8 +14977,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
+      <c r="E7" s="348"/>
+      <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
@@ -14936,8 +14993,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="345"/>
-      <c r="F8" s="345"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.35">
@@ -14952,8 +15009,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="345"/>
-      <c r="F9" s="345"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
@@ -16298,7 +16355,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B80" s="156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>107</v>
@@ -16370,7 +16427,7 @@
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="I2" s="278"/>
     </row>
@@ -16424,7 +16481,7 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16437,7 +16494,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16447,11 +16504,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="347" t="str">
+      <c r="E7" s="350" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="347"/>
+      <c r="F7" s="350"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16472,8 +16529,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="347"/>
-      <c r="F8" s="347"/>
+      <c r="E8" s="350"/>
+      <c r="F8" s="350"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16494,8 +16551,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="347"/>
-      <c r="F9" s="347"/>
+      <c r="E9" s="350"/>
+      <c r="F9" s="350"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16505,8 +16562,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="E10" s="347"/>
-      <c r="F10" s="347"/>
+      <c r="E10" s="350"/>
+      <c r="F10" s="350"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16517,10 +16574,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B11" s="160" t="s">
-        <v>281</v>
-      </c>
-      <c r="E11" s="347"/>
-      <c r="F11" s="347"/>
+        <v>280</v>
+      </c>
+      <c r="E11" s="350"/>
+      <c r="F11" s="350"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16538,8 +16595,8 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="347"/>
-      <c r="F12" s="347"/>
+      <c r="E12" s="350"/>
+      <c r="F12" s="350"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16556,8 +16613,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="347"/>
-      <c r="F13" s="347"/>
+      <c r="E13" s="350"/>
+      <c r="F13" s="350"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16574,8 +16631,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="347"/>
-      <c r="F14" s="347"/>
+      <c r="E14" s="350"/>
+      <c r="F14" s="350"/>
     </row>
     <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B16" s="36" t="s">
@@ -16591,7 +16648,7 @@
         <v>153</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
@@ -16601,25 +16658,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="347" t="s">
-        <v>342</v>
-      </c>
-      <c r="F18" s="348"/>
+      <c r="E18" s="350" t="s">
+        <v>341</v>
+      </c>
+      <c r="F18" s="351"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="E19" s="348"/>
-      <c r="F19" s="348"/>
+      <c r="E19" s="351"/>
+      <c r="F19" s="351"/>
     </row>
     <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B20" s="160" t="s">
-        <v>313</v>
-      </c>
-      <c r="E20" s="348"/>
-      <c r="F20" s="348"/>
+        <v>312</v>
+      </c>
+      <c r="E20" s="351"/>
+      <c r="F20" s="351"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B21" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16629,12 +16686,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="348"/>
-      <c r="F21" s="348"/>
+      <c r="E21" s="351"/>
+      <c r="F21" s="351"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B22" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16644,8 +16701,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="348"/>
-      <c r="F22" s="348"/>
+      <c r="E22" s="351"/>
+      <c r="F22" s="351"/>
     </row>
     <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B24" s="160" t="s">
@@ -16665,8 +16722,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="346"/>
-      <c r="F25" s="346"/>
+      <c r="E25" s="349"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B26" s="119" t="s">
@@ -16676,8 +16733,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="346"/>
-      <c r="F26" s="346"/>
+      <c r="E26" s="349"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B27" s="100" t="s">
@@ -16691,8 +16748,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="346"/>
-      <c r="F27" s="346"/>
+      <c r="E27" s="349"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B28" s="100" t="s">
@@ -16702,8 +16759,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="346"/>
-      <c r="F28" s="346"/>
+      <c r="E28" s="349"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B30" s="160" t="s">
@@ -16723,8 +16780,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="346"/>
-      <c r="F31" s="346"/>
+      <c r="E31" s="349"/>
+      <c r="F31" s="349"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B32" s="119" t="s">
@@ -16734,8 +16791,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="346"/>
-      <c r="F32" s="346"/>
+      <c r="E32" s="349"/>
+      <c r="F32" s="349"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B33" s="100" t="s">
@@ -16749,8 +16806,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="346"/>
-      <c r="F33" s="346"/>
+      <c r="E33" s="349"/>
+      <c r="F33" s="349"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B34" s="100" t="s">
@@ -16760,8 +16817,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="E34" s="349"/>
+      <c r="F34" s="349"/>
     </row>
     <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B36" s="160" t="s">
@@ -16781,8 +16838,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B38" s="119" t="s">
@@ -16792,8 +16849,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="346"/>
-      <c r="F38" s="346"/>
+      <c r="E38" s="349"/>
+      <c r="F38" s="349"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B39" s="100" t="s">
@@ -16807,8 +16864,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="346"/>
-      <c r="F39" s="346"/>
+      <c r="E39" s="349"/>
+      <c r="F39" s="349"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B40" s="100" t="s">
@@ -16819,8 +16876,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="346"/>
-      <c r="F40" s="346"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B42" s="100" t="s">
@@ -16882,8 +16939,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="346"/>
-      <c r="F49" s="346"/>
+      <c r="E49" s="349"/>
+      <c r="F49" s="349"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" s="119" t="s">
@@ -16893,8 +16950,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="346"/>
-      <c r="F50" s="346"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" s="100" t="s">
@@ -16908,8 +16965,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="346"/>
-      <c r="F51" s="346"/>
+      <c r="E51" s="349"/>
+      <c r="F51" s="349"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" s="100" t="s">
@@ -16919,12 +16976,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="E52" s="349"/>
+      <c r="F52" s="349"/>
     </row>
     <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B54" s="160" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>151</v>
@@ -16940,8 +16997,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="346"/>
-      <c r="F55" s="346"/>
+      <c r="E55" s="349"/>
+      <c r="F55" s="349"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B56" s="119" t="s">
@@ -16951,8 +17008,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="346"/>
-      <c r="F56" s="346"/>
+      <c r="E56" s="349"/>
+      <c r="F56" s="349"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B57" s="100" t="s">
@@ -16966,8 +17023,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="346"/>
-      <c r="F57" s="346"/>
+      <c r="E57" s="349"/>
+      <c r="F57" s="349"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B58" s="100" t="s">
@@ -16977,8 +17034,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="346"/>
-      <c r="F58" s="346"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B60" s="100" t="s">
@@ -16993,7 +17050,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
@@ -17002,7 +17059,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
       <c r="B62" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17011,10 +17068,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B63" s="109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.35">
@@ -17027,7 +17084,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.35">
@@ -17039,7 +17096,7 @@
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.35">
@@ -17055,20 +17112,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B68" s="109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B69" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17078,19 +17135,19 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B70" s="100" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B71" s="100" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17100,14 +17157,14 @@
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B72" s="100" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17130,7 +17187,7 @@
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B76" s="275" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17153,15 +17210,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B79" s="109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B80" s="149" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C123</f>
+        <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
@@ -17212,12 +17269,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B85" s="109" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B86" s="149" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17230,7 +17287,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B87" s="100" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -17242,16 +17299,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B89" s="109" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B90" s="149" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C90" s="135">
-        <f>Thesis!E19</f>
-        <v>3.4500000000000003E-2</v>
+        <f>(Thesis!E19+Thesis!C67)/2</f>
+        <v>5.7250000000000002E-2</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.35">
@@ -17270,27 +17327,27 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>61.41108960250569</v>
+        <v>57.531434982190753</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
       <c r="B93" s="111" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>61.41108960250569</v>
+        <v>57.531434982190753</v>
       </c>
       <c r="D93" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>128</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>9.6748867013066508E-2</v>
+        <v>0.15381189022401565</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.35">
@@ -17298,7 +17355,7 @@
     </row>
     <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
       <c r="E95" s="320" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
@@ -17306,30 +17363,30 @@
     </row>
     <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E96" s="313" t="s">
+        <v>336</v>
+      </c>
+      <c r="F96" s="318" t="s">
         <v>337</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>338</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
     <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E97" s="314" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
     <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
       <c r="E98" s="315" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F98" s="319" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE509B16-D88F-4A21-9E9E-32F47F329E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6A106C-DF3B-43B8-8A6D-F8BEB8F6066A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <definedName name="Market_currency">Thesis!$D$6</definedName>
     <definedName name="Market_Price">Thesis!$C$6</definedName>
     <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -180,10 +181,6 @@
   </si>
   <si>
     <t>Total Liabilities</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HKD</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1417,10 +1414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Base Cost of Equity</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1582,10 +1575,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1793,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2357,23 +2342,37 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Implied Return</t>
+  </si>
+  <si>
+    <t>Target Return</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>偉易達</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>0303.HK</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>USD</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CNS_02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -2381,26 +2380,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="18">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.00\x"/>
-    <numFmt numFmtId="180" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="181" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ "/>
-    <numFmt numFmtId="183" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="184" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="185" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="186" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="187" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="188" formatCode="0.000_ "/>
-    <numFmt numFmtId="189" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0.00\)"/>
-    <numFmt numFmtId="191" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="192" formatCode="0.0\x"/>
-    <numFmt numFmtId="193" formatCode="0\x"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_);\(#,##0.00\)"/>
+    <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="180" formatCode="0.0\x"/>
+    <numFmt numFmtId="181" formatCode="0\x"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3075,7 +3074,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3117,23 +3116,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3142,13 +3141,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3219,10 +3218,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3233,7 +3232,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3271,7 +3270,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3281,7 +3280,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3292,29 +3291,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="185" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="185" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="184" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3330,7 +3329,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3344,38 +3343,38 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="39" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="186" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="187" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3395,17 +3394,17 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="186" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3420,11 +3419,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3433,51 +3432,51 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3493,7 +3492,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -3527,21 +3526,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="186" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3550,7 +3549,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3560,13 +3559,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="186" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3577,7 +3576,7 @@
     <xf numFmtId="10" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="43" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3596,9 +3595,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3607,23 +3606,23 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3641,13 +3640,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3655,7 +3654,7 @@
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3692,7 +3691,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3714,21 +3713,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="193" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="187" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3739,7 +3738,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="189" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3747,30 +3746,30 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4061,7 +4060,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J162"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
@@ -4071,24 +4070,24 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" s="44">
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.9" x14ac:dyDescent="0.45">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="247" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4100,7 +4099,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="str">
         <f>D5&amp;" Stock Information"</f>
         <v>0303.HK Stock Information</v>
@@ -4110,30 +4109,30 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
+        <v>421</v>
+      </c>
+      <c r="D5" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" s="50">
         <v>52.2</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>41</v>
+        <v>405</v>
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
@@ -4143,9 +4142,9 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="B8" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C8" s="279">
         <v>6</v>
@@ -4153,9 +4152,9 @@
       <c r="D8" s="5"/>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="B9" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C9" s="33">
         <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
@@ -4164,7 +4163,7 @@
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="B10" s="4" t="str">
         <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
         <v>Capitalization (HKD):</v>
@@ -4176,29 +4175,29 @@
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="342" t="s">
-        <v>371</v>
-      </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="24.4" customHeight="1">
+      <c r="B12" s="340" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="B15" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4206,17 +4205,17 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="B17" s="4" t="s">
         <v>1</v>
       </c>
@@ -4229,30 +4228,30 @@
       </c>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="B18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C19" s="249">
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E19" s="336">
         <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="B20" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
@@ -4262,15 +4261,15 @@
         <v>34.810338706696939</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E20" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4279,13 +4278,13 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4293,45 +4292,45 @@
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
     </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="342" t="s">
-        <v>372</v>
-      </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="345" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B25" s="340" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
+    </row>
+    <row r="26" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B26" s="342" t="s">
+        <v>347</v>
+      </c>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
+    </row>
+    <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" s="108">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C28" s="108">
-        <f>Data!C3</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="343" t="s">
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="B30" s="47" t="s">
         <v>233</v>
-      </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B30" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="C30" s="188">
         <f>Normalized_FCF!C8</f>
@@ -4342,22 +4341,22 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="B31" s="47"/>
       <c r="C31" s="76"/>
     </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="343" t="s">
+    <row r="32" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B32" s="341" t="s">
+        <v>234</v>
+      </c>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="47" t="s">
         <v>235</v>
-      </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B33" s="47" t="s">
-        <v>236</v>
       </c>
       <c r="C33" s="188">
         <f>Normalized_FCF!C9</f>
@@ -4368,9 +4367,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C34" s="188">
         <f>Normalized_FCF!C10</f>
@@ -4381,18 +4380,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B36" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="341" t="s">
+        <v>237</v>
+      </c>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="47" t="s">
         <v>238</v>
-      </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B37" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="C37" s="188">
         <f>Normalized_FCF!C11</f>
@@ -4403,18 +4402,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B39" s="343" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
+      <c r="B39" s="341" t="s">
+        <v>241</v>
+      </c>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C40" s="322">
         <f>Normalized_FCF!C48</f>
@@ -4427,9 +4426,9 @@
       <c r="E40" s="321"/>
       <c r="F40" s="321"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:6">
       <c r="B41" s="47" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C41" s="322">
         <f>Normalized_FCF!C47</f>
@@ -4442,9 +4441,9 @@
       <c r="E41" s="321"/>
       <c r="F41" s="321"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C42" s="188">
         <f>Normalized_FCF!C12</f>
@@ -4455,14 +4454,14 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:6">
       <c r="B44" s="1" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C45" s="188">
         <f>Normalized_FCF!C15</f>
@@ -4473,18 +4472,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B47" s="343" t="s">
-        <v>243</v>
-      </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:6">
+      <c r="B47" s="341" t="s">
+        <v>242</v>
+      </c>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C48" s="188">
         <f>Normalized_FCF!C14</f>
@@ -4495,18 +4494,18 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B50" s="343" t="s">
-        <v>349</v>
+    <row r="50" spans="1:6">
+      <c r="B50" s="341" t="s">
+        <v>346</v>
       </c>
       <c r="C50" s="344"/>
       <c r="D50" s="344"/>
       <c r="E50" s="344"/>
       <c r="F50" s="344"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="B51" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="1">
         <f>Normalized_FCF!C17</f>
@@ -4517,27 +4516,27 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="342" t="s">
-        <v>354</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="342" t="s">
-        <v>373</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B53" s="340" t="s">
+        <v>351</v>
+      </c>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
+    </row>
+    <row r="54" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B54" s="340" t="s">
+        <v>369</v>
+      </c>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="188">
         <f>Normalized_FCF!G19</f>
@@ -4548,9 +4547,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6">
       <c r="B57" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C57" s="188">
         <f>Normalized_FCF!C19</f>
@@ -4561,27 +4560,27 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.10069379612803481</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6">
       <c r="B59" s="254" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4589,115 +4588,115 @@
       <c r="E61" s="36"/>
       <c r="F61" s="36"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6">
       <c r="A62" s="233"/>
     </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B64" s="345" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B63" s="340" t="s">
+        <v>370</v>
+      </c>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="342" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
+    </row>
+    <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C67" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6">
       <c r="B68" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C68" s="263">
         <f>IF(D68="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="B69" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C69" s="263">
         <f>IF(D69="Y",1%,0)</f>
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="B70" s="80" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C70" s="263">
         <f>SUM(C67:C69)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6">
       <c r="C71" s="122"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C72" s="122"/>
     </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="342" t="s">
-        <v>375</v>
-      </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="342" t="s">
-        <v>376</v>
-      </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B73" s="340" t="s">
+        <v>371</v>
+      </c>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="340" t="s">
+        <v>372</v>
+      </c>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C76" s="263">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6">
       <c r="B77" s="47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C77" s="248">
-        <f>Valuation_Model!C6*C28*Exchange_Rate/Common_Shares</f>
+        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>65.702701973542702</v>
       </c>
       <c r="D77" s="1" t="str">
@@ -4705,9 +4704,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4715,40 +4714,40 @@
       <c r="E79" s="36"/>
       <c r="F79" s="36"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6">
       <c r="A80" s="233"/>
     </row>
-    <row r="81" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B81" s="342" t="s">
-        <v>377</v>
-      </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:6">
+      <c r="B81" s="340" t="s">
+        <v>373</v>
+      </c>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="84" spans="2:6" x14ac:dyDescent="0.35">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B85" s="342" t="s">
-        <v>355</v>
-      </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B85" s="340" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C86" s="188">
         <f>Valuation_Model!C7</f>
@@ -4759,12 +4758,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:6">
       <c r="B87" s="47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C87" s="248">
-        <f>C86*C28*Exchange_Rate/Common_Shares</f>
+        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>4.760009469907196</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4772,41 +4771,41 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:6">
       <c r="B88" s="337" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C88" s="338">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
-    <row r="89" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:6">
       <c r="B89" s="337" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C89" s="338">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
-    <row r="90" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:6">
       <c r="B90" s="337" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C90" s="339">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
     </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:6">
       <c r="B92" s="1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="93" spans="2:6" x14ac:dyDescent="0.35">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="188">
         <f>BS!C66</f>
@@ -4817,9 +4816,9 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="94" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:6">
       <c r="B94" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
@@ -4830,12 +4829,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="95" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:6">
       <c r="B95" s="47" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C95" s="248">
-        <f>C94*C28*Exchange_Rate/Common_Shares</f>
+        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-0.6893116784200376</v>
       </c>
       <c r="D95" s="1" t="str">
@@ -4843,14 +4842,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6">
       <c r="B97" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B98" s="47" t="s">
-        <v>259</v>
       </c>
       <c r="C98" s="188">
         <f>Valuation_Model!C9</f>
@@ -4861,12 +4860,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C99" s="248">
-        <f>C98*C28*Exchange_Rate/Common_Shares</f>
+        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.1953661901247949E-2</v>
       </c>
       <c r="D99" s="1" t="str">
@@ -4874,18 +4873,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B101" s="342" t="s">
-        <v>378</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B101" s="340" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
+    </row>
+    <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
@@ -4896,9 +4895,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6">
       <c r="B104" s="337" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4909,9 +4908,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4919,33 +4918,33 @@
       <c r="E106" s="36"/>
       <c r="F106" s="36"/>
     </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B108" s="343" t="s">
-        <v>379</v>
-      </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B108" s="341" t="s">
+        <v>375</v>
+      </c>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
+    </row>
+    <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C110" s="260" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D110" s="260" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E110" s="260" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F110" s="260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="B111" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
@@ -4967,7 +4966,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6">
       <c r="B112" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
@@ -4989,7 +4988,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="B113" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
@@ -5011,7 +5010,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6">
       <c r="B114" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
@@ -5033,7 +5032,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6">
       <c r="B115" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
@@ -5055,9 +5054,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6">
       <c r="B117" s="235" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
@@ -5068,18 +5067,18 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="346" t="s">
-        <v>382</v>
-      </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B119" s="345" t="s">
+        <v>378</v>
+      </c>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5087,50 +5086,50 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B123" s="347" t="s">
-        <v>380</v>
-      </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B124" s="342" t="s">
-        <v>381</v>
-      </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6">
+      <c r="B123" s="343" t="s">
+        <v>376</v>
+      </c>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="340" t="s">
+        <v>377</v>
+      </c>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
+    </row>
+    <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="B126" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C126" s="251">
         <f>E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6">
       <c r="B127" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" s="250">
         <f>C19</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6">
       <c r="B128" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
@@ -5141,12 +5140,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+        <v>409</v>
+      </c>
+      <c r="C130" s="338">
+        <f>C19</f>
+        <v>0.25</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5156,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5166,9 +5172,9 @@
         <v>34.810338706696939</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6">
       <c r="B133" s="80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
@@ -5179,21 +5185,28 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="B134" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
         <v>0.48799999999999999</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+        <v>410</v>
+      </c>
+      <c r="C136" s="92">
+        <f>Scenarios!C90</f>
+        <v>0.06</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5203,41 +5216,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>57.531434982190753</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+        <v>57.084827396539964</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>57.531434982190753</v>
+        <v>57.084827396539964</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6">
       <c r="B140" s="238" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.15381189022401565</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" ht="13.9" x14ac:dyDescent="0.45">
+        <v>0.16038071696769829</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" ht="13.9">
       <c r="A142" s="247" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
@@ -5245,103 +5258,114 @@
       <c r="E142" s="36"/>
       <c r="F142" s="36"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B144" s="341" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="347" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+    </row>
+    <row r="146" spans="2:6">
+      <c r="B146" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
+      <c r="B147" s="344" t="s">
         <v>388</v>
-      </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B146" s="234" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="147" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B147" s="344" t="s">
-        <v>392</v>
       </c>
       <c r="C147" s="344"/>
       <c r="D147" s="344"/>
       <c r="E147" s="344"/>
       <c r="F147" s="344"/>
     </row>
-    <row r="148" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="2:6">
       <c r="B148" s="238" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
+      <c r="B149" s="238" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
+      <c r="B150" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="152" spans="2:6">
+      <c r="B152" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="153" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="149" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B149" s="238" t="s">
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
+    </row>
+    <row r="155" spans="2:6">
+      <c r="B155" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="150" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B150" s="238" t="s">
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
+    </row>
+    <row r="157" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="152" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B152" s="1" t="s">
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
+    </row>
+    <row r="159" spans="2:6">
+      <c r="B159" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="160" spans="2:6">
+      <c r="B160" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="238" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B153" s="343" t="s">
-        <v>393</v>
-      </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B155" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B156" s="340" t="s">
-        <v>394</v>
-      </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B157" s="340" t="s">
-        <v>395</v>
-      </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B159" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="160" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B160" s="238" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B161" s="238" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B162" s="238" t="s">
-        <v>400</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5358,17 +5382,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -5393,7 +5406,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
@@ -5401,7 +5414,7 @@
     <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
@@ -5450,9 +5463,9 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -5466,7 +5479,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5474,7 +5487,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5508,9 +5521,9 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="181">
         <v>1510.8</v>
@@ -5542,9 +5555,9 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="181">
         <f>77.9+C7</f>
@@ -5585,9 +5598,9 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" s="189">
         <v>278.39999999999998</v>
@@ -5619,9 +5632,9 @@
       <c r="L7" s="189"/>
       <c r="M7" s="189"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" s="181">
         <v>81.7</v>
@@ -5653,9 +5666,9 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C9" s="181"/>
       <c r="D9" s="181"/>
@@ -5669,9 +5682,9 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10" s="181"/>
       <c r="D10" s="181"/>
@@ -5685,9 +5698,9 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C11" s="181"/>
       <c r="D11" s="181"/>
@@ -5701,7 +5714,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -5735,9 +5748,9 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C13" s="181"/>
       <c r="D13" s="181"/>
@@ -5751,9 +5764,9 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="181">
         <v>24.7</v>
@@ -5785,9 +5798,9 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="182">
         <v>166.6</v>
@@ -5819,9 +5832,9 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="181">
         <v>0</v>
@@ -5853,15 +5866,15 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="181"/>
       <c r="D19" s="181"/>
@@ -5875,9 +5888,9 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C20" s="181">
         <v>-32.4</v>
@@ -5901,9 +5914,9 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="181">
         <v>117.9</v>
@@ -5929,9 +5942,9 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>355.2</v>
@@ -5963,9 +5976,9 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-54.4</v>
@@ -5997,9 +6010,9 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-171.1</v>
@@ -6031,7 +6044,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6048,7 +6061,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6056,7 +6069,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6083,7 +6096,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6110,7 +6123,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6145,7 +6158,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6180,9 +6193,9 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C32" s="183">
         <f>BS!G28</f>
@@ -6215,9 +6228,9 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6231,12 +6244,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6285,9 +6298,9 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37" s="183">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -6334,9 +6347,9 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C38" s="184">
         <f>IF(C36="","",C36+C37)</f>
@@ -6383,9 +6396,9 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="183">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -6432,9 +6445,9 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="185">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -6481,9 +6494,9 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C41" s="185">
         <f>IF(C$4="","",C39-C40)</f>
@@ -6530,9 +6543,9 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" s="183">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -6579,9 +6592,9 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C43" s="186">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -6628,9 +6641,9 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C44" s="187">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -6677,9 +6690,9 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C45" s="188">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -6726,9 +6739,9 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="183">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -6775,9 +6788,9 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="186">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -6824,9 +6837,9 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="183">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -6873,12 +6886,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -6927,9 +6940,9 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" s="183">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -6976,14 +6989,14 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C55" s="188">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7030,9 +7043,9 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C56" s="188">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7079,9 +7092,9 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" s="188">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7128,9 +7141,9 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C58" s="188">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7177,15 +7190,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C61" s="183">
         <f>IF(C$4="","",-C19)</f>
@@ -7232,9 +7245,9 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="183">
         <f>IF(C$4="","",-C20)</f>
@@ -7281,9 +7294,9 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C63" s="183">
         <f>IF(C$4="","",-C21)</f>
@@ -7330,9 +7343,9 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -7379,7 +7392,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7428,12 +7441,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7483,9 +7496,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -7532,7 +7545,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -7582,9 +7595,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -7631,7 +7644,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -7681,9 +7694,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -7697,13 +7710,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -7752,9 +7765,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" s="185">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -7786,9 +7799,9 @@
       <c r="L77" s="335"/>
       <c r="M77" s="335"/>
     </row>
-    <row r="78" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C78" s="185">
         <f t="shared" si="40"/>
@@ -7820,7 +7833,7 @@
       <c r="L78" s="335"/>
       <c r="M78" s="335"/>
     </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -7869,7 +7882,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -7950,7 +7963,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -7961,7 +7974,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -7973,13 +7986,13 @@
         <v>Quarter Report</v>
       </c>
       <c r="H1" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -7988,27 +8001,27 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D3" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G3" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H3" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8020,7 +8033,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="19">
         <v>150.19999999999999</v>
@@ -8029,7 +8042,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8050,7 +8063,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8062,7 +8075,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8071,9 +8084,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8083,7 +8096,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8092,9 +8105,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8104,7 +8117,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8113,7 +8126,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8125,7 +8138,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8134,7 +8147,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8146,7 +8159,7 @@
       </c>
       <c r="H10" s="295"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8158,9 +8171,9 @@
       </c>
       <c r="H11" s="295"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8171,7 +8184,7 @@
         <v>546.64999999999986</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8182,34 +8195,34 @@
         <v>135.18</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G14" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H14" s="204" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8218,7 +8231,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8227,7 +8240,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8239,7 +8252,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8248,9 +8261,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8259,7 +8272,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8268,9 +8281,9 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8279,7 +8292,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8288,7 +8301,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8300,7 +8313,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G19" s="19">
         <v>3.9</v>
@@ -8309,7 +8322,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8320,7 +8333,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8329,7 +8342,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8340,7 +8353,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8349,7 +8362,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8361,7 +8374,7 @@
       </c>
       <c r="H22" s="295"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8373,9 +8386,9 @@
       </c>
       <c r="H23" s="295"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -8386,7 +8399,7 @@
         <v>40.835000000000001</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -8397,24 +8410,24 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C26" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F26" s="205" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G26" s="206" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H26" s="207" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8433,7 +8446,7 @@
         <v>-86.245000000000118</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8441,14 +8454,14 @@
         <v>19.5</v>
       </c>
       <c r="F28" s="210" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G28" s="181">
         <v>0</v>
       </c>
       <c r="H28" s="209"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8456,7 +8469,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="211" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -8467,7 +8480,7 @@
         <v>-86.245000000000118</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8483,16 +8496,16 @@
       </c>
       <c r="H30" s="209"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>19.5</v>
       </c>
       <c r="F31" s="211" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G31" s="212">
         <f>C31+C40</f>
@@ -8500,7 +8513,7 @@
       </c>
       <c r="H31" s="209"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -8509,7 +8522,7 @@
         <v>650.29999999999995</v>
       </c>
       <c r="F32" s="213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" s="214">
         <f>G35+G40</f>
@@ -8520,7 +8533,7 @@
         <v>723.05499999999984</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -8531,25 +8544,25 @@
       <c r="G33" s="2"/>
       <c r="H33" s="216"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="217" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G34" s="218" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" s="219" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F35" s="220" t="s">
         <v>31</v>
@@ -8563,7 +8576,7 @@
         <v>587.4849999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -8571,7 +8584,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="211" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G36" s="212">
         <f>C4+C15</f>
@@ -8579,7 +8592,7 @@
       </c>
       <c r="H36" s="216"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -8587,7 +8600,7 @@
         <v>135.80000000000001</v>
       </c>
       <c r="F37" s="211" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G37" s="212">
         <f>C6</f>
@@ -8595,7 +8608,7 @@
       </c>
       <c r="H37" s="216"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -8603,7 +8616,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="211" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G38" s="212">
         <f>C7+C17</f>
@@ -8611,7 +8624,7 @@
       </c>
       <c r="H38" s="216"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -8619,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="212">
         <f>C7+C17+C19+C20</f>
@@ -8630,16 +8643,16 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>135.80000000000001</v>
       </c>
       <c r="F40" s="220" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G40" s="214">
         <f>G12+G24</f>
@@ -8650,7 +8663,7 @@
         <v>135.57</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -8659,7 +8672,7 @@
         <v>3.6999999999999886</v>
       </c>
       <c r="F41" s="211" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G41" s="212">
         <f>C70</f>
@@ -8670,7 +8683,7 @@
         <v>135.18</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -8678,7 +8691,7 @@
         <v>139.5</v>
       </c>
       <c r="F42" s="222" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G42" s="223">
         <f>C82</f>
@@ -8689,9 +8702,9 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -8700,23 +8713,23 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C45" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46" s="188">
         <f>G29</f>
@@ -8728,7 +8741,7 @@
       </c>
       <c r="F46" s="283"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -8743,25 +8756,25 @@
       </c>
       <c r="F47" s="283"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="283"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C49" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="283"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -8773,9 +8786,9 @@
       </c>
       <c r="F50" s="283"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="202"/>
       <c r="D51" s="92">
@@ -8784,24 +8797,24 @@
       </c>
       <c r="F51" s="283"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="283"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C53" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="283"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -8813,9 +8826,9 @@
       </c>
       <c r="F54" s="283"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -8827,24 +8840,24 @@
       </c>
       <c r="F55" s="283"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="283"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C57" s="262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="283"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -8853,9 +8866,9 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -8864,24 +8877,24 @@
       </c>
       <c r="F59" s="283"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="283"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="262" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F61" s="283"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -8892,12 +8905,12 @@
         <v>0</v>
       </c>
       <c r="F62" s="283" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -8906,23 +8919,23 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C65" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F65" s="287" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -8933,12 +8946,12 @@
         <v>-22.489472833069584</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -8946,9 +8959,9 @@
       </c>
       <c r="F67" s="283"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -8956,9 +8969,9 @@
       </c>
       <c r="F68" s="283"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -8966,9 +8979,9 @@
       </c>
       <c r="F69" s="283"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -8976,24 +8989,24 @@
       </c>
       <c r="F70" s="283"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="283"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="285" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C72" s="261" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F72" s="283"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9004,12 +9017,12 @@
         <v>-172.68947283306957</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9020,12 +9033,12 @@
         <v>0.86976928897797345</v>
       </c>
       <c r="F74" s="283" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C75" s="293"/>
       <c r="D75" s="292">
@@ -9033,12 +9046,12 @@
         <v>172.68947283306957</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9046,27 +9059,27 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="283"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C78" s="261" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
       <c r="F78" s="283"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9078,9 +9091,9 @@
       </c>
       <c r="F79" s="283"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9092,9 +9105,9 @@
       </c>
       <c r="F80" s="283"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9106,9 +9119,9 @@
       </c>
       <c r="F81" s="283"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9120,9 +9133,9 @@
       </c>
       <c r="F82" s="283"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9131,24 +9144,24 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D85" s="270" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="267" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
         <v>-1204.8018700000002</v>
       </c>
       <c r="D86" s="248">
-        <f>C86*$H$1/Common_Shares</f>
+        <f>C86*scaling_factor/Common_Shares</f>
         <v>-4.7600094699071969</v>
       </c>
       <c r="E86" s="269" t="str">
@@ -9156,16 +9169,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="267" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
         <v>-174.47108129167054</v>
       </c>
       <c r="D87" s="248">
-        <f>C87*$H$1/Common_Shares</f>
+        <f>C87*scaling_factor/Common_Shares</f>
         <v>-0.6893116784200376</v>
       </c>
       <c r="E87" s="269" t="str">
@@ -9173,16 +9186,16 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
         <v>3.0255810000000003</v>
       </c>
       <c r="D88" s="248">
-        <f>C88*$H$1/Common_Shares</f>
+        <f>C88*scaling_factor/Common_Shares</f>
         <v>1.195366190124795E-2</v>
       </c>
       <c r="E88" s="269" t="str">
@@ -9190,9 +9203,9 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
@@ -9221,7 +9234,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
@@ -9233,14 +9246,14 @@
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C16</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -9290,15 +9303,15 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -9313,13 +9326,13 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" s="107">
-        <f>Data!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
@@ -9327,7 +9340,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9384,10 +9397,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="191">
         <f>C25</f>
@@ -9439,10 +9452,10 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="184">
         <f>C4+C5</f>
@@ -9494,10 +9507,10 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="191">
         <f>C35</f>
@@ -9549,10 +9562,10 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="192">
         <f>C6+C7</f>
@@ -9606,10 +9619,10 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="191">
         <f>BS!$G$39*BS!D58</f>
@@ -9661,10 +9674,10 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="191">
         <f>-C4*C78</f>
@@ -9716,10 +9729,10 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C11" s="193">
         <f>C63</f>
@@ -9773,10 +9786,10 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="191">
         <f>C50</f>
@@ -9828,10 +9841,10 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="184">
         <f>SUM(C8:C12)</f>
@@ -9883,10 +9896,10 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C14" s="191">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -9938,10 +9951,10 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C15" s="191">
         <f>-C4*C83</f>
@@ -9995,10 +10008,10 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C16" s="194">
         <f>SUM(C13:C15)</f>
@@ -10052,10 +10065,10 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C17" s="191">
         <f>-C4*C85</f>
@@ -10063,7 +10076,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10078,17 +10091,17 @@
       <c r="P17" s="195"/>
       <c r="Q17" s="195"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C18" s="191">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10103,10 +10116,10 @@
       <c r="P18" s="196"/>
       <c r="Q18" s="196"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="184">
         <f>C16+C17</f>
@@ -10160,7 +10173,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10179,15 +10192,15 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10202,10 +10215,10 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10223,10 +10236,10 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="197">
         <f>-C4*C28</f>
@@ -10280,10 +10293,10 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="191">
         <f>-C4*C29</f>
@@ -10337,10 +10350,10 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="184">
         <f>C23+C24</f>
@@ -10394,21 +10407,21 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="302"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E27" s="302"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" s="63">
         <f>AVERAGE(G28:J28)</f>
@@ -10416,7 +10429,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10464,7 +10477,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -10476,7 +10489,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10524,10 +10537,10 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -10579,28 +10592,28 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="302"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" s="302"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C33" s="198">
         <f>AVERAGE(G33:J33)</f>
         <v>-78.45</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10647,10 +10660,10 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="198">
         <f>AVERAGE(G34:J34)</f>
@@ -10658,7 +10671,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -10706,10 +10719,10 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="184">
         <f>C33+C34</f>
@@ -10763,18 +10776,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="302"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E37" s="302"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -10832,7 +10845,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -10890,10 +10903,10 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -10945,28 +10958,28 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="302"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="302"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="296">
         <v>0.16500000000000001</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11014,18 +11027,18 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11040,14 +11053,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E46" s="302"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11102,10 +11115,10 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11157,10 +11170,10 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11214,10 +11227,10 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C50" s="184">
         <f>C47+C48</f>
@@ -11269,31 +11282,31 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="302"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E52" s="302"/>
       <c r="G52" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C53" s="87">
         <f>G53</f>
         <v>0</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11310,17 +11323,17 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>3.1551835157759174E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11337,10 +11350,10 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -11392,24 +11405,24 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="302"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57" s="302"/>
       <c r="G57" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="191">
         <f>BS!$C67*C66</f>
@@ -11461,10 +11474,10 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C59" s="191">
         <f>BS!$C68*C67</f>
@@ -11516,10 +11529,10 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C60" s="191">
         <f>BS!$C69*C68</f>
@@ -11571,10 +11584,10 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C61" s="184">
         <f>SUM(C58:C60)</f>
@@ -11626,16 +11639,16 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" s="297">
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11682,10 +11695,10 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C63" s="184">
         <f>C61+C62</f>
@@ -11737,24 +11750,24 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="302"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65" s="302"/>
       <c r="G65" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C66" s="177">
         <f>G66</f>
@@ -11776,10 +11789,10 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C67" s="177">
         <f>G67</f>
@@ -11801,10 +11814,10 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C68" s="177">
         <f>G68</f>
@@ -11826,10 +11839,10 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -11853,18 +11866,18 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>60</v>
+        <v>427</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -11879,10 +11892,10 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -11900,10 +11913,10 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -11957,10 +11970,10 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12014,10 +12027,10 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12071,10 +12084,10 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12128,10 +12141,10 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12185,10 +12198,10 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12196,7 +12209,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>365</v>
+        <v>428</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12244,10 +12257,10 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12301,10 +12314,10 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -12358,10 +12371,10 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -12415,10 +12428,10 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -12472,7 +12485,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -12530,10 +12543,10 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -12587,10 +12600,10 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C85" s="298">
         <v>0</v>
@@ -12613,10 +12626,10 @@
       <c r="P85" s="253"/>
       <c r="Q85" s="253"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -12637,10 +12650,10 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -12694,18 +12707,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="302"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E89" s="302"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -12761,19 +12774,19 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
         <v>Dividend (HKD)</v>
       </c>
       <c r="C91" s="74">
-        <f>C90*Common_Shares/$C$3</f>
+        <f>C90*Common_Shares/scaling_factor</f>
         <v>0</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
-        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/$C$3)</f>
+        <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>0</v>
       </c>
       <c r="H91" s="74">
@@ -12817,18 +12830,18 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C92" s="23">
-        <f>C90/(C19*$C$3/Common_Shares)</f>
+        <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
-        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*$C$3/Common_Shares))</f>
+        <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0</v>
       </c>
       <c r="H92" s="171">
@@ -12872,10 +12885,10 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
@@ -12927,14 +12940,14 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="302"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
@@ -12952,10 +12965,10 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C96" s="77">
         <f>C4/G4-1</f>
@@ -13009,10 +13022,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
@@ -13066,18 +13079,18 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C99" s="54"/>
       <c r="D99" s="56"/>
       <c r="E99" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F99" s="56"/>
       <c r="G99" s="37"/>
@@ -13092,17 +13105,17 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
       <c r="E100" s="302"/>
       <c r="G100" s="97" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13159,10 +13172,10 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C102" s="200">
         <f>BS!C4</f>
@@ -13216,10 +13229,10 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="200">
         <f>BS!C6+BS!C7</f>
@@ -13273,7 +13286,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13330,7 +13343,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13387,21 +13400,21 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="302"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
       <c r="E107" s="303"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="12"/>
@@ -13414,10 +13427,10 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
@@ -13471,10 +13484,10 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -13528,10 +13541,10 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="94">
         <f>BS!$G$38/C$4</f>
@@ -13555,21 +13568,21 @@
       <c r="P110" s="225"/>
       <c r="Q110" s="225"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="302"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E112" s="302"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13618,10 +13631,10 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -13670,11 +13683,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="302"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -13728,10 +13741,10 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C117" s="23">
         <f>C81</f>
@@ -13783,9 +13796,9 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C118" s="42">
         <f>C4/C101</f>
@@ -13837,9 +13850,9 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
@@ -13893,10 +13906,10 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
@@ -13950,7 +13963,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -13969,15 +13982,15 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C122" s="54"/>
       <c r="D122" s="56"/>
       <c r="E122" s="66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F122" s="56"/>
       <c r="G122" s="37"/>
@@ -13992,10 +14005,10 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
@@ -14013,7 +14026,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14071,10 +14084,10 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14128,9 +14141,9 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -14178,688 +14191,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -14881,7 +14894,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
@@ -14890,34 +14903,34 @@
     <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="131" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C3" s="107">
-        <f>Normalized_FCF!C3</f>
+        <f>scaling_factor</f>
         <v>1000000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" s="110">
         <f>Normalized_FCF!C19</f>
@@ -14928,7 +14941,7 @@
         <v>USD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F4" s="135">
         <f>Thesis!C76</f>
@@ -14936,9 +14949,9 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8">
       <c r="B5" s="227" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" s="228">
         <f>Thesis!C70</f>
@@ -14947,9 +14960,9 @@
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
       <c r="B6" s="150" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" s="232">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -14960,14 +14973,14 @@
         <v>USD</v>
       </c>
       <c r="E6" s="348" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="348"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="226">
         <f>BS!G31</f>
@@ -14981,9 +14994,9 @@
       <c r="F7" s="348"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
@@ -14997,9 +15010,9 @@
       <c r="F8" s="348"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8">
       <c r="B9" s="227" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C9" s="229">
         <f>BS!H42</f>
@@ -15013,9 +15026,9 @@
       <c r="F9" s="348"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
@@ -15027,9 +15040,9 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="230" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
@@ -15041,12 +15054,12 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="112">
-        <f>(C10*C3)/Common_Shares*C11</f>
+        <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
         <v>60.265334487116725</v>
       </c>
       <c r="D12" t="str">
@@ -15055,12 +15068,12 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15068,15 +15081,15 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="162">
         <f>Scenarios!C65</f>
@@ -15084,9 +15097,9 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="163">
         <f>Scenarios!C64</f>
@@ -15094,12 +15107,12 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="141">
-        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*C3</f>
+        <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
         <v>67.988678435556125</v>
       </c>
       <c r="D18" t="str">
@@ -15108,28 +15121,28 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="129" t="s">
+      <c r="D20" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="129" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="129" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="129" t="s">
+      <c r="F20" s="130" t="s">
         <v>111</v>
       </c>
-      <c r="F20" s="130" t="s">
-        <v>112</v>
-      </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15151,7 +15164,7 @@
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15173,7 +15186,7 @@
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15195,7 +15208,7 @@
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15217,7 +15230,7 @@
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15239,7 +15252,7 @@
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15261,7 +15274,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15283,7 +15296,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15305,7 +15318,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15327,7 +15340,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15349,7 +15362,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15371,7 +15384,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15393,7 +15406,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15415,7 +15428,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15437,7 +15450,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15459,7 +15472,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15481,7 +15494,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15503,7 +15516,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -15525,7 +15538,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -15547,7 +15560,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -15569,7 +15582,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -15591,7 +15604,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -15613,7 +15626,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -15635,7 +15648,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -15657,7 +15670,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -15679,7 +15692,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -15701,7 +15714,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -15723,7 +15736,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -15745,7 +15758,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -15767,7 +15780,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -15789,9 +15802,9 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -15811,10 +15824,10 @@
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
@@ -15822,13 +15835,13 @@
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C54" s="137"/>
       <c r="D54" s="137"/>
@@ -15836,7 +15849,7 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
         <v>2395.5971104204846</v>
@@ -15863,7 +15876,7 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
@@ -15885,7 +15898,7 @@
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
@@ -15906,7 +15919,7 @@
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
@@ -15927,7 +15940,7 @@
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
@@ -15948,7 +15961,7 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
@@ -15969,7 +15982,7 @@
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
@@ -15990,16 +16003,16 @@
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="115"/>
       <c r="D63" s="115"/>
@@ -16007,7 +16020,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16030,7 +16043,7 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
@@ -16056,7 +16069,7 @@
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16083,7 +16096,7 @@
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16110,7 +16123,7 @@
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16137,7 +16150,7 @@
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16164,7 +16177,7 @@
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16190,7 +16203,7 @@
         <v>136.32930902109723</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16216,24 +16229,24 @@
         <v>159.30082525459741</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C73" s="172" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D73" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E73" s="173" t="s">
         <v>114</v>
       </c>
-      <c r="E73" s="173" t="s">
-        <v>115</v>
-      </c>
       <c r="F73" s="173" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16255,7 +16268,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16278,7 +16291,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16301,7 +16314,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16324,7 +16337,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16346,38 +16359,38 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C80" s="156" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.35">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16408,7 +16421,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I98"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -16418,22 +16431,22 @@
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="277" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I2" s="278"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H3" s="276">
         <v>0</v>
@@ -16443,16 +16456,16 @@
         <v>-52.2</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="121">
         <v>3</v>
       </c>
       <c r="D4" s="121"/>
       <c r="E4" s="156" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="156"/>
       <c r="H4" s="276">
@@ -16463,7 +16476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:9">
       <c r="H5" s="276">
         <v>2</v>
       </c>
@@ -16472,16 +16485,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="107">
         <f>Valuation_Model!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="276">
@@ -16492,9 +16505,9 @@
         <v>67.988942786517455</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C7" s="115">
         <f>Normalized_FCF!G8</f>
@@ -16517,9 +16530,9 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
@@ -16539,9 +16552,9 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" s="201">
         <f>Normalized_FCF!C19</f>
@@ -16561,7 +16574,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:9">
       <c r="E10" s="350"/>
       <c r="F10" s="350"/>
       <c r="H10" s="276">
@@ -16572,9 +16585,9 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11" s="350"/>
       <c r="F11" s="350"/>
@@ -16586,9 +16599,9 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="159">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16605,9 +16618,9 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="159">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16623,9 +16636,9 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -16634,49 +16647,49 @@
       <c r="E14" s="350"/>
       <c r="F14" s="350"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.35">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="151">
         <v>10</v>
       </c>
       <c r="E18" s="350" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F18" s="351"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:6">
       <c r="E19" s="351"/>
       <c r="F19" s="351"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E20" s="351"/>
       <c r="F20" s="351"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16689,9 +16702,9 @@
       <c r="E21" s="351"/>
       <c r="F21" s="351"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16704,18 +16717,18 @@
       <c r="E22" s="351"/>
       <c r="F22" s="351"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="167">
         <f>C18</f>
@@ -16725,9 +16738,9 @@
       <c r="E25" s="349"/>
       <c r="F25" s="349"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26" s="165">
         <v>0.03</v>
@@ -16736,9 +16749,9 @@
       <c r="E26" s="349"/>
       <c r="F26" s="349"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
@@ -16751,9 +16764,9 @@
       <c r="E27" s="349"/>
       <c r="F27" s="349"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C28" s="166">
         <v>0.6</v>
@@ -16762,18 +16775,18 @@
       <c r="E28" s="349"/>
       <c r="F28" s="349"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="167">
         <f>C18</f>
@@ -16783,9 +16796,9 @@
       <c r="E31" s="349"/>
       <c r="F31" s="349"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C32" s="165">
         <v>0.01</v>
@@ -16794,9 +16807,9 @@
       <c r="E32" s="349"/>
       <c r="F32" s="349"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
@@ -16809,9 +16822,9 @@
       <c r="E33" s="349"/>
       <c r="F33" s="349"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C34" s="166">
         <v>0.2</v>
@@ -16820,18 +16833,18 @@
       <c r="E34" s="349"/>
       <c r="F34" s="349"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="167">
         <f>C18</f>
@@ -16841,9 +16854,9 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C38" s="165">
         <v>0.05</v>
@@ -16852,9 +16865,9 @@
       <c r="E38" s="349"/>
       <c r="F38" s="349"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
@@ -16867,9 +16880,9 @@
       <c r="E39" s="349"/>
       <c r="F39" s="349"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C40" s="168">
         <f>1-C28-C34</f>
@@ -16879,9 +16892,9 @@
       <c r="E40" s="349"/>
       <c r="F40" s="349"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -16892,23 +16905,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="151">
         <v>15</v>
@@ -16916,23 +16929,23 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E48" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="167">
         <f>C46</f>
@@ -16942,9 +16955,9 @@
       <c r="E49" s="349"/>
       <c r="F49" s="349"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50" s="165">
         <v>0</v>
@@ -16953,9 +16966,9 @@
       <c r="E50" s="349"/>
       <c r="F50" s="349"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
@@ -16968,9 +16981,9 @@
       <c r="E51" s="349"/>
       <c r="F51" s="349"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C52" s="166">
         <v>0.05</v>
@@ -16979,18 +16992,18 @@
       <c r="E52" s="349"/>
       <c r="F52" s="349"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E54" s="160" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55" s="167">
         <f>C46</f>
@@ -17000,9 +17013,9 @@
       <c r="E55" s="349"/>
       <c r="F55" s="349"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56" s="165">
         <v>0.08</v>
@@ -17011,9 +17024,9 @@
       <c r="E56" s="349"/>
       <c r="F56" s="349"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
@@ -17026,9 +17039,9 @@
       <c r="E57" s="349"/>
       <c r="F57" s="349"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C58" s="166">
         <v>0.05</v>
@@ -17037,9 +17050,9 @@
       <c r="E58" s="349"/>
       <c r="F58" s="349"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -17050,33 +17063,33 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F60" s="312">
         <f>Thesis!E20</f>
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E63" s="282" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C64" s="167">
         <f>C18</f>
@@ -17084,24 +17097,24 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.35">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C65" s="152">
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="D65" s="152"/>
       <c r="E65" s="281" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.35">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
@@ -17112,20 +17125,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="281" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C69" s="273" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -17133,21 +17146,21 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C70" s="273" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="281" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C71" s="273" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -17155,39 +17168,39 @@
       </c>
       <c r="E71" s="281"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C72" s="272" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
         <v>-7.9974290871077408E-2</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="275" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C76" s="274">
         <f>F60</f>
@@ -17195,9 +17208,9 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
@@ -17208,23 +17221,23 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.35">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -17234,9 +17247,9 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
@@ -17244,9 +17257,9 @@
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
@@ -17257,24 +17270,24 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
         <v>0.48799999999999999</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.35">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
@@ -17285,35 +17298,35 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>9.2083708290373378E-2</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.35">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>(Thesis!E19+Thesis!C67)/2</f>
-        <v>5.7250000000000002E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.35">
+        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -17321,72 +17334,72 @@
       </c>
       <c r="D91" s="117"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>57.531434982190753</v>
+        <v>57.084827396539964</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>57.531434982190753</v>
+        <v>57.084827396539964</v>
       </c>
       <c r="D93" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E93" s="147" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.15381189022401565</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.35">
+        <v>0.16038071696769829</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="100"/>
     </row>
-    <row r="95" spans="2:8" ht="14.65" x14ac:dyDescent="0.5">
+    <row r="95" spans="2:8" ht="14.65">
       <c r="E95" s="320" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F95" s="317"/>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="13.9">
       <c r="E96" s="313" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F96" s="318" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="97" spans="5:8" ht="13.9">
       <c r="E97" s="314" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F97" s="318" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9" x14ac:dyDescent="0.45">
+    <row r="98" spans="5:8" ht="13.9">
       <c r="E98" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F98" s="319" t="s">
         <v>336</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>339</v>
       </c>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6A106C-DF3B-43B8-8A6D-F8BEB8F6066A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716A438A-0661-4B2E-8593-69403D9D393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716A438A-0661-4B2E-8593-69403D9D393D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457EB9C1-F86B-4048-B365-0BE1EF6D3232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3747,29 +3747,29 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4180,13 +4180,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4293,22 +4293,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4320,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4346,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4381,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4403,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4473,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4495,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4517,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4593,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4666,22 +4666,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4718,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4874,13 +4874,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4919,13 +4919,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,13 +5068,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5087,22 +5087,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C136" s="92">
         <f>Scenarios!C90</f>
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>418</v>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>57.084827396539964</v>
+        <v>53.971814816813243</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>57.084827396539964</v>
+        <v>53.971814816813243</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.16038071696769829</v>
+        <v>0.20616775897983042</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="13.9">
@@ -5259,13 +5259,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5302,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5316,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,17 +5355,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5382,6 +5371,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -17320,8 +17320,8 @@
         <v>413</v>
       </c>
       <c r="C90" s="135">
-        <f>MAX(6%,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.06</v>
+        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>57.084827396539964</v>
+        <v>53.971814816813243</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>57.084827396539964</v>
+        <v>53.971814816813243</v>
       </c>
       <c r="D93" t="s">
         <v>405</v>
@@ -17360,7 +17360,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.16038071696769829</v>
+        <v>0.20616775897983042</v>
       </c>
     </row>
     <row r="94" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457EB9C1-F86B-4048-B365-0BE1EF6D3232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22246129-B90A-420E-BB24-1C6C899AAD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2287,10 +2287,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>in contrast to a cash yield of</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>HKD</t>
   </si>
   <si>
@@ -2346,6 +2342,15 @@
   </si>
   <si>
     <t>Target Return</t>
+  </si>
+  <si>
+    <t>in contrast to a position yield of</t>
+  </si>
+  <si>
+    <t>Position Price Output</t>
+  </si>
+  <si>
+    <t>@ Position Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3739,37 +3744,37 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4082,7 +4087,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4114,10 +4119,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4128,7 +4133,7 @@
         <v>52.2</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4180,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4210,7 +4215,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4233,7 +4238,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4245,10 +4250,10 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="E19" s="336">
-        <v>3.4500000000000003E-2</v>
+        <v>419</v>
+      </c>
+      <c r="E19" s="339">
+        <v>0.2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4269,7 +4274,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4293,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4320,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4346,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4381,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4403,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4473,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4495,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4517,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4593,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4632,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4644,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4666,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4718,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4737,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4772,28 +4777,28 @@
       </c>
     </row>
     <row r="88" spans="2:6">
-      <c r="B88" s="337" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="338">
+      <c r="B88" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
     <row r="89" spans="2:6">
-      <c r="B89" s="337" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="338">
+      <c r="B89" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
     <row r="90" spans="2:6">
-      <c r="B90" s="337" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="339">
+      <c r="B90" s="336" t="s">
+        <v>416</v>
+      </c>
+      <c r="C90" s="338">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
@@ -4874,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4896,8 +4901,8 @@
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="337" t="s">
-        <v>416</v>
+      <c r="B104" s="336" t="s">
+        <v>415</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4919,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5068,17 +5073,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5087,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5142,14 +5147,14 @@
     </row>
     <row r="130" spans="1:6">
       <c r="B130" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C130" s="338">
+        <v>408</v>
+      </c>
+      <c r="C130" s="337">
         <f>C19</f>
         <v>0.25</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -5196,14 +5201,14 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="234" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C136" s="92">
-        <f>Scenarios!C90</f>
+        <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -5212,7 +5217,7 @@
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C91</f>
+        <f>Scenarios!C97</f>
         <v>0</v>
       </c>
     </row>
@@ -5222,16 +5227,16 @@
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C92</f>
+        <f>Scenarios!C98</f>
         <v>53.971814816813243</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C93</f>
+        <f>Scenarios!C99</f>
         <v>53.971814816813243</v>
       </c>
       <c r="D139" s="101" t="str">
@@ -5244,7 +5249,7 @@
         <v>263</v>
       </c>
       <c r="C140" s="92">
-        <f>Scenarios!F93</f>
+        <f>Scenarios!F99</f>
         <v>0.20616775897983042</v>
       </c>
     </row>
@@ -5259,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B144" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5302,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+      <c r="B153" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
+      <c r="C153" s="341"/>
+      <c r="D153" s="341"/>
+      <c r="E153" s="341"/>
+      <c r="F153" s="341"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5316,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+      <c r="B156" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
+      <c r="C156" s="346"/>
+      <c r="D156" s="346"/>
+      <c r="E156" s="346"/>
+      <c r="F156" s="346"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="B157" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
+      <c r="C157" s="346"/>
+      <c r="D157" s="346"/>
+      <c r="E157" s="346"/>
+      <c r="F157" s="346"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5355,6 +5360,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5371,17 +5387,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -6066,7 +6071,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8721,7 +8726,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -11877,7 +11882,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12209,7 +12214,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -16420,7 +16425,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I98"/>
+  <dimension ref="B2:I104"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -17312,16 +17317,16 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>413</v>
-      </c>
-      <c r="C90" s="135">
-        <f>MAX(Thesis!C67,(Thesis!E19+Thesis!C67)/2)</f>
-        <v>0.08</v>
+        <v>421</v>
+      </c>
+      <c r="C90" s="168">
+        <f>Thesis!E19</f>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17333,6 +17338,8 @@
         <v>0</v>
       </c>
       <c r="D91" s="117"/>
+      <c r="E91" s="100"/>
+      <c r="F91" s="100"/>
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
@@ -17340,69 +17347,123 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>53.971814816813243</v>
+        <v>39.34545300145686</v>
       </c>
       <c r="D92" s="117"/>
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
-        <v>407</v>
+        <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>53.971814816813243</v>
-      </c>
-      <c r="D93" t="s">
-        <v>405</v>
+        <v>39.34545300145686</v>
+      </c>
+      <c r="D93" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
       </c>
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.20616775897983042</v>
-      </c>
-    </row>
-    <row r="94" spans="2:8">
-      <c r="B94" s="100"/>
-    </row>
-    <row r="95" spans="2:8" ht="14.65">
-      <c r="E95" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F95" s="317"/>
+        <v>0.42129629629629628</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
+      <c r="B95" s="109" t="s">
+        <v>405</v>
+      </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
-    <row r="96" spans="2:8" ht="13.9">
-      <c r="E96" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F96" s="318" t="s">
-        <v>334</v>
+    <row r="96" spans="2:8">
+      <c r="B96" s="149" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="135">
+        <f>Thesis!C67</f>
+        <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="316"/>
     </row>
-    <row r="97" spans="5:8" ht="13.9">
-      <c r="E97" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F97" s="318" t="s">
-        <v>335</v>
-      </c>
+    <row r="97" spans="2:8">
+      <c r="B97" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C97" s="117">
+        <f>PV(C96, C76, -C77, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="316"/>
     </row>
-    <row r="98" spans="5:8" ht="13.9">
-      <c r="E98" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F98" s="319" t="s">
-        <v>336</v>
-      </c>
+    <row r="98" spans="2:8">
+      <c r="B98" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" s="117">
+        <f>C60/(1+C96)^C76</f>
+        <v>53.971814816813243</v>
+      </c>
+      <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="316"/>
+    </row>
+    <row r="99" spans="2:8" ht="13.15">
+      <c r="B99" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="112">
+        <f>C97+C98</f>
+        <v>53.971814816813243</v>
+      </c>
+      <c r="D99" t="s">
+        <v>404</v>
+      </c>
+      <c r="E99" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F99" s="329">
+        <f>(1-C99/C60)</f>
+        <v>0.20616775897983042</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
+      <c r="B100" s="100"/>
+    </row>
+    <row r="101" spans="2:8" ht="14.65">
+      <c r="E101" s="320" t="s">
+        <v>332</v>
+      </c>
+      <c r="F101" s="317"/>
+    </row>
+    <row r="102" spans="2:8" ht="13.9">
+      <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" ht="13.9">
+      <c r="E103" s="314" t="s">
+        <v>333</v>
+      </c>
+      <c r="F103" s="318" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" ht="13.9">
+      <c r="E104" s="315" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="319" t="s">
+        <v>336</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22246129-B90A-420E-BB24-1C6C899AAD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C2E5A-1903-41D3-A023-8AFF41C3CFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3752,29 +3752,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4185,13 +4185,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4225,7 +4225,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7579000000000002</v>
+        <v>7.7550999999999997</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4247,7 +4247,7 @@
         <v>277</v>
       </c>
       <c r="C19" s="249">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>419</v>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.2083708290373378E-2</v>
+        <v>9.195230665086962E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4298,22 +4298,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4325,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4351,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4386,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4408,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4478,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4500,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4522,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10069379612803481</v>
+        <v>0.10065745348000395</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4598,22 +4598,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4671,22 +4671,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.702701973542702</v>
+        <v>65.678988395702575</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4723,13 +4723,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4742,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.760009469907196</v>
+        <v>4.7582914757959367</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.6893116784200376</v>
+        <v>-0.68906289038467028</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1953661901247949E-2</v>
+        <v>1.1949347556731585E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4879,13 +4879,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-2.643445053008028</v>
+        <v>-2.6424909744367104</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4924,13 +4924,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>95.78 HKD</v>
+        <v>95.74 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>71.68 HKD</v>
+        <v>71.66 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.78 HKD</v>
+        <v>66.76 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>62.34 HKD</v>
+        <v>62.31 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>60.27 HKD</v>
+        <v>60.24 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>67.988942786517455</v>
+        <v>67.964404053122792</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5073,13 +5073,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5092,22 +5092,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="C127" s="250">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C130" s="337">
         <f>C19</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>418</v>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.48799999999999999</v>
+        <v>0.54483386436049175</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C98</f>
-        <v>53.971814816813243</v>
+        <v>53.95233517909076</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C99</f>
-        <v>53.971814816813243</v>
+        <v>53.95233517909076</v>
       </c>
       <c r="D139" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5264,13 +5264,13 @@
       <c r="F142" s="36"/>
     </row>
     <row r="144" spans="1:6">
-      <c r="B144" s="347" t="s">
+      <c r="B144" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
+      <c r="C144" s="342"/>
+      <c r="D144" s="342"/>
+      <c r="E144" s="342"/>
+      <c r="F144" s="342"/>
     </row>
     <row r="146" spans="2:6">
       <c r="B146" s="234" t="s">
@@ -5307,13 +5307,13 @@
       </c>
     </row>
     <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="341" t="s">
+      <c r="B153" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="341"/>
-      <c r="D153" s="341"/>
-      <c r="E153" s="341"/>
-      <c r="F153" s="341"/>
+      <c r="C153" s="343"/>
+      <c r="D153" s="343"/>
+      <c r="E153" s="343"/>
+      <c r="F153" s="343"/>
     </row>
     <row r="155" spans="2:6">
       <c r="B155" s="1" t="s">
@@ -5321,22 +5321,22 @@
       </c>
     </row>
     <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="346" t="s">
+      <c r="B156" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="346"/>
-      <c r="D156" s="346"/>
-      <c r="E156" s="346"/>
-      <c r="F156" s="346"/>
+      <c r="C156" s="340"/>
+      <c r="D156" s="340"/>
+      <c r="E156" s="340"/>
+      <c r="F156" s="340"/>
     </row>
     <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="346" t="s">
+      <c r="B157" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="346"/>
-      <c r="D157" s="346"/>
-      <c r="E157" s="346"/>
-      <c r="F157" s="346"/>
+      <c r="C157" s="340"/>
+      <c r="D157" s="340"/>
+      <c r="E157" s="340"/>
+      <c r="F157" s="340"/>
     </row>
     <row r="159" spans="2:6">
       <c r="B159" s="1" t="s">
@@ -5360,17 +5360,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5387,6 +5376,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B156:F156"/>
+    <mergeCell ref="B157:F157"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations disablePrompts="1" count="3">
@@ -8753,11 +8753,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.217810287390929</v>
+        <v>19.210874148899233</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.643445053008028</v>
+        <v>-2.6424909744367104</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9163,11 +9163,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1204.8018700000002</v>
+        <v>-1204.3670300000001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7600094699071969</v>
+        <v>-4.7582914757959367</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9180,11 +9180,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-174.47108129167054</v>
+        <v>-174.40811076773792</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.6893116784200376</v>
+        <v>-0.68906289038467028</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9197,11 +9197,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0255810000000003</v>
+        <v>3.024489</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.195366190124795E-2</v>
+        <v>1.1949347556731585E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9214,11 +9214,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-1376.2473702916707</v>
+        <v>-1375.7506517677382</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-5.4373674864259867</v>
+        <v>-5.4354050186238752</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -14039,46 +14039,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2562161578834168</v>
+        <v>5.254319071656206</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1208879017415807</v>
+        <v>6.1186787361007653</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5140096821397533</v>
+        <v>5.5120195524513074</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1515383168729771</v>
+        <v>6.1493180888103245</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.26028687791365</v>
+        <v>8.2573055552286245</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3622297145634796</v>
+        <v>7.359572520838273</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0971640363526554</v>
+        <v>5.09532435560119</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2036440225963698</v>
+        <v>6.2014049884165958</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4833592670083586</v>
+        <v>5.4813801997417491</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5354649727317424</v>
+        <v>5.5334670993480106</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14096,46 +14096,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10069379612803481</v>
+        <v>0.10065745348000395</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.1172583889222525</v>
+        <v>0.11721606774139397</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10563236938965044</v>
+        <v>0.10559424429983347</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1178455616259191</v>
+        <v>0.11780302852127057</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15824304363819253</v>
+        <v>0.15818593017679355</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14103888342075629</v>
+        <v>0.1409879793264037</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.7646820619782665E-2</v>
+        <v>9.761157769350938E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11884375522215267</v>
+        <v>0.11880086184706122</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10504519668598387</v>
+        <v>0.10500728351995688</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10604339028221728</v>
+        <v>0.10600511684574733</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7579000000000002</v>
+        <v>7.7550999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15065,7 +15065,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15118,7 +15118,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.988678435556125</v>
+        <v>67.964139797571661</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16054,23 +16054,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16081,23 +16081,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>60.265334487116711</v>
+        <v>60.243583377078693</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>61.317525532115766</v>
+        <v>61.295394662745196</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>63.468840937115125</v>
+        <v>63.445933609794075</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>65.6850292003964</v>
+        <v>65.661322001056234</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>69.137160662933425</v>
+        <v>69.112207511970382</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16108,23 +16108,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>60.265334487116711</v>
+        <v>60.243583377078693</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>62.336053285176952</v>
+        <v>62.313554806310442</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>66.784376871045055</v>
+        <v>66.760272892489127</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>71.682603886999331</v>
+        <v>71.656732028521688</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>79.992502892418983</v>
+        <v>79.963631805127477</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16135,23 +16135,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>60.265334487116711</v>
+        <v>60.243583377078693</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.565424686987129</v>
+        <v>63.542482500425862</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>70.995001353695187</v>
+        <v>70.969377666384133</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>79.712162899350332</v>
+        <v>79.683392993046013</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>95.775085216111023</v>
+        <v>95.740517841099077</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16162,23 +16162,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>60.265334487116696</v>
+        <v>60.243583377078679</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>64.785642588643583</v>
+        <v>64.762259998090954</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>75.402453100554368</v>
+        <v>75.37523866511674</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.605989465337288</v>
+        <v>88.574009577673991</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>114.91106435567103</v>
+        <v>114.86959037686285</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16189,23 +16189,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>60.265334487116696</v>
+        <v>60.243583377078679</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>65.890440156983203</v>
+        <v>65.8666588202246</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>79.618521345676072</v>
+        <v>79.589785236707414</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>97.637499805361216</v>
+        <v>97.60226024317879</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>136.32930902109723</v>
+        <v>136.28010471770855</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16215,23 +16215,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>60.265334487116696</v>
+        <v>60.243583377078679</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>66.838580563041177</v>
+        <v>66.814457021157864</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>83.447648987948966</v>
+        <v>83.417530860985948</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>106.37138471296478</v>
+        <v>106.33299289595291</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>159.30082525459741</v>
+        <v>159.24333001610336</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>95.775085216111023</v>
+        <v>95.740517841099077</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>71.682603886999331</v>
+        <v>71.656732028521688</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.784376871045055</v>
+        <v>66.760272892489127</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16334,7 +16334,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>62.336053285176952</v>
+        <v>62.313554806310442</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>60.265334487116711</v>
+        <v>60.243583377078693</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>67.988942786517455</v>
+        <v>67.964404053122792</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>60.265334487116725</v>
+        <v>60.2435833770787</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.784376871045055</v>
+        <v>66.760272892489127</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16818,7 +16818,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>62.336053285176952</v>
+        <v>62.313554806310442</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>71.682603886999331</v>
+        <v>71.656732028521688</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.874357557062297</v>
+        <v>66.850221102459898</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16977,7 +16977,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>60.265334487116711</v>
+        <v>60.243583377078693</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>95.775085216111023</v>
+        <v>95.740517841099077</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.988942786517455</v>
+        <v>67.964404053122792</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17123,7 +17123,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.988678435556125</v>
+        <v>67.964139797571661</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-7.9974290871077408E-2</v>
+        <v>-7.9974290871077422E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17237,7 +17237,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C127</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.810338706696939</v>
+        <v>30.935095153902036</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.48799999999999999</v>
+        <v>0.54483386436049175</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.2083708290373378E-2</v>
+        <v>9.195230665086962E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.34545300145686</v>
+        <v>39.331252345557175</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>39.34545300145686</v>
+        <v>39.331252345557175</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.971814816813243</v>
+        <v>53.95233517909076</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>53.971814816813243</v>
+        <v>53.95233517909076</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631C2E5A-1903-41D3-A023-8AFF41C3CFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0FEABD-A966-4E2D-84F0-FF6E06B5D1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2302,10 +2302,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Result (Buy)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Result (Sell)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2338,9 +2334,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Implied Return</t>
-  </si>
-  <si>
     <t>Target Return</t>
   </si>
   <si>
@@ -2351,6 +2344,15 @@
   </si>
   <si>
     <t>@ Position Yield</t>
+  </si>
+  <si>
+    <t>Result (Target)</t>
+  </si>
+  <si>
+    <t>Base Equity Return</t>
+  </si>
+  <si>
+    <t>Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3752,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4064,7 +4066,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J162"/>
+  <dimension ref="A1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4087,7 +4089,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4119,10 +4121,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4185,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4215,7 +4217,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4225,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7550999999999997</v>
+        <v>7.7549000000000001</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4238,7 +4240,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4250,7 +4252,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4263,7 +4265,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>30.935095153902036</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4278,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.195230665086962E-2</v>
+        <v>9.1942919609277585E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4298,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4325,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4351,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4386,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4408,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4478,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4500,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4522,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4571,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10065745348000395</v>
+        <v>0.10065485757657319</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4598,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4637,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4649,7 +4651,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4671,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4702,7 +4704,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.678988395702575</v>
+        <v>65.677294568714004</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4723,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4742,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4769,7 +4771,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7582914757959367</v>
+        <v>4.7581687619308468</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4778,7 +4780,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4787,7 +4789,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4796,7 +4798,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4840,7 +4842,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.68906289038467028</v>
+        <v>-0.68904511981071548</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1949347556731585E-2</v>
+        <v>1.1949039389266131E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4879,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4893,7 +4895,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,11 +4904,11 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-2.6424909744367104</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4924,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4986,7 +4988,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>71.66 HKD</v>
+        <v>71.65 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5065,7 +5067,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>67.964404053122792</v>
+        <v>67.962651286451745</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5073,17 +5075,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5092,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5145,19 +5147,19 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4">
       <c r="B131" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5167,30 +5169,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="2:4">
       <c r="B132" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.935095153902036</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>30.934297353869699</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4">
       <c r="B133" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>30.935095153902036</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="2:4">
       <c r="B134" s="238" t="s">
         <v>263</v>
       </c>
@@ -5199,167 +5201,232 @@
         <v>0.54483386436049175</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>409</v>
-      </c>
-      <c r="C136" s="92">
-        <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>420</v>
+      </c>
+      <c r="C136" s="337">
+        <f>Scenarios!C90</f>
+        <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4">
       <c r="B137" s="236" t="str">
         <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C137" s="240">
-        <f>Scenarios!C97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
+        <f>Scenarios!C91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4">
       <c r="B138" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C138" s="240">
-        <f>Scenarios!C98</f>
-        <v>53.95233517909076</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
+        <f>Scenarios!C92</f>
+        <v>39.330238012992908</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4">
       <c r="B139" s="80" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
       <c r="C139" s="239">
-        <f>Scenarios!C99</f>
-        <v>53.95233517909076</v>
-      </c>
-      <c r="D139" s="101" t="str">
+        <f>Scenarios!C93</f>
+        <v>39.330238012992908</v>
+      </c>
+      <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="2:4">
       <c r="B140" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C140" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.42129629629629628</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4">
+      <c r="B142" s="234" t="s">
+        <v>408</v>
+      </c>
+      <c r="C142" s="92">
+        <f>Scenarios!C96</f>
+        <v>0.08</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4">
+      <c r="B143" s="236" t="str">
+        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C143" s="240">
+        <f>Scenarios!C97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4">
+      <c r="B144" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C144" s="240">
+        <f>Scenarios!C98</f>
+        <v>53.950943776396301</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C145" s="239">
+        <f>Scenarios!C99</f>
+        <v>53.950943776396301</v>
+      </c>
+      <c r="D145" s="101" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="B146" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C146" s="92">
         <f>Scenarios!F99</f>
         <v>0.20616775897983042</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="13.9">
-      <c r="A142" s="247" t="s">
+    <row r="148" spans="1:6" ht="13.9">
+      <c r="A148" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B142" s="36"/>
-      <c r="C142" s="36"/>
-      <c r="D142" s="36"/>
-      <c r="E142" s="36"/>
-      <c r="F142" s="36"/>
-    </row>
-    <row r="144" spans="1:6">
-      <c r="B144" s="341" t="s">
+      <c r="B148" s="36"/>
+      <c r="C148" s="36"/>
+      <c r="D148" s="36"/>
+      <c r="E148" s="36"/>
+      <c r="F148" s="36"/>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C144" s="342"/>
-      <c r="D144" s="342"/>
-      <c r="E144" s="342"/>
-      <c r="F144" s="342"/>
-    </row>
-    <row r="146" spans="2:6">
-      <c r="B146" s="234" t="s">
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="2:6">
-      <c r="B147" s="344" t="s">
+    <row r="153" spans="1:6">
+      <c r="B153" s="344" t="s">
         <v>388</v>
       </c>
-      <c r="C147" s="344"/>
-      <c r="D147" s="344"/>
-      <c r="E147" s="344"/>
-      <c r="F147" s="344"/>
-    </row>
-    <row r="148" spans="2:6">
-      <c r="B148" s="238" t="s">
+      <c r="C153" s="344"/>
+      <c r="D153" s="344"/>
+      <c r="E153" s="344"/>
+      <c r="F153" s="344"/>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="B154" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="149" spans="2:6">
-      <c r="B149" s="238" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="150" spans="2:6">
-      <c r="B150" s="238" t="s">
+    <row r="156" spans="1:6">
+      <c r="B156" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="152" spans="2:6">
-      <c r="B152" s="1" t="s">
+    <row r="158" spans="1:6">
+      <c r="B158" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="153" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B153" s="343" t="s">
+    <row r="159" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C153" s="343"/>
-      <c r="D153" s="343"/>
-      <c r="E153" s="343"/>
-      <c r="F153" s="343"/>
-    </row>
-    <row r="155" spans="2:6">
-      <c r="B155" s="1" t="s">
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="156" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B156" s="340" t="s">
+    <row r="162" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="340"/>
-      <c r="D156" s="340"/>
-      <c r="E156" s="340"/>
-      <c r="F156" s="340"/>
-    </row>
-    <row r="157" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B157" s="340" t="s">
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C157" s="340"/>
-      <c r="D157" s="340"/>
-      <c r="E157" s="340"/>
-      <c r="F157" s="340"/>
-    </row>
-    <row r="159" spans="2:6">
-      <c r="B159" s="1" t="s">
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="160" spans="2:6">
-      <c r="B160" s="238" t="s">
+    <row r="166" spans="2:6">
+      <c r="B166" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="161" spans="2:2">
-      <c r="B161" s="238" t="s">
+    <row r="167" spans="2:6">
+      <c r="B167" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="162" spans="2:2">
-      <c r="B162" s="238" t="s">
+    <row r="168" spans="2:6">
+      <c r="B168" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5376,20 +5443,9 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B156:F156"/>
-    <mergeCell ref="B157:F157"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B147:F147"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
@@ -6071,7 +6127,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -8726,7 +8782,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -8753,11 +8809,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.210874148899233</v>
+        <v>19.210378710435542</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6424909744367104</v>
+        <v>-2.6424228259673308</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9163,11 +9219,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1204.3670300000001</v>
+        <v>-1204.3359700000001</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7582914757959367</v>
+        <v>-4.7581687619308468</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9180,11 +9236,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-174.40811076773792</v>
+        <v>-174.40361287317131</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.68906289038467028</v>
+        <v>-0.68904511981071537</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9197,11 +9253,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.024489</v>
+        <v>3.0244110000000002</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1949347556731585E-2</v>
+        <v>1.1949039389266131E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9214,11 +9270,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-1375.7506517677382</v>
+        <v>-1375.7151718731714</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-5.4354050186238752</v>
+        <v>-5.4352648423522956</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -11882,7 +11938,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12214,7 +12270,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -14039,46 +14095,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.254319071656206</v>
+        <v>5.2541835654971205</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1186787361007653</v>
+        <v>6.118520938554993</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5120195524513074</v>
+        <v>5.5118774003307038</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1493180888103245</v>
+        <v>6.1491595010915647</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2573055552286245</v>
+        <v>8.2570926036082657</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.359572520838273</v>
+        <v>7.3593827212864733</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.09532435560119</v>
+        <v>5.0951929498332289</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2014049884165958</v>
+        <v>6.2012450574037548</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4813801997417491</v>
+        <v>5.4812388377941348</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5334670993480106</v>
+        <v>5.5333243941063159</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14096,46 +14152,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10065745348000395</v>
+        <v>0.10065485757657319</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11721606774139397</v>
+        <v>0.11721304479990408</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10559424429983347</v>
+        <v>0.10559152107913225</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11780302852127057</v>
+        <v>0.11779999044236714</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15818593017679355</v>
+        <v>0.1581818506438365</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.1409879793264037</v>
+        <v>0.14098434331966422</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.761157769350938E-2</v>
+        <v>9.7609060341632733E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11880086184706122</v>
+        <v>0.11879779803455469</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10500728351995688</v>
+        <v>0.10500457543666925</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10600511684574733</v>
+        <v>0.10600238302885662</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -15051,7 +15107,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7550999999999997</v>
+        <v>7.7549000000000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15065,7 +15121,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15118,7 +15174,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.964139797571661</v>
+        <v>67.962387037715629</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16054,23 +16110,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16081,23 +16137,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>60.243583377078693</v>
+        <v>60.242029726361693</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>61.295394662745196</v>
+        <v>61.293813886361583</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>63.445933609794075</v>
+        <v>63.44429737212829</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>65.661322001056234</v>
+        <v>65.659628629674785</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>69.112207511970382</v>
+        <v>69.110425144044441</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16108,23 +16164,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>60.243583377078693</v>
+        <v>60.242029726361693</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>62.313554806310442</v>
+        <v>62.31194777210569</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>66.760272892489127</v>
+        <v>66.758551179735136</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>71.656732028521688</v>
+        <v>71.654884038630442</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>79.963631805127477</v>
+        <v>79.96156958460665</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16135,23 +16191,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>60.243583377078693</v>
+        <v>60.242029726361693</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.542482500425862</v>
+        <v>63.540843772814348</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>70.969377666384133</v>
+        <v>70.967547403004787</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>79.683392993046013</v>
+        <v>79.681337999738574</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>95.740517841099077</v>
+        <v>95.738048742883947</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16162,23 +16218,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>60.243583377078679</v>
+        <v>60.242029726361679</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>64.762259998090954</v>
+        <v>64.760589813051482</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>75.37523866511674</v>
+        <v>75.373294776871191</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.574009577673991</v>
+        <v>88.571725299983768</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>114.86959037686285</v>
+        <v>114.86662794980514</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16189,23 +16245,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>60.243583377078679</v>
+        <v>60.242029726361679</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>65.8666588202246</v>
+        <v>65.864960153313277</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>79.589785236707414</v>
+        <v>79.587732657495366</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>97.60226024317879</v>
+        <v>97.599743131594337</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>136.28010471770855</v>
+        <v>136.27659012460936</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16215,23 +16271,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>60.243583377078679</v>
+        <v>60.242029726361679</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>66.814457021157864</v>
+        <v>66.812733911023344</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>83.417530860985948</v>
+        <v>83.415379566202887</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>106.33299289595291</v>
+        <v>106.33025062330921</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>159.24333001610336</v>
+        <v>159.2392232133538</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16266,7 +16322,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>95.740517841099077</v>
+        <v>95.738048742883947</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16288,7 +16344,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>71.656732028521688</v>
+        <v>71.654884038630442</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16311,7 +16367,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.760272892489127</v>
+        <v>66.758551179735136</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16334,7 +16390,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>62.313554806310442</v>
+        <v>62.31194777210569</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16357,7 +16413,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>60.243583377078693</v>
+        <v>60.242029726361693</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16507,7 +16563,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>67.964404053122792</v>
+        <v>67.962651286451745</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16713,7 +16769,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>60.2435833770787</v>
+        <v>60.242029726361707</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16760,7 +16816,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.760272892489127</v>
+        <v>66.758551179735136</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16818,7 +16874,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>62.313554806310442</v>
+        <v>62.31194777210569</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16876,7 +16932,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>71.656732028521688</v>
+        <v>71.654884038630442</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16903,7 +16959,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.850221102459898</v>
+        <v>66.848497069988298</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -16977,7 +17033,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>60.243583377078693</v>
+        <v>60.242029726361693</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17035,7 +17091,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>95.740517841099077</v>
+        <v>95.738048742883947</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17061,7 +17117,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.964404053122792</v>
+        <v>67.962651286451745</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17123,7 +17179,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.964139797571661</v>
+        <v>67.962387037715629</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17258,7 +17314,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.935095153902036</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17268,7 +17324,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>30.935095153902036</v>
+        <v>30.934297353869699</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17309,7 +17365,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.195230665086962E-2</v>
+        <v>9.1942919609277585E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17317,12 +17373,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17347,7 +17403,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.331252345557175</v>
+        <v>39.330238012992908</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17357,7 +17413,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>39.331252345557175</v>
+        <v>39.330238012992908</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17380,7 +17436,7 @@
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17407,7 +17463,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.95233517909076</v>
+        <v>53.950943776396301</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17419,7 +17475,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>53.95233517909076</v>
+        <v>53.950943776396301</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F0FEABD-A966-4E2D-84F0-FF6E06B5D1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4B2D68-484F-447F-9923-BD616135A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3754,29 +3754,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4132,7 +4132,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>52.2</v>
+        <v>53.85</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>13212.2967426</v>
+        <v>13629.926812050002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4187,13 +4187,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.1942919609277585E-2</v>
+        <v>8.0674411817778235E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4300,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4327,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4353,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4388,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4410,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4502,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4524,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10065485757657319</v>
+        <v>9.7570725450271498E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4600,22 +4600,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4673,22 +4673,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4725,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4744,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4881,13 +4881,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4926,13 +4926,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,13 +5075,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5094,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5320,13 +5320,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5363,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5377,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,17 +5416,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5432,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -14152,46 +14152,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10065485757657319</v>
+        <v>9.7570725450271498E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11721304479990408</v>
+        <v>0.11362155874753933</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10559152107913225</v>
+        <v>0.10235612628283572</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11779999044236714</v>
+        <v>0.11419051998313026</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1581818506438365</v>
+        <v>0.15333505299179695</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14098434331966422</v>
+        <v>0.13666448878897813</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.7609060341632733E-2</v>
+        <v>9.4618253478797196E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11879779803455469</v>
+        <v>0.11515775408363518</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10500457543666925</v>
+        <v>0.10178716504724485</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10600238302885662</v>
+        <v>0.1027543991477496</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14209,39 +14209,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2609465503664988E-2</v>
+        <v>1.222310305090645E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1292510523090134E-2</v>
+        <v>1.0946500451351995E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3071156617544679E-2</v>
+        <v>1.2670647640405427E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.747614396636402E-2</v>
+        <v>1.6940663232018604E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4433523838829012E-2</v>
+        <v>1.3991271019254863E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2965194722555898E-2</v>
+        <v>1.2567932488717137E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5614242097275433E-2</v>
+        <v>1.5135811280924375E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3547985144994196E-2</v>
+        <v>1.3132865823002729E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3729634107832107E-2</v>
+        <v>1.3308948940182653E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-52.2</v>
+        <v>-53.85</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>52.2</v>
+        <v>53.85</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>52.2</v>
+        <v>53.85</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.1942919609277585E-2</v>
+        <v>8.0674411817778235E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E4B2D68-484F-447F-9923-BD616135A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DA482A-8AF4-4EAF-A449-2479871991C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2340,12 +2340,6 @@
     <t>in contrast to a position yield of</t>
   </si>
   <si>
-    <t>Position Price Output</t>
-  </si>
-  <si>
-    <t>@ Position Yield</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2353,6 +2347,15 @@
   </si>
   <si>
     <t>Entry Yield</t>
+  </si>
+  <si>
+    <t>Result (Entry)</t>
+  </si>
+  <si>
+    <t>Entry Price Output</t>
+  </si>
+  <si>
+    <t>@ Entry Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -3754,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4089,7 +4092,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4121,10 +4124,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4187,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4217,7 +4220,7 @@
         <v>355</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4240,7 +4243,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4265,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>30.934297353869699</v>
+        <v>38.606046318120192</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4280,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>8.0674411817778235E-2</v>
+        <v>0.15157025452393125</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4300,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4582,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>0</v>
+        <v>9.3606035283194056E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4600,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4639,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="286" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4673,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4725,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4829,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-22.489472833069584</v>
+        <v>-128.80975700607837</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4842,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.68904511981071548</v>
+        <v>-3.9465457953523835</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4881,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4895,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4926,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4966,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>95.74 HKD</v>
+        <v>92.48 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4988,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>71.65 HKD</v>
+        <v>68.4 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5010,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>66.76 HKD</v>
+        <v>63.5 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5032,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>62.31 HKD</v>
+        <v>59.05 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5054,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>60.24 HKD</v>
+        <v>56.98 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5067,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>67.962651286451745</v>
+        <v>64.705150610910081</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5094,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5140,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5149,7 +5152,7 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
@@ -5166,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>0</v>
+        <v>9.1544529585798831</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5176,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>30.934297353869699</v>
+        <v>29.451593359540311</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5185,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>30.934297353869699</v>
+        <v>38.606046318120192</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5198,19 +5201,19 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.54483386436049175</v>
+        <v>0.4033543550455666</v>
       </c>
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5220,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>0</v>
+        <v>10.618109606481479</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5230,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>39.330238012992908</v>
+        <v>37.445110307239631</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5239,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>39.330238012992908</v>
+        <v>48.063219913721113</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5252,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.42129629629629628</v>
+        <v>0.25719638297824987</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5264,7 +5267,7 @@
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5274,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>0</v>
+        <v>12.990334127165582</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5284,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>53.950943776396301</v>
+        <v>51.365034715006345</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5293,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>53.950943776396301</v>
+        <v>64.355368842171927</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5306,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>0.20616775897983042</v>
+        <v>5.4057793766911777E-3</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5320,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5363,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5377,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5416,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5432,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6110,8 +6113,14 @@
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
+      <c r="C25" s="39">
+        <f>(0.17+0.48)*Exchange_Rate</f>
+        <v>5.0406849999999999</v>
+      </c>
+      <c r="D25" s="39">
+        <f>(0.17+0.42)*Exchange_Rate</f>
+        <v>4.5753909999999998</v>
+      </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -6127,7 +6136,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7459,11 +7468,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>0</v>
+        <v>4.5753909999999998</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -9004,7 +9013,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-22.489472833069584</v>
+        <v>-128.80975700607837</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9071,11 +9080,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-162.39999999999998</v>
+        <v>-268.72028417300868</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-172.68947283306957</v>
+        <v>-279.00975700607836</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9087,11 +9096,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.92487684729064046</v>
+        <v>0.55894552382691576</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.86976928897797345</v>
+        <v>0.53833242826962435</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9104,7 +9113,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>172.68947283306957</v>
+        <v>279.00975700607836</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9236,11 +9245,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-174.40361287317131</v>
+        <v>-998.90678460643721</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.68904511981071537</v>
+        <v>-3.9465457953523835</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9270,11 +9279,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-1375.7151718731714</v>
+        <v>-2200.2183436064374</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-5.4352648423522956</v>
+        <v>-8.6927655178939638</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -11938,7 +11947,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12270,7 +12279,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12787,16 +12796,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>0</v>
+        <v>4.5753909999999998</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12843,16 +12852,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>0</v>
+        <v>1275.8434100761049</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>0</v>
+        <v>1275.8434100761049</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>0</v>
+        <v>1158.073249146003</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12898,16 +12907,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0</v>
+        <v>7.4397872893505443</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0</v>
+        <v>6.3888002507566579</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>0</v>
+        <v>6.4373165600111406</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12953,16 +12962,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>0</v>
+        <v>9.3606035283194056E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>0</v>
+        <v>9.3606035283194056E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>0</v>
+        <v>8.4965478180129977E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -15061,7 +15070,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-22.489472833069584</v>
+        <v>-128.80975700607837</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15093,7 +15102,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1966.2159298249671</v>
+        <v>1859.8956456519584</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15121,7 +15130,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15174,7 +15183,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>67.962387037715629</v>
+        <v>64.70488636217398</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16110,23 +16119,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16137,23 +16146,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>60.242029726361693</v>
+        <v>56.984529050820022</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>61.293813886361583</v>
+        <v>58.03631321081992</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>63.44429737212829</v>
+        <v>60.186796696586633</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>65.659628629674785</v>
+        <v>62.402127954133142</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>69.110425144044441</v>
+        <v>65.852924468502763</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16164,23 +16173,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>60.242029726361693</v>
+        <v>56.984529050820022</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>62.31194777210569</v>
+        <v>59.054447096564019</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>66.758551179735136</v>
+        <v>63.501050504193472</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>71.654884038630442</v>
+        <v>68.397383363088778</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>79.96156958460665</v>
+        <v>76.704068909064972</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16191,23 +16200,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>60.242029726361693</v>
+        <v>56.984529050820022</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.540843772814348</v>
+        <v>60.283343097272684</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>70.967547403004787</v>
+        <v>67.710046727463123</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>79.681337999738574</v>
+        <v>76.42383732419691</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>95.738048742883947</v>
+        <v>92.480548067342298</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16218,23 +16227,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>60.242029726361679</v>
+        <v>56.984529050820008</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>64.760589813051482</v>
+        <v>61.503089137509818</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>75.373294776871191</v>
+        <v>72.115794101329513</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.571725299983768</v>
+        <v>85.31422462444209</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>114.86662794980514</v>
+        <v>111.60912727426346</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16245,23 +16254,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>60.242029726361679</v>
+        <v>56.984529050820008</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>65.864960153313277</v>
+        <v>62.607459477771613</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>79.587732657495366</v>
+        <v>76.330231981953688</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>97.599743131594337</v>
+        <v>94.342242456052674</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>136.27659012460936</v>
+        <v>133.01908944906768</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16271,23 +16280,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>60.242029726361679</v>
+        <v>56.984529050820008</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>66.812733911023344</v>
+        <v>63.555233235481673</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>83.415379566202887</v>
+        <v>80.157878890661223</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>106.33025062330921</v>
+        <v>103.07274994776755</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>159.2392232133538</v>
+        <v>155.98172253781212</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16322,7 +16331,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>95.738048742883947</v>
+        <v>92.480548067342298</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16344,7 +16353,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>71.654884038630442</v>
+        <v>68.397383363088778</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16367,7 +16376,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>66.758551179735136</v>
+        <v>63.501050504193472</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16390,7 +16399,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>62.31194777210569</v>
+        <v>59.054447096564019</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16413,7 +16422,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>60.242029726361693</v>
+        <v>56.984529050820022</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16534,7 +16543,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16543,7 +16552,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16563,7 +16572,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>67.962651286451745</v>
+        <v>69.745835610910078</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16769,7 +16778,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>60.242029726361707</v>
+        <v>56.984529050820043</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16816,7 +16825,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>66.758551179735136</v>
+        <v>63.501050504193472</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16874,7 +16883,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>62.31194777210569</v>
+        <v>59.054447096564019</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16932,7 +16941,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>71.654884038630442</v>
+        <v>68.397383363088778</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16959,7 +16968,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>66.848497069988298</v>
+        <v>63.590996394446634</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17033,7 +17042,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>60.242029726361693</v>
+        <v>56.984529050820022</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17091,7 +17100,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>95.738048742883947</v>
+        <v>92.480548067342298</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17117,7 +17126,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>67.962651286451745</v>
+        <v>64.705150610910081</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17179,7 +17188,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>67.962387037715629</v>
+        <v>64.70488636217398</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17242,7 +17251,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-7.9974290871077422E-2</v>
+        <v>-0.13434425908635869</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17275,7 +17284,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>0</v>
+        <v>5.0406849999999999</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17302,7 +17311,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>9.1544529585798831</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17314,7 +17323,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.934297353869699</v>
+        <v>29.451593359540311</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17324,7 +17333,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>30.934297353869699</v>
+        <v>38.606046318120192</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17335,7 +17344,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.54483386436049175</v>
+        <v>0.4033543550455666</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17365,7 +17374,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.0674411817778235E-2</v>
+        <v>0.15157025452393125</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17373,12 +17382,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17391,7 +17400,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>10.618109606481479</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17403,7 +17412,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>39.330238012992908</v>
+        <v>37.445110307239631</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17413,7 +17422,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>39.330238012992908</v>
+        <v>48.063219913721113</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17424,7 +17433,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.42129629629629628</v>
+        <v>0.25719638297824987</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17451,7 +17460,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0</v>
+        <v>12.990334127165582</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17463,7 +17472,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>53.950943776396301</v>
+        <v>51.365034715006345</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17475,7 +17484,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>53.950943776396301</v>
+        <v>64.355368842171927</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17485,7 +17494,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>0.20616775897983042</v>
+        <v>5.4057793766911777E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DA482A-8AF4-4EAF-A449-2479871991C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98683CF8-1E06-49F2-B93A-543082734C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>53.85</v>
+        <v>54.35</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>13629.926812050002</v>
+        <v>13756.481378550001</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7549000000000001</v>
+        <v>7.7589302062988281</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>38.606046318120192</v>
+        <v>38.625338845755344</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15157025452393125</v>
+        <v>0.14793773051313952</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.7570725450271498E-2</v>
+        <v>9.67233515064677E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.3606035283194056E-2</v>
+        <v>9.2793093543592248E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.677294568714004</v>
+        <v>65.711426929706505</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7581687619308468</v>
+        <v>4.7606415728910418</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-128.80975700607837</v>
+        <v>-128.86501144894248</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.9465457953523835</v>
+        <v>-3.9502906039595347</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1949039389266131E-2</v>
+        <v>1.1955249281567975E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-2.6424228259673308</v>
+        <v>-2.6437960879200806</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>92.48 HKD</v>
+        <v>92.53 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.4 HKD</v>
+        <v>68.43 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.5 HKD</v>
+        <v>63.53 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>59.05 HKD</v>
+        <v>59.08 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>56.98 HKD</v>
+        <v>57.01 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>64.705150610910081</v>
+        <v>64.73708395408849</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>9.1544529585798831</v>
+        <v>9.1592105098024668</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>29.451593359540311</v>
+        <v>29.466128335952877</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>38.606046318120192</v>
+        <v>38.625338845755344</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4033543550455666</v>
+        <v>0.40335065334193276</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>10.618109606481479</v>
+        <v>10.623627817189252</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>37.445110307239631</v>
+        <v>37.463590251208615</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>48.063219913721113</v>
+        <v>48.087218068397867</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25719638297824987</v>
+        <v>0.25719208942896932</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>12.990334127165582</v>
+        <v>12.997085178297537</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>51.365034715006345</v>
+        <v>51.390384432384927</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>64.355368842171927</v>
+        <v>64.387469610682459</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>5.4057793766911777E-3</v>
+        <v>5.4005265923621204E-3</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6115,11 +6115,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.5753909999999998</v>
+        <v>4.5777688217163082</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.5753909999999998</v>
+        <v>4.5777688217163082</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8818,11 +8818,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.210378710435542</v>
+        <v>19.220362306520816</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6424228259673308</v>
+        <v>-2.6437960879200806</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-128.80975700607837</v>
+        <v>-128.86501144894248</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9080,11 +9080,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-268.72028417300868</v>
+        <v>-268.7755386158729</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.00975700607836</v>
+        <v>-279.06501144894247</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9096,11 +9096,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55894552382691576</v>
+        <v>0.55883061670527234</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53833242826962435</v>
+        <v>0.53822583927716949</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9113,7 +9113,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.00975700607836</v>
+        <v>279.06501144894247</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1204.3359700000001</v>
+        <v>-1204.9618610382081</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7581687619308468</v>
+        <v>-4.7606415728910418</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9245,11 +9245,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-998.90678460643721</v>
+        <v>-999.85462986624418</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.9465457953523835</v>
+        <v>-3.9502906039595347</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9262,11 +9262,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0244110000000002</v>
+        <v>3.0259827804565429</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1949039389266131E-2</v>
+        <v>1.1955249281567975E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9279,11 +9279,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2200.2183436064374</v>
+        <v>-2201.7905081239956</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.6927655178939638</v>
+        <v>-8.6989769275690083</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12796,16 +12796,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.5753909999999998</v>
+        <v>4.5777688217163082</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12852,16 +12852,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1275.8434100761049</v>
+        <v>1276.5064633904751</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1275.8434100761049</v>
+        <v>1276.5064633904751</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1158.073249146003</v>
+        <v>1158.6750975390462</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12907,16 +12907,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4397872893505443</v>
+        <v>7.4436537321925522</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.3888002507566579</v>
+        <v>6.3921204976989205</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4373165600111406</v>
+        <v>6.4406620207840337</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12962,16 +12962,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.3606035283194056E-2</v>
+        <v>9.2793093543592248E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.3606035283194056E-2</v>
+        <v>9.2793093543592248E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4965478180129977E-2</v>
+        <v>8.4227577216491406E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14104,46 +14104,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2541835654971205</v>
+        <v>5.2569141543765205</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.118520938554993</v>
+        <v>6.1217007218695523</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5118774003307038</v>
+        <v>5.5147419121899395</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1491595010915647</v>
+        <v>6.1523552072068979</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2570926036082657</v>
+        <v>8.2613837984168477</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3593827212864733</v>
+        <v>7.3632073780323779</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0951929498332289</v>
+        <v>5.0978409116019376</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2012450574037548</v>
+        <v>6.2044678322804039</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4812388377941348</v>
+        <v>5.4840874268525956</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5333243941063159</v>
+        <v>5.5362000519260919</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14161,46 +14161,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.7570725450271498E-2</v>
+        <v>9.67233515064677E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11362155874753933</v>
+        <v>0.11263478789088413</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10235612628283572</v>
+        <v>0.10146719249659503</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11419051998313026</v>
+        <v>0.1131988078602925</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15333505299179695</v>
+        <v>0.15200338175559977</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.13666448878897813</v>
+        <v>0.13547759665192968</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.4618253478797196E-2</v>
+        <v>9.3796520912639139E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11515775408363518</v>
+        <v>0.11415764180828709</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10178716504724485</v>
+        <v>0.10090317252718667</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.1027543991477496</v>
+        <v>0.10186200647518108</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14218,39 +14218,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.222310305090645E-2</v>
+        <v>1.2110655000760117E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0946500451351995E-2</v>
+        <v>1.0845796675350596E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2670647640405427E-2</v>
+        <v>1.2554082344725524E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6940663232018604E-2</v>
+        <v>1.6784815364198746E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3991271019254863E-2</v>
+        <v>1.386255647445951E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2567932488717137E-2</v>
+        <v>1.2452312134635102E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5135811280924375E-2</v>
+        <v>1.4996567386895631E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3132865823002729E-2</v>
+        <v>1.3012048290132418E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3308948940182653E-2</v>
+        <v>1.3186511507430283E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-128.80975700607837</v>
+        <v>-128.86501144894248</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.8956456519584</v>
+        <v>1859.8403912090942</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7549000000000001</v>
+        <v>7.7589302062988281</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>64.70488636217398</v>
+        <v>64.73681956802281</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16119,23 +16119,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16146,23 +16146,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>56.984529050820022</v>
+        <v>57.012450002137477</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.03631321081992</v>
+        <v>58.064780772299557</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.186796696586633</v>
+        <v>60.216381860110133</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.402127954133142</v>
+        <v>62.432864420960101</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>65.852924468502763</v>
+        <v>65.885454307500652</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16173,23 +16173,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>56.984529050820022</v>
+        <v>57.012450002137477</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.054447096564019</v>
+        <v>59.0834437802244</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.501050504193472</v>
+        <v>63.532358078911344</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.397383363088778</v>
+        <v>68.431235552376677</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>76.704068909064972</v>
+        <v>76.742238066516222</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16200,23 +16200,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>56.984529050820022</v>
+        <v>57.012450002137477</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.283343097272684</v>
+        <v>60.312978435770994</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>67.710046727463123</v>
+        <v>67.743541709251474</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.42383732419691</v>
+        <v>76.461860845843859</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>92.480548067342298</v>
+        <v>92.526916230025961</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16227,23 +16227,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>56.984529050820008</v>
+        <v>57.012450002137463</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.503089137509818</v>
+        <v>61.533358375629561</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.115794101329513</v>
+        <v>72.151578741374863</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.31422462444209</v>
+        <v>85.356868462907656</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>111.60912727426346</v>
+        <v>111.66543652199108</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16254,23 +16254,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>56.984529050820008</v>
+        <v>57.012450002137463</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>62.607459477771613</v>
+        <v>62.638302654988138</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.330231981953688</v>
+        <v>76.368206857088154</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.342242456052674</v>
+        <v>94.389578137653629</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.01908944906768</v>
+        <v>133.08652541208684</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16280,23 +16280,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>56.984529050820008</v>
+        <v>57.012450002137463</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.555233235481673</v>
+        <v>63.586568968858586</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.157878890661223</v>
+        <v>80.197842986376344</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.07274994776755</v>
+        <v>103.12462285696462</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>155.98172253781212</v>
+        <v>156.06109213614727</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>92.480548067342298</v>
+        <v>92.526916230025961</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.397383363088778</v>
+        <v>68.431235552376677</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.501050504193472</v>
+        <v>63.532358078911344</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.054447096564019</v>
+        <v>59.0834437802244</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>56.984529050820022</v>
+        <v>57.012450002137477</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-53.85</v>
+        <v>-54.35</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.745835610910078</v>
+        <v>69.780388588182731</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>53.85</v>
+        <v>54.35</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>56.984529050820043</v>
+        <v>57.012450002137491</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.501050504193472</v>
+        <v>63.532358078911344</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.054447096564019</v>
+        <v>59.0834437802244</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.397383363088778</v>
+        <v>68.431235552376677</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.590996394446634</v>
+        <v>63.622350713867021</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>56.984529050820022</v>
+        <v>57.012450002137477</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>92.480548067342298</v>
+        <v>92.526916230025961</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>64.705150610910081</v>
+        <v>64.73708395408849</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>64.70488636217398</v>
+        <v>64.73681956802281</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13434425908635869</v>
+        <v>-0.13437393834016864</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0406849999999999</v>
+        <v>5.0433046340942385</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>9.1544529585798831</v>
+        <v>9.1592105098024668</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>29.451593359540311</v>
+        <v>29.466128335952877</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.606046318120192</v>
+        <v>38.625338845755344</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.4033543550455666</v>
+        <v>0.40335065334193276</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>53.85</v>
+        <v>54.35</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15157025452393125</v>
+        <v>0.14793773051313952</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.618109606481479</v>
+        <v>10.623627817189252</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.445110307239631</v>
+        <v>37.463590251208615</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.063219913721113</v>
+        <v>48.087218068397867</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.25719638297824987</v>
+        <v>0.25719208942896932</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>12.990334127165582</v>
+        <v>12.997085178297537</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.365034715006345</v>
+        <v>51.390384432384927</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.355368842171927</v>
+        <v>64.387469610682459</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.4057793766911777E-3</v>
+        <v>5.4005265923621204E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98683CF8-1E06-49F2-B93A-543082734C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF4674-CAC7-43B6-BF36-946626046D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12689" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>54.35</v>
+        <v>55.75</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>13756.481378550001</v>
+        <v>14110.83416475</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7589302062988281</v>
+        <v>7.7691999999999997</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>38.625338845755344</v>
+        <v>38.67449654927848</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.14793773051313952</v>
+        <v>0.13796564912031539</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.67233515064677E-2</v>
+        <v>9.4419233289180268E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.2793093543592248E-2</v>
+        <v>9.0582600896860987E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.711426929706505</v>
+        <v>65.798403198397494</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7606415728910418</v>
+        <v>4.7669428032847794</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-128.86501144894248</v>
+        <v>-129.00581112201462</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.9502906039595347</v>
+        <v>-3.9598411005151521</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1955249281567975E-2</v>
+        <v>1.1971073363046128E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-2.6437960879200806</v>
+        <v>-2.6472954415279868</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>92.53 HKD</v>
+        <v>92.65 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.43 HKD</v>
+        <v>68.52 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.53 HKD</v>
+        <v>63.61 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>59.08 HKD</v>
+        <v>59.16 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>57.01 HKD</v>
+        <v>57.08 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>64.73708395408849</v>
+        <v>64.818448718764827</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>9.1592105098024668</v>
+        <v>9.1713337278106533</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>29.466128335952877</v>
+        <v>29.503162821467825</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>38.625338845755344</v>
+        <v>38.67449654927848</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40335065334193276</v>
+        <v>0.403341219764763</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>10.623627817189252</v>
+        <v>10.637689351851849</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>37.463590251208615</v>
+        <v>37.510676341877797</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>48.087218068397867</v>
+        <v>48.148365693729644</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25719208942896932</v>
+        <v>0.25718114756747057</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>12.997085178297537</v>
+        <v>13.014288243662049</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>51.390384432384927</v>
+        <v>51.454974405868022</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>64.387469610682459</v>
+        <v>64.469262649530066</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>5.4005265923621204E-3</v>
+        <v>5.3871401759368887E-3</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,6 +5419,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5435,17 +5446,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6115,11 +6115,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.5777688217163082</v>
+        <v>4.5838279999999996</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.5777688217163082</v>
+        <v>4.5838279999999996</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8818,11 +8818,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.220362306520816</v>
+        <v>19.245802560589539</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6437960879200806</v>
+        <v>-2.6472954415279868</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-128.86501144894248</v>
+        <v>-129.00581112201462</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9080,11 +9080,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-268.7755386158729</v>
+        <v>-268.91633828894498</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.06501144894247</v>
+        <v>-279.20581112201461</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9096,11 +9096,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55883061670527234</v>
+        <v>0.55853802322197776</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53822583927716949</v>
+        <v>0.53795441934538279</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9113,7 +9113,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.06501144894247</v>
+        <v>279.20581112201461</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1204.9618610382081</v>
+        <v>-1206.5567599999999</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7606415728910418</v>
+        <v>-4.7669428032847794</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9245,11 +9245,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-999.85462986624418</v>
+        <v>-1002.271947769156</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.9502906039595347</v>
+        <v>-3.9598411005151521</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9262,11 +9262,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0259827804565429</v>
+        <v>3.0299879999999999</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1955249281567975E-2</v>
+        <v>1.1971073363046128E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9279,11 +9279,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2201.7905081239956</v>
+        <v>-2205.7987197691559</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.6989769275690083</v>
+        <v>-8.7148128304368857</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12796,16 +12796,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.5777688217163082</v>
+        <v>4.5838279999999996</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12852,16 +12852,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1276.5064633904751</v>
+        <v>1278.1960594673401</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1276.5064633904751</v>
+        <v>1278.1960594673401</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1158.6750975390462</v>
+        <v>1160.208730901124</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12907,16 +12907,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4436537321925522</v>
+        <v>7.4535062229586773</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.3921204976989205</v>
+        <v>6.4005811690903327</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4406620207840337</v>
+        <v>6.4491869421963601</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12962,16 +12962,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.2793093543592248E-2</v>
+        <v>9.0582600896860987E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.2793093543592248E-2</v>
+        <v>9.0582600896860987E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.4227577216491406E-2</v>
+        <v>8.2221130044843035E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14104,46 +14104,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2569141543765205</v>
+        <v>5.2638722558718003</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1217007218695523</v>
+        <v>6.1298034630777245</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5147419121899395</v>
+        <v>5.5220412769538365</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1523552072068979</v>
+        <v>6.1604985229829632</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2613837984168477</v>
+        <v>8.2723186444639296</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3632073780323779</v>
+        <v>7.3729533892402044</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.0978409116019376</v>
+        <v>5.1045884622424946</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2044678322804039</v>
+        <v>6.2126801248218868</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4840874268525956</v>
+        <v>5.4913462170485996</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5362000519260919</v>
+        <v>5.5435278188875143</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14161,46 +14161,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.67233515064677E-2</v>
+        <v>9.4419233289180268E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11263478789088413</v>
+        <v>0.10995163162471255</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10146719249659503</v>
+        <v>9.9050067748050877E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.1131988078602925</v>
+        <v>0.11050221565888724</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15200338175559977</v>
+        <v>0.14838239721011534</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.13547759665192968</v>
+        <v>0.13225028500879291</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.3796520912639139E-2</v>
+        <v>9.1562124883273449E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11415764180828709</v>
+        <v>0.11143820851698452</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10090317252718667</v>
+        <v>9.8499483713876221E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10186200647518108</v>
+        <v>9.9435476571973352E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14218,39 +14218,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2110655000760117E-2</v>
+        <v>1.1806530928992151E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0845796675350596E-2</v>
+        <v>1.0573435861978566E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2554082344725524E-2</v>
+        <v>1.2238822877772776E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6784815364198746E-2</v>
+        <v>1.6363313274335461E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.386255647445951E-2</v>
+        <v>1.3514438464338554E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2452312134635102E-2</v>
+        <v>1.2139608332150994E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4996567386895631E-2</v>
+        <v>1.4619971972695562E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3012048290132418E-2</v>
+        <v>1.2685288333070798E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3186511507430283E-2</v>
+        <v>1.2855370411279569E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-128.86501144894248</v>
+        <v>-129.00581112201462</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.8403912090942</v>
+        <v>1859.6995915360221</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7589302062988281</v>
+        <v>7.7691999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>64.73681956802281</v>
+        <v>64.818183982755244</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16119,23 +16119,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16146,23 +16146,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.012450002137477</v>
+        <v>57.083590367960603</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.064780772299557</v>
+        <v>58.137314013123181</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.216381860110133</v>
+        <v>60.29176298056553</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.432864420960101</v>
+        <v>62.511179298781151</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>65.885454307500652</v>
+        <v>65.96833906608191</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16173,23 +16173,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.012450002137477</v>
+        <v>57.083590367960603</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.0834437802244</v>
+        <v>59.157325333078688</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.532358078911344</v>
+        <v>63.61212825697902</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.431235552376677</v>
+        <v>68.517489931188805</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>76.742238066516222</v>
+        <v>76.839492967178742</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16200,23 +16200,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.012450002137477</v>
+        <v>57.083590367960603</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.312978435770994</v>
+        <v>60.388487412371241</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>67.743541709251474</v>
+        <v>67.82888584996239</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.461860845843859</v>
+        <v>76.558744636554607</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>92.526916230025961</v>
+        <v>92.645063880599679</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16227,23 +16227,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.012450002137463</v>
+        <v>57.083590367960589</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.533358375629561</v>
+        <v>61.610482658707134</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.151578741374863</v>
+        <v>72.242757401760954</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.356868462907656</v>
+        <v>85.465525770168838</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>111.66543652199108</v>
+        <v>111.80891609976587</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16254,23 +16254,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.012450002137463</v>
+        <v>57.083590367960589</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>62.638302654988138</v>
+        <v>62.716889452806619</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.368206857088154</v>
+        <v>76.46496668649003</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.389578137653629</v>
+        <v>94.51019122521646</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.08652541208684</v>
+        <v>133.25835814653482</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16280,23 +16280,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.012450002137463</v>
+        <v>57.083590367960589</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.586568968858586</v>
+        <v>63.666410900975002</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.197842986376344</v>
+        <v>80.299671758525804</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.12462285696462</v>
+        <v>103.25679773266738</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>156.06109213614727</v>
+        <v>156.26333422528165</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>92.526916230025961</v>
+        <v>92.645063880599679</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.431235552376677</v>
+        <v>68.517489931188805</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.532358078911344</v>
+        <v>63.61212825697902</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.0834437802244</v>
+        <v>59.157325333078688</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.012450002137477</v>
+        <v>57.083590367960603</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-54.35</v>
+        <v>-55.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.780388588182731</v>
+        <v>69.868428718764832</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>54.35</v>
+        <v>55.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.012450002137491</v>
+        <v>57.083590367960618</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.532358078911344</v>
+        <v>63.61212825697902</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.0834437802244</v>
+        <v>59.157325333078688</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.431235552376677</v>
+        <v>68.517489931188805</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.622350713867021</v>
+        <v>63.702240007040913</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.012450002137477</v>
+        <v>57.083590367960603</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>92.526916230025961</v>
+        <v>92.645063880599679</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>64.73708395408849</v>
+        <v>64.818448718764827</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>64.73681956802281</v>
+        <v>64.818183982755244</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13437393834016864</v>
+        <v>-0.13444957419837114</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0433046340942385</v>
+        <v>5.0499799999999997</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>9.1592105098024668</v>
+        <v>9.1713337278106533</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>29.466128335952877</v>
+        <v>29.503162821467825</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.625338845755344</v>
+        <v>38.67449654927848</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40335065334193276</v>
+        <v>0.403341219764763</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>54.35</v>
+        <v>55.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.14793773051313952</v>
+        <v>0.13796564912031539</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.623627817189252</v>
+        <v>10.637689351851849</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.463590251208615</v>
+        <v>37.510676341877797</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.087218068397867</v>
+        <v>48.148365693729644</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.25719208942896932</v>
+        <v>0.25718114756747057</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>12.997085178297537</v>
+        <v>13.014288243662049</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.390384432384927</v>
+        <v>51.454974405868022</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.387469610682459</v>
+        <v>64.469262649530066</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.4005265923621204E-3</v>
+        <v>5.3871401759368887E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDF4674-CAC7-43B6-BF36-946626046D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BFC49F-7B84-4B94-B4A0-5E5F6A65B957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3757,29 +3757,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4135,7 +4135,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>55.75</v>
+        <v>55.65</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>404</v>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>14110.83416475</v>
+        <v>14085.523251449998</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4190,13 +4190,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4230,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="50">
-        <v>7.7691999999999997</v>
+        <v>7.7786</v>
       </c>
       <c r="D17" s="32" t="str">
         <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="C20" s="252">
         <f>C133</f>
-        <v>38.67449654927848</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>315</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13796564912031539</v>
+        <v>0.13918053194738822</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4303,22 +4303,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4330,13 +4330,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4356,13 +4356,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4391,13 +4391,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4413,13 +4413,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4505,7 +4505,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>346</v>
       </c>
       <c r="C50" s="344"/>
@@ -4527,22 +4527,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>351</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.4419233289180268E-2</v>
+        <v>9.4703343132953519E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.0582600896860987E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4603,22 +4603,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4676,22 +4676,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C77" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.798403198397494</v>
+        <v>65.878013066860788</v>
       </c>
       <c r="D77" s="1" t="str">
         <f>Market_currency</f>
@@ -4728,13 +4728,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4747,13 +4747,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="C87" s="248">
         <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7669428032847794</v>
+        <v>4.7727103549440075</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C94" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-129.00581112201462</v>
+        <v>-129.13468585556711</v>
       </c>
       <c r="D94" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C95" s="248">
         <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.9598411005151521</v>
+        <v>-3.968592738991028</v>
       </c>
       <c r="D95" s="1" t="str">
         <f>Market_currency</f>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="C99" s="248">
         <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1971073363046128E-2</v>
+        <v>1.1985557233922492E-2</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Market_currency</f>
@@ -4884,13 +4884,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="C103" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -4911,7 +4911,7 @@
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
-        <v>-2.6472954415279868</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4929,13 +4929,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E111" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>92.65 HKD</v>
+        <v>92.75 HKD</v>
       </c>
       <c r="F111" s="259">
         <f>Valuation_Model!F74</f>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="E112" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.52 HKD</v>
+        <v>68.6 HKD</v>
       </c>
       <c r="F112" s="246">
         <f>Valuation_Model!F75</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="E113" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.61 HKD</v>
+        <v>63.69 HKD</v>
       </c>
       <c r="F113" s="246">
         <f>Valuation_Model!F76</f>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E114" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>59.16 HKD</v>
+        <v>59.22 HKD</v>
       </c>
       <c r="F114" s="246">
         <f>Valuation_Model!F77</f>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E115" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>57.08 HKD</v>
+        <v>57.15 HKD</v>
       </c>
       <c r="F115" s="246">
         <f>Valuation_Model!F78</f>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="C117" s="241">
         <f>Scenarios!C60</f>
-        <v>64.818448718764827</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="D117" s="236" t="str">
         <f>Market_currency</f>
@@ -5078,13 +5078,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5097,22 +5097,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="C128" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="D128" s="236" t="str">
         <f>Market_currency</f>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C131" s="240">
         <f>Scenarios!C81</f>
-        <v>9.1713337278106533</v>
+        <v>9.1824301775147958</v>
       </c>
     </row>
     <row r="132" spans="2:4">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C132" s="240">
         <f>Scenarios!C82</f>
-        <v>29.503162821467825</v>
+        <v>29.537056136005432</v>
       </c>
     </row>
     <row r="133" spans="2:4">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="C133" s="239">
         <f>Scenarios!C83</f>
-        <v>38.67449654927848</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="D133" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="C134" s="92">
         <f>Scenarios!F83</f>
-        <v>0.403341219764763</v>
+        <v>0.40333258405570871</v>
       </c>
     </row>
     <row r="136" spans="2:4">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C91</f>
-        <v>10.637689351851849</v>
+        <v>10.650559953703702</v>
       </c>
     </row>
     <row r="138" spans="2:4">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C92</f>
-        <v>37.510676341877797</v>
+        <v>37.553768709955989</v>
       </c>
     </row>
     <row r="139" spans="2:4">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C93</f>
-        <v>48.148365693729644</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="D139" s="47" t="str">
         <f>Reporting_currency</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="C140" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25718114756747057</v>
+        <v>0.2571711311409639</v>
       </c>
     </row>
     <row r="142" spans="2:4">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C97</f>
-        <v>13.014288243662049</v>
+        <v>13.030034306254134</v>
       </c>
     </row>
     <row r="144" spans="2:4">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C144" s="240">
         <f>Scenarios!C98</f>
-        <v>51.454974405868022</v>
+        <v>51.514086021887501</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
-        <v>64.469262649530066</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="D145" s="101" t="str">
         <f>Reporting_currency</f>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3871401759368887E-3</v>
+        <v>5.3748859487811051E-3</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="13.9">
@@ -5323,13 +5323,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5366,13 +5366,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>389</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5380,22 +5380,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>390</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>391</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5419,17 +5419,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5446,6 +5435,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6115,11 +6115,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.5838279999999996</v>
+        <v>4.5893739999999994</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7468,11 +7468,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.5838279999999996</v>
+        <v>4.5893739999999994</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8818,11 +8818,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.245802560589539</v>
+        <v>19.269088168383075</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6472954415279868</v>
+        <v>-2.6504984195888377</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-129.00581112201462</v>
+        <v>-129.13468585556711</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9080,11 +9080,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-268.91633828894498</v>
+        <v>-269.04521302249748</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.20581112201461</v>
+        <v>-279.3346858555671</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9096,11 +9096,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55853802322197776</v>
+        <v>0.55827047919800865</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53795441934538279</v>
+        <v>0.53770622699417447</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9113,7 +9113,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.20581112201461</v>
+        <v>279.3346858555671</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9228,11 +9228,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1206.5567599999999</v>
+        <v>-1208.01658</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7669428032847794</v>
+        <v>-4.7727103549440075</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9245,11 +9245,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-1002.271947769156</v>
+        <v>-1004.4870673961143</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.9598411005151521</v>
+        <v>-3.968592738991028</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9262,11 +9262,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0299879999999999</v>
+        <v>3.0336540000000003</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1971073363046128E-2</v>
+        <v>1.1985557233922493E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9279,11 +9279,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2205.7987197691559</v>
+        <v>-2209.4699933961147</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.7148128304368857</v>
+        <v>-8.7293175367011138</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12796,16 +12796,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.5838279999999996</v>
+        <v>4.5893739999999994</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12852,16 +12852,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1278.1960594673401</v>
+        <v>1279.74255626997</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1278.1960594673401</v>
+        <v>1279.74255626997</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1160.208730901124</v>
+        <v>1161.6124741527419</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -12907,16 +12907,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4535062229586773</v>
+        <v>7.4625242632325559</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4005811690903327</v>
+        <v>6.4083252692537283</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4491869421963601</v>
+        <v>6.4569898507656651</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -12962,16 +12962,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.0582600896860987E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.0582600896860987E-2</v>
+        <v>9.085516621743038E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2221130044843035E-2</v>
+        <v>8.2468535489667552E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14104,46 +14104,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2638722558718003</v>
+        <v>5.2702410453488628</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1298034630777245</v>
+        <v>6.1372199477290312</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5220412769538365</v>
+        <v>5.5287224266221893</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1604985229829632</v>
+        <v>6.1679521457647217</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.2723186444639296</v>
+        <v>8.282327370620802</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3729533892402044</v>
+        <v>7.3818739681748262</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1045884622424946</v>
+        <v>5.1107645333366971</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2126801248218868</v>
+        <v>6.2201968824254141</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4913462170485996</v>
+        <v>5.4979902285865005</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5435278188875143</v>
+        <v>5.5502349652471841</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14161,46 +14161,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4419233289180268E-2</v>
+        <v>9.4703343132953519E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10995163162471255</v>
+        <v>0.11028247884508592</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.9050067748050877E-2</v>
+        <v>9.9348111888988136E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11050221565888724</v>
+        <v>0.11083471960044423</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.14838239721011534</v>
+        <v>0.14882888356910695</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.13225028500879291</v>
+        <v>0.1326482294371038</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.1562124883273449E-2</v>
+        <v>9.183763761611316E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11143820851698452</v>
+        <v>0.11177352888455372</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>9.8499483713876221E-2</v>
+        <v>9.8795871133629837E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.9435476571973352E-2</v>
+        <v>9.9734680417739155E-2</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14218,39 +14218,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1806530928992151E-2</v>
+        <v>1.1827746617993037E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0573435861978566E-2</v>
+        <v>1.0592435746726057E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2238822877772776E-2</v>
+        <v>1.226081537171307E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6363313274335461E-2</v>
+        <v>1.6392717251468139E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3514438464338554E-2</v>
+        <v>1.3538723169575462E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2139608332150994E-2</v>
+        <v>1.2161422542990439E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4619971972695562E-2</v>
+        <v>1.4646243261056202E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2685288333070798E-2</v>
+        <v>1.2708083100964907E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2855370411279569E-2</v>
+        <v>1.2878470807346559E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-129.00581112201462</v>
+        <v>-129.13468585556711</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.6995915360221</v>
+        <v>1859.5707168024696</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7691999999999997</v>
+        <v>7.7786</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!D17</f>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>64.818183982755244</v>
+        <v>64.892647274488766</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16119,23 +16119,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16146,23 +16146,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.083590367960603</v>
+        <v>57.148695530159657</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.137314013123181</v>
+        <v>58.203694081652934</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.29176298056553</v>
+        <v>60.3607497293576</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.511179298781151</v>
+        <v>62.582851332208861</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>65.96833906608191</v>
+        <v>66.044193937100715</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16173,23 +16173,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.083590367960603</v>
+        <v>57.148695530159657</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.157325333078688</v>
+        <v>59.224939519201975</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.61212825697902</v>
+        <v>63.68513233491673</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.517489931188805</v>
+        <v>68.59642903457798</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>76.839492967178742</v>
+        <v>76.928500910157368</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16200,23 +16200,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.083590367960603</v>
+        <v>57.148695530159657</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.388487412371241</v>
+        <v>60.457591188612597</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>67.82888584996239</v>
+        <v>67.906991807292314</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.558744636554607</v>
+        <v>76.647412900504776</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>92.645063880599679</v>
+        <v>92.753195075211181</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16227,23 +16227,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.083590367960589</v>
+        <v>57.148695530159642</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.610482658707134</v>
+        <v>61.681064934062384</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.242757401760954</v>
+        <v>72.326203727801555</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.465525770168838</v>
+        <v>85.564970400109843</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>111.80891609976587</v>
+        <v>111.940233749979</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16254,23 +16254,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.083590367960589</v>
+        <v>57.148695530159642</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>62.716889452806619</v>
+        <v>62.788810376139061</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.46496668649003</v>
+        <v>76.553521487956203</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.51019122521646</v>
+        <v>94.62057904818603</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.25835814653482</v>
+        <v>133.41562760069687</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16280,23 +16280,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.083590367960589</v>
+        <v>57.148695530159642</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.666410900975002</v>
+        <v>63.73948065579755</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.299671758525804</v>
+        <v>80.39286619183018</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.25679773266738</v>
+        <v>103.37776812542148</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>156.26333422528165</v>
+        <v>156.44843753301163</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>92.645063880599679</v>
+        <v>92.753195075211181</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.517489931188805</v>
+        <v>68.59642903457798</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.61212825697902</v>
+        <v>63.68513233491673</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.157325333078688</v>
+        <v>59.224939519201975</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.083590367960603</v>
+        <v>57.148695530159657</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-55.75</v>
+        <v>-55.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.868428718764832</v>
+        <v>69.94900233080395</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>55.75</v>
+        <v>55.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.083590367960618</v>
+        <v>57.148695530159671</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.61212825697902</v>
+        <v>63.68513233491673</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -16883,7 +16883,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.157325333078688</v>
+        <v>59.224939519201975</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.517489931188805</v>
+        <v>68.59642903457798</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.702240007040913</v>
+        <v>63.775353111706025</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.083590367960603</v>
+        <v>57.148695530159657</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>92.645063880599679</v>
+        <v>92.753195075211181</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>64.818448718764827</v>
+        <v>64.892912330803952</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>64.818183982755244</v>
+        <v>64.892647274488766</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17251,7 +17251,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13444957419837114</v>
+        <v>-0.13451881296684234</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0499799999999997</v>
+        <v>5.0560900000000002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>9.1713337278106533</v>
+        <v>9.1824301775147958</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17323,7 +17323,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>29.503162821467825</v>
+        <v>29.537056136005432</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17333,7 +17333,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.67449654927848</v>
+        <v>38.719486313520228</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.403341219764763</v>
+        <v>0.40333258405570871</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>55.75</v>
+        <v>55.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13796564912031539</v>
+        <v>0.13918053194738822</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.637689351851849</v>
+        <v>10.650559953703702</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.510676341877797</v>
+        <v>37.553768709955989</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.148365693729644</v>
+        <v>48.204328663659695</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.25718114756747057</v>
+        <v>0.2571711311409639</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17460,7 +17460,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.014288243662049</v>
+        <v>13.030034306254134</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17472,7 +17472,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.454974405868022</v>
+        <v>51.514086021887501</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.469262649530066</v>
+        <v>64.544120328141631</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.3871401759368887E-3</v>
+        <v>5.3748859487811051E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7BFC49F-7B84-4B94-B4A0-5E5F6A65B957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB4DEC-7A58-4982-BB58-2D3451AD7777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2358,6 +2358,24 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2365,6 +2383,9 @@
   </si>
   <si>
     <t>0303.HK</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>USD</t>
@@ -3056,7 +3077,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3757,29 +3778,36 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4069,13 +4097,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4092,7 +4119,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4110,9 +4137,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>0303.HK Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>424</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4124,340 +4150,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>425</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>253109133</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45808</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>432</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>55.65</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="48" t="s">
         <v>404</v>
       </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>253109133</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45808</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (HKD):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>14085.523251449998</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>USD/HKD</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>7.7786</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C15" s="32" t="str">
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>7.7786</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>USD/HKD</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="C22" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>428</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="E19" s="339">
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (HKD):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>38.719486313520228</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="280">
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>0.13918053194738822</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
         <v>362</v>
       </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>210.2763260031652</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>0</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-4.9000000000000004</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>-4.9000000000000004</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4465,405 +4483,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-33.887093790522258</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
-        <v>351</v>
-      </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
-        <v>369</v>
-      </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>199.70000000000005</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>199.70000000000005</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>171.48923221264295</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
         <v>398</v>
       </c>
-      <c r="C58" s="92">
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>9.4703343132953519E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>9.085516621743038E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
         <v>363</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="C67" s="311">
+      <c r="C72" s="311">
         <v>0.08</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
         <v>364</v>
       </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>65.878013066860788</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
         <v>365</v>
       </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>155.30000000000001</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>4.7727103549440075</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
         <v>412</v>
       </c>
-      <c r="C88" s="337">
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
         <v>413</v>
       </c>
-      <c r="C89" s="337">
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
         <v>415</v>
       </c>
-      <c r="C90" s="338">
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>150.19999999999999</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-129.13468585556711</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.968592738991028</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0.39</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4872,591 +4898,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1985557233922492E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-129.13468585556711</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-3.968592738991028</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
-        <v>374</v>
-      </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>57.148695530159671</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0.39</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
+        <f>Reporting_currency</f>
+        <v>USD</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>414</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-2.6504984195888377</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.1985557233922492E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>57.148695530159671</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-2.6504984195888377</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
         <v>366</v>
       </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>92.75 HKD</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>68.6 HKD</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.03</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>63.69 HKD</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.01</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>59.22 HKD</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.15 HKD</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>64.892912330803952</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
         <v>410</v>
       </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>5.0560900000000002</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
         <v>418</v>
       </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>0303.HK</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>9.1824301775147958</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>29.537056136005432</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>38.719486313520228</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.40333258405570871</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
         <v>421</v>
       </c>
-      <c r="C136" s="337">
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>10.650559953703702</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>37.553768709955989</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>48.204328663659695</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.2571711311409639</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
-      <c r="C142" s="92">
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>13.030034306254134</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>51.514086021887501</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
-      <c r="C145" s="239">
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>64.544120328141631</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>5.3748859487811051E-3</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
-        <v>389</v>
-      </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
-        <v>390</v>
-      </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
-        <v>391</v>
-      </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5480,7 +5603,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6136,7 +6259,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -9319,7 +9442,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -11947,7 +12070,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12279,7 +12402,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -15014,7 +15137,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15024,7 +15147,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15042,10 +15165,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15060,8 +15183,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15076,8 +15199,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15092,8 +15215,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15119,7 +15242,7 @@
         <v>7.7786</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>USD/HKD</v>
       </c>
       <c r="H11" s="121"/>
@@ -16587,11 +16710,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16612,8 +16735,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16634,8 +16757,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16645,8 +16768,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16659,8 +16782,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16678,8 +16801,8 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16696,8 +16819,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16714,8 +16837,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16741,21 +16864,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
+      <c r="E18" s="353" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="351"/>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16769,8 +16892,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16784,8 +16907,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16805,8 +16928,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16816,8 +16939,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16831,8 +16954,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16842,8 +16965,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16863,8 +16986,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16874,8 +16997,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16889,8 +17012,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16900,8 +17023,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16921,8 +17044,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16932,8 +17055,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16947,8 +17070,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16959,8 +17082,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17022,8 +17145,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17033,8 +17156,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17048,8 +17171,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17059,8 +17182,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17080,8 +17203,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17091,8 +17214,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17106,8 +17229,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17117,8 +17240,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17136,7 +17259,7 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
@@ -17301,7 +17424,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17390,7 +17513,7 @@
         <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17448,7 +17571,7 @@
         <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AB4DEC-7A58-4982-BB58-2D3451AD7777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7771FC-D303-471C-B9D7-253C69FE767F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5569,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8649,7 +8649,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>0</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7771FC-D303-471C-B9D7-253C69FE767F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A41570-1F21-4C6F-80E9-F41CA562F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>55.65</v>
+        <v>53.15</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4229,8 +4229,7 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>14085.523251449998</v>
+        <v>7.8063000000000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4267,13 +4266,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4322,7 +4321,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4338,7 +4337,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>38.719486313520228</v>
+        <v>31.682749537465</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4352,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.13918053194738822</v>
+        <v>0.15825743289603778</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4372,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4399,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4425,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4460,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4482,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4552,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4574,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4596,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4646,7 +4645,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.4703343132953519E-2</v>
+        <v>9.915787479489864E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4654,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.085516621743038E-2</v>
+        <v>9.5128692380056445E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4673,22 +4672,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4745,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4798,13 +4797,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4816,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4954,13 +4953,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4999,13 +4998,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5148,13 +5147,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5166,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5204,7 +5203,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5239,7 +5238,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5249,7 +5248,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>9.1824301775147958</v>
+        <v>8.033729008746354</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5258,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>29.537056136005432</v>
+        <v>23.649020528718648</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5267,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>38.719486313520228</v>
+        <v>31.682749537465</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5293,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.40333258405570871</v>
+        <v>0.51176872173718813</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5446,13 +5445,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5488,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5502,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5541,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5568,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13085,16 +13084,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.085516621743038E-2</v>
+        <v>9.5128692380056445E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.085516621743038E-2</v>
+        <v>9.5128692380056445E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.2468535489667552E-2</v>
+        <v>8.6347582314205071E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14284,46 +14283,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.4703343132953519E-2</v>
+        <v>9.915787479489864E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11028247884508592</v>
+        <v>0.11546980146244649</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.9348111888988136E-2</v>
+        <v>0.1040211180926094</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11083471960044423</v>
+        <v>0.11604801779425629</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.14882888356910695</v>
+        <v>0.15582930142278084</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.1326482294371038</v>
+        <v>0.13888756290074933</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.183763761611316E-2</v>
+        <v>9.6157375979994297E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11177352888455372</v>
+        <v>0.11703098555833329</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>9.8795871133629837E-2</v>
+        <v>0.10344290176079964</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>9.9734680417739155E-2</v>
+        <v>0.10442586952487647</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14341,39 +14340,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1827746617993037E-2</v>
+        <v>1.2384084652705785E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.0592435746726057E-2</v>
+        <v>1.1090668848641676E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.226081537171307E-2</v>
+        <v>1.2837523526544352E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6392717251468139E-2</v>
+        <v>1.7163776388413959E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3538723169575462E-2</v>
+        <v>1.4175539875576189E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2161422542990439E-2</v>
+        <v>1.273345558828632E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4646243261056202E-2</v>
+        <v>1.5335154044737115E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2708083100964907E-2</v>
+        <v>1.3305829248705495E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2878470807346559E-2</v>
+        <v>1.3484231428576406E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16646,7 +16645,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-55.65</v>
+        <v>-53.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16886,7 +16885,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>55.65</v>
+        <v>53.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17425,7 +17424,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17434,7 +17433,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>9.1824301775147958</v>
+        <v>8.033729008746354</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17446,7 +17445,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>29.537056136005432</v>
+        <v>23.649020528718648</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17456,7 +17455,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>38.719486313520228</v>
+        <v>31.682749537465</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17467,7 +17466,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.40333258405570871</v>
+        <v>0.51176872173718813</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17484,7 +17483,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>55.65</v>
+        <v>53.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17497,7 +17496,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.13918053194738822</v>
+        <v>0.15825743289603778</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A41570-1F21-4C6F-80E9-F41CA562F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128DFFE-DF96-4E18-8235-8B6095A66453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4229,7 +4229,8 @@
         <v>429</v>
       </c>
       <c r="C14" s="35">
-        <v>7.8063000000000002</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>13452.75041895</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4266,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4372,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4399,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4425,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4460,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4482,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4552,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4574,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4596,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4672,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4745,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4797,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4816,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4953,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4998,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5147,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5166,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5445,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5488,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5502,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5541,17 +5542,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5568,6 +5558,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0128DFFE-DF96-4E18-8235-8B6095A66453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6152A197-CEB1-438C-9215-3FF29241A574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>53.15</v>
+        <v>52.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13452.75041895</v>
+        <v>13224.952199249999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.7786</v>
+        <v>7.8074000000000003</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>31.682749537465</v>
+        <v>31.795615222825994</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15825743289603778</v>
+        <v>0.16693505087596905</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>9.915787479489864E-2</v>
+        <v>0.1012393097082739</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.5128692380056445E-2</v>
+        <v>9.7125550239234457E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>65.878013066860788</v>
+        <v>66.121924153216384</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7727103549440075</v>
+        <v>4.7903811515169625</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-129.13468585556711</v>
+        <v>-129.52953610304712</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.968592738991028</v>
+        <v>-3.9954658616405205</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.1985557233922492E-2</v>
+        <v>1.2029933348947941E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-2.6504984195888377</v>
+        <v>-2.6603117991795302</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>92.75 HKD</v>
+        <v>93.08 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.6 HKD</v>
+        <v>68.84 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.69 HKD</v>
+        <v>63.91 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>59.22 HKD</v>
+        <v>59.43 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>57.15 HKD</v>
+        <v>57.35 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>64.892912330803952</v>
+        <v>65.120996571434517</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>8.033729008746354</v>
+        <v>8.0634736151603477</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>23.649020528718648</v>
+        <v>23.732141607665646</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>31.682749537465</v>
+        <v>31.795615222825994</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51176872173718813</v>
+        <v>0.51174556753062317</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>10.650559953703702</v>
+        <v>10.689993287037037</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>37.553768709955989</v>
+        <v>37.685761904765343</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>48.204328663659695</v>
+        <v>48.375755191802384</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.2571711311409639</v>
+        <v>0.25714043490202776</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>13.030034306254134</v>
+        <v>13.078277561855415</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>51.514086021887501</v>
+        <v>51.695146645768645</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>64.544120328141631</v>
+        <v>64.773424207624061</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3748859487811051E-3</v>
+        <v>5.3373317687051003E-3</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -6238,11 +6238,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.5893739999999994</v>
+        <v>4.6063659999999995</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7443,11 +7443,11 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>32.4</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>32.4</v>
       </c>
       <c r="E62" s="183">
@@ -7591,11 +7591,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.5893739999999994</v>
+        <v>4.6063659999999995</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8941,11 +8941,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.269088168383075</v>
+        <v>19.340431307154763</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6504984195888377</v>
+        <v>-2.6603117991795302</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-129.13468585556711</v>
+        <v>-129.52953610304712</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9203,11 +9203,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-269.04521302249748</v>
+        <v>-269.44006326997749</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.3346858555671</v>
+        <v>-279.72953610304711</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9219,11 +9219,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55827047919800865</v>
+        <v>0.55745236316063507</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53770622699417447</v>
+        <v>0.53694723157396262</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9236,7 +9236,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.3346858555671</v>
+        <v>279.72953610304711</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9351,11 +9351,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1208.01658</v>
+        <v>-1212.4892200000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7727103549440075</v>
+        <v>-4.7903811515169634</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-1004.4870673961143</v>
+        <v>-1011.2889001709301</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.968592738991028</v>
+        <v>-3.9954658616405205</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9385,11 +9385,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0336540000000003</v>
+        <v>3.0448860000000004</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.1985557233922493E-2</v>
+        <v>1.2029933348947943E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9402,11 +9402,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2209.4699933961147</v>
+        <v>-2220.7332341709302</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.7293175367011138</v>
+        <v>-8.773817079808536</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12919,16 +12919,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.5893739999999994</v>
+        <v>4.6063659999999995</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12975,16 +12975,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1279.74255626997</v>
+        <v>1284.4807592397301</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1279.74255626997</v>
+        <v>1284.4807592397301</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1161.6124741527419</v>
+        <v>1165.9133045406777</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13030,16 +13030,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4625242632325559</v>
+        <v>7.4901540036461398</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4083252692537283</v>
+        <v>6.4320518740096624</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4569898507656651</v>
+        <v>6.4808966344673662</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13085,16 +13085,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.5128692380056445E-2</v>
+        <v>9.7125550239234457E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.5128692380056445E-2</v>
+        <v>9.7125550239234457E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.6347582314205071E-2</v>
+        <v>8.8160114832535871E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14227,46 +14227,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2702410453488628</v>
+        <v>5.2897539322573106</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1372199477290312</v>
+        <v>6.1599427943202691</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5287224266221893</v>
+        <v>5.5491923319890573</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1679521457647217</v>
+        <v>6.1907887772662811</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.282327370620802</v>
+        <v>8.3129924039524923</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.3818739681748262</v>
+        <v>7.4092051036340907</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1107645333366971</v>
+        <v>5.1296869639231906</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2201968824254141</v>
+        <v>6.2432269482745202</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.4979902285865005</v>
+        <v>5.5183463490430471</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5502349652471841</v>
+        <v>5.5707845200512773</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14284,46 +14284,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>9.915787479489864E-2</v>
+        <v>0.1012393097082739</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11546980146244649</v>
+        <v>0.11789364199656018</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1040211180926094</v>
+        <v>0.10620463793280492</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11604801779425629</v>
+        <v>0.11848399573715371</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15582930142278084</v>
+        <v>0.15910033308999985</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.13888756290074933</v>
+        <v>0.14180296849060461</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.6157375979994297E-2</v>
+        <v>9.8175827060730914E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11703098555833329</v>
+        <v>0.11948759709616306</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10344290176079964</v>
+        <v>0.10561428419221143</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10442586952487647</v>
+        <v>0.10661788555122062</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14341,39 +14341,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2384084652705785E-2</v>
+        <v>1.2597399029498801E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1090668848641676E-2</v>
+        <v>1.1281704292924497E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2837523526544352E-2</v>
+        <v>1.305864833370014E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7163776388413959E-2</v>
+        <v>1.745942038362109E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4175539875576189E-2</v>
+        <v>1.4419711854294246E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.273345558828632E-2</v>
+        <v>1.2952787837653931E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5335154044737115E-2</v>
+        <v>1.5599300238809141E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3305829248705495E-2</v>
+        <v>1.3535020565908077E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3484231428576406E-2</v>
+        <v>1.3716495701987292E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-129.13468585556711</v>
+        <v>-129.52953610304712</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.5707168024696</v>
+        <v>1859.1758665549896</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.7786</v>
+        <v>7.8074000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>64.892647274488766</v>
+        <v>65.120730533757381</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16242,23 +16242,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16269,23 +16269,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.148695530159657</v>
+        <v>57.348107073407824</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.203694081652934</v>
+        <v>58.407011720893067</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.3607497293576</v>
+        <v>60.572053793231206</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.582851332208861</v>
+        <v>62.802382651136327</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>66.044193937100715</v>
+        <v>66.276540758434891</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16296,23 +16296,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.148695530159657</v>
+        <v>57.348107073407824</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.224939519201975</v>
+        <v>59.432038284686087</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.68513233491673</v>
+        <v>63.908744811491864</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.59642903457798</v>
+        <v>68.838225418919322</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>76.928500910157368</v>
+        <v>77.201146505155734</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16323,23 +16323,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.148695530159657</v>
+        <v>57.348107073407824</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.457591188612597</v>
+        <v>60.669253804671222</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>67.906991807292314</v>
+        <v>68.146235573920194</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.647412900504776</v>
+        <v>76.91901777677765</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>92.753195075211181</v>
+        <v>93.084431058191129</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16350,23 +16350,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.148695530159642</v>
+        <v>57.34810707340781</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.681064934062384</v>
+        <v>61.897257419746516</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.326203727801555</v>
+        <v>72.58180947516</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.564970400109843</v>
+        <v>85.86959222750356</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>111.940233749979</v>
+        <v>112.34250908629159</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16377,23 +16377,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.148695530159642</v>
+        <v>57.34810707340781</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>62.788810376139061</v>
+        <v>63.009104251370395</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.553521487956203</v>
+        <v>76.824778734490906</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.62057904818603</v>
+        <v>94.958728956348082</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.41562760069687</v>
+        <v>133.8974148469805</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16403,23 +16403,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.148695530159642</v>
+        <v>57.34810707340781</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.73948065579755</v>
+        <v>63.963294355168706</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.39286619183018</v>
+        <v>80.678338480592473</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.37776812542148</v>
+        <v>103.7483412261149</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>156.44843753301163</v>
+        <v>157.0155029689503</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>92.753195075211181</v>
+        <v>93.084431058191129</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.59642903457798</v>
+        <v>68.838225418919322</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.68513233491673</v>
+        <v>63.908744811491864</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.224939519201975</v>
+        <v>59.432038284686087</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.148695530159657</v>
+        <v>57.348107073407824</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-53.15</v>
+        <v>-52.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16666,7 +16666,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>69.94900233080395</v>
+        <v>70.195806571434517</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>53.15</v>
+        <v>52.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.148695530159671</v>
+        <v>57.348107073407839</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.68513233491673</v>
+        <v>63.908744811491864</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.224939519201975</v>
+        <v>59.432038284686087</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.59642903457798</v>
+        <v>68.838225418919322</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.775353111706025</v>
+        <v>63.999299627616196</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.148695530159657</v>
+        <v>57.348107073407824</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>92.753195075211181</v>
+        <v>93.084431058191129</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>64.892912330803952</v>
+        <v>65.120996571434517</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>64.892647274488766</v>
+        <v>65.120730533757381</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13451881296684234</v>
+        <v>-0.13473100139344599</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0560900000000002</v>
+        <v>5.0748100000000003</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.033729008746354</v>
+        <v>8.0634736151603477</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>23.649020528718648</v>
+        <v>23.732141607665646</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>31.682749537465</v>
+        <v>31.795615222825994</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17467,7 +17467,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.51176872173718813</v>
+        <v>0.51174556753062317</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>53.15</v>
+        <v>52.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15825743289603778</v>
+        <v>0.16693505087596905</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.650559953703702</v>
+        <v>10.689993287037037</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.553768709955989</v>
+        <v>37.685761904765343</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.204328663659695</v>
+        <v>48.375755191802384</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17556,7 +17556,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.2571711311409639</v>
+        <v>0.25714043490202776</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.030034306254134</v>
+        <v>13.078277561855415</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.514086021887501</v>
+        <v>51.695146645768645</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17607,7 +17607,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.544120328141631</v>
+        <v>64.773424207624061</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.3748859487811051E-3</v>
+        <v>5.3373317687051003E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6152A197-CEB1-438C-9215-3FF29241A574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3CEB0A-4A91-4F39-A8C7-094E7493E211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3785,29 +3785,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4257,7 +4257,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8074000000000003</v>
+        <v>7.8068999999999997</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4267,13 +4267,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>31.795615222825994</v>
+        <v>31.793656028443358</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16693505087596905</v>
+        <v>0.16690907088940898</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4373,22 +4373,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4400,13 +4400,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4426,13 +4426,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4461,13 +4461,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4483,13 +4483,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4553,13 +4553,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4575,7 +4575,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4597,22 +4597,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.1012393097082739</v>
+        <v>0.10123282615999223</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.7125550239234457E-2</v>
+        <v>9.7119330143540669E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4673,22 +4673,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4746,22 +4746,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>66.121924153216384</v>
+        <v>66.117689585744927</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4798,13 +4798,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4817,13 +4817,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7903811515169625</v>
+        <v>4.7900743668542374</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-129.52953610304712</v>
+        <v>-129.52268106402835</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.9954658616405205</v>
+        <v>-3.994998547913966</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2029933348947941E-2</v>
+        <v>1.2029162930284306E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4954,13 +4954,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-2.6603117991795302</v>
+        <v>-2.6601414280060807</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -4999,13 +4999,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.84 HKD</v>
+        <v>68.83 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.91 HKD</v>
+        <v>63.9 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>57.35 HKD</v>
+        <v>57.34 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>65.120996571434517</v>
+        <v>65.117037542048564</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5167,22 +5167,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>8.0634736151603477</v>
+        <v>8.0629572157434382</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>23.732141607665646</v>
+        <v>23.73069881269992</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>31.795615222825994</v>
+        <v>31.793656028443358</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51174556753062317</v>
+        <v>0.51174596958725316</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>10.689993287037037</v>
+        <v>10.689308680555555</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>37.685761904765343</v>
+        <v>37.683470799796623</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>48.375755191802384</v>
+        <v>48.372779480352179</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25714043490202776</v>
+        <v>0.25714096792078378</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>13.078277561855415</v>
+        <v>13.077440005334559</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>51.695146645768645</v>
+        <v>51.692003840598929</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>64.773424207624061</v>
+        <v>64.769443845933495</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3373317687051003E-3</v>
+        <v>5.3379838708205174E-3</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="13.9">
@@ -5446,13 +5446,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5489,13 +5489,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5503,22 +5503,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5542,6 +5542,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5558,17 +5569,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6238,11 +6238,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.6063659999999995</v>
+        <v>4.606071</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7591,11 +7591,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.6063659999999995</v>
+        <v>4.606071</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8941,11 +8941,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.340431307154763</v>
+        <v>19.33919271099553</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6603117991795302</v>
+        <v>-2.6601414280060807</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-129.52953610304712</v>
+        <v>-129.52268106402835</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9203,11 +9203,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-269.44006326997749</v>
+        <v>-269.43320823095877</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.72953610304711</v>
+        <v>-279.72268106402834</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9219,11 +9219,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55745236316063507</v>
+        <v>0.55746654611056035</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53694723157396262</v>
+        <v>0.53696039030034648</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9236,7 +9236,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.72953610304711</v>
+        <v>279.72268106402834</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9351,11 +9351,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1212.4892200000002</v>
+        <v>-1212.41157</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7903811515169634</v>
+        <v>-4.7900743668542374</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9368,11 +9368,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-1011.2889001709301</v>
+        <v>-1011.1706187987629</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.9954658616405205</v>
+        <v>-3.994998547913966</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9385,11 +9385,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0448860000000004</v>
+        <v>3.0446909999999998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2029933348947943E-2</v>
+        <v>1.2029162930284306E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9402,11 +9402,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2220.7332341709302</v>
+        <v>-2220.5374977987631</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.773817079808536</v>
+        <v>-8.7730437518379194</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12919,16 +12919,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.6063659999999995</v>
+        <v>4.606071</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12975,16 +12975,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1284.4807592397301</v>
+        <v>1284.398498771505</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1284.4807592397301</v>
+        <v>1284.398498771505</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1165.9133045406777</v>
+        <v>1165.838637346443</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13030,16 +13030,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4901540036461398</v>
+        <v>7.4896743206528482</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4320518740096624</v>
+        <v>6.4316399537882054</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4808966344673662</v>
+        <v>6.480481586139212</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13085,16 +13085,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.7125550239234457E-2</v>
+        <v>9.7119330143540669E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.7125550239234457E-2</v>
+        <v>9.7119330143540669E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.8160114832535871E-2</v>
+        <v>8.8154468899521526E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14227,46 +14227,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2897539322573106</v>
+        <v>5.2894151668595937</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1599427943202691</v>
+        <v>6.1595483004558371</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5491923319890573</v>
+        <v>5.5488369516875489</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1907887772662811</v>
+        <v>6.1903923079693781</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.3129924039524923</v>
+        <v>8.3124600249015934</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.4092051036340907</v>
+        <v>7.4087306047545889</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1296869639231906</v>
+        <v>5.129358449503286</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2432269482745202</v>
+        <v>6.2428271207424171</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5183463490430471</v>
+        <v>5.5179929441740097</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5707845200512773</v>
+        <v>5.5704277569470388</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14284,46 +14284,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.1012393097082739</v>
+        <v>0.10123282615999223</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11789364199656018</v>
+        <v>0.11788609187475287</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10620463793280492</v>
+        <v>0.10619783639593396</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11848399573715371</v>
+        <v>0.11847640780802637</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15910033308999985</v>
+        <v>0.15909014401725538</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14180296849060461</v>
+        <v>0.14179388717233662</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.8175827060730914E-2</v>
+        <v>9.8169539703412176E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11948759709616306</v>
+        <v>0.11947994489459171</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10561428419221143</v>
+        <v>0.10560752046266048</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10661788555122062</v>
+        <v>0.10661105754922562</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-129.52953610304712</v>
+        <v>-129.52268106402835</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.1758665549896</v>
+        <v>1859.1827215940084</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8074000000000003</v>
+        <v>7.8068999999999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>65.120730533757381</v>
+        <v>65.116771521408964</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16242,23 +16242,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16269,23 +16269,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.348107073407824</v>
+        <v>57.344645833906995</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.407011720893067</v>
+        <v>58.403482667225695</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.572053793231206</v>
+        <v>60.568386086358387</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.802382651136327</v>
+        <v>62.798572109974408</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>66.276540758434891</v>
+        <v>66.272507725911723</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16296,23 +16296,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.348107073407824</v>
+        <v>57.344645833906995</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.432038284686087</v>
+        <v>59.428443586465868</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.908744811491864</v>
+        <v>63.904863416898536</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.838225418919322</v>
+        <v>68.834028331482827</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>77.201146505155734</v>
+        <v>77.196413841145343</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16323,23 +16323,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.348107073407824</v>
+        <v>57.344645833906995</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.669253804671222</v>
+        <v>60.665579872934103</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>68.146235573920194</v>
+        <v>68.142082802763454</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.91901777677765</v>
+        <v>76.914303180800687</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>93.084431058191129</v>
+        <v>93.078681199944924</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16350,23 +16350,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.34810707340781</v>
+        <v>57.344645833906981</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.897257419746516</v>
+        <v>61.893504844439491</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.58180947516</v>
+        <v>72.577372641837798</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.86959222750356</v>
+        <v>85.864304420569653</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>112.34250908629159</v>
+        <v>112.33552590593894</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16377,23 +16377,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.34810707340781</v>
+        <v>57.344645833906981</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>63.009104251370395</v>
+        <v>63.005280471383735</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.824778734490906</v>
+        <v>76.820070173752455</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.958728956348082</v>
+        <v>94.952859064678591</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.8974148469805</v>
+        <v>133.88905125152414</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16403,23 +16403,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.34810707340781</v>
+        <v>57.344645833906981</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.963294355168706</v>
+        <v>63.959409467124061</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.678338480592473</v>
+        <v>80.673383130926453</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.7483412261149</v>
+        <v>103.7419084317973</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>157.0155029689503</v>
+        <v>157.00565884936802</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>93.084431058191129</v>
+        <v>93.078681199944924</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16476,7 +16476,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.838225418919322</v>
+        <v>68.834028331482827</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.908744811491864</v>
+        <v>63.904863416898536</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.432038284686087</v>
+        <v>59.428443586465868</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.348107073407824</v>
+        <v>57.344645833906995</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16666,7 +16666,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16695,7 +16695,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>70.195806571434517</v>
+        <v>70.19152254204856</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.348107073407839</v>
+        <v>57.344645833907009</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16948,7 +16948,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.908744811491864</v>
+        <v>63.904863416898536</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.432038284686087</v>
+        <v>59.428443586465868</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.838225418919322</v>
+        <v>68.834028331482827</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.999299627616196</v>
+        <v>63.995412433728859</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.348107073407824</v>
+        <v>57.344645833906995</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>93.084431058191129</v>
+        <v>93.078681199944924</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17249,7 +17249,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>65.120996571434517</v>
+        <v>65.117037542048564</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>65.120730533757381</v>
+        <v>65.116771521408964</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13473100139344599</v>
+        <v>-0.13472731688957484</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17407,7 +17407,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0748100000000003</v>
+        <v>5.0744850000000001</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.0634736151603477</v>
+        <v>8.0629572157434382</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17446,7 +17446,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>23.732141607665646</v>
+        <v>23.73069881269992</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17456,7 +17456,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>31.795615222825994</v>
+        <v>31.793656028443358</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17467,7 +17467,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.51174556753062317</v>
+        <v>0.51174596958725316</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16693505087596905</v>
+        <v>0.16690907088940898</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.689993287037037</v>
+        <v>10.689308680555555</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.685761904765343</v>
+        <v>37.683470799796623</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.375755191802384</v>
+        <v>48.372779480352179</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17556,7 +17556,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.25714043490202776</v>
+        <v>0.25714096792078378</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.078277561855415</v>
+        <v>13.077440005334559</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.695146645768645</v>
+        <v>51.692003840598929</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17607,7 +17607,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.773424207624061</v>
+        <v>64.769443845933495</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17617,7 +17617,7 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.3373317687051003E-3</v>
+        <v>5.3379838708205174E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3CEB0A-4A91-4F39-A8C7-094E7493E211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868E5562-9E61-49BF-AF84-3CB59C126471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2374,6 +2374,18 @@
   </si>
   <si>
     <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>in contrast to a benchmark yield of</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
   </si>
   <si>
     <t>Y</t>
@@ -4097,7 +4109,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J179"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
@@ -4119,7 +4131,7 @@
         <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4162,7 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4197,10 +4209,10 @@
         <v>426</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4209,7 +4221,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>52.25</v>
+        <v>51.75</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4230,7 +4242,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13224.952199249999</v>
+        <v>13098.39763275</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4257,7 +4269,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8068999999999997</v>
+        <v>7.8139000000000003</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4297,7 +4309,7 @@
         <v>355</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D22" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4313,7 +4325,7 @@
         <v>56</v>
       </c>
       <c r="C23" s="48" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>31.793656028443358</v>
+        <v>31.821083851628465</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4353,10 +4365,14 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16690907088940898</v>
-      </c>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+        <v>0.17134418888864666</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E26" s="339">
+        <v>0.1174</v>
+      </c>
     </row>
     <row r="27" spans="1:6">
       <c r="D27" s="5"/>
@@ -4646,7 +4662,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10123282615999223</v>
+        <v>0.10230256777637912</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4655,7 +4671,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.7119330143540669E-2</v>
+        <v>9.814560386473431E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4712,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4724,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="286" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4777,7 +4793,7 @@
       </c>
       <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>66.117689585744927</v>
+        <v>66.176973530345236</v>
       </c>
       <c r="D82" s="1" t="str">
         <f>Market_currency</f>
@@ -4844,7 +4860,7 @@
       </c>
       <c r="C92" s="248">
         <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7900743668542374</v>
+        <v>4.794369352132386</v>
       </c>
       <c r="D92" s="1" t="str">
         <f>Market_currency</f>
@@ -4902,7 +4918,7 @@
       </c>
       <c r="C99" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-129.52268106402835</v>
+        <v>-129.61865161029084</v>
       </c>
       <c r="D99" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4915,7 +4931,7 @@
       </c>
       <c r="C100" s="248">
         <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-3.994998547913966</v>
+        <v>-4.001543404669051</v>
       </c>
       <c r="D100" s="1" t="str">
         <f>Market_currency</f>
@@ -4946,7 +4962,7 @@
       </c>
       <c r="C104" s="248">
         <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2029162930284306E-2</v>
+        <v>1.2039948791575213E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
@@ -4968,7 +4984,7 @@
       </c>
       <c r="C108" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Market_currency</f>
@@ -4981,7 +4997,7 @@
       </c>
       <c r="C109" s="248">
         <f>BS!D47</f>
-        <v>-2.6601414280060807</v>
+        <v>-2.6625266244343737</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5039,7 +5055,7 @@
       </c>
       <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
-        <v>93.08 HKD</v>
+        <v>93.16 HKD</v>
       </c>
       <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
@@ -5061,7 +5077,7 @@
       </c>
       <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
-        <v>68.83 HKD</v>
+        <v>68.89 HKD</v>
       </c>
       <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
@@ -5083,7 +5099,7 @@
       </c>
       <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
-        <v>63.9 HKD</v>
+        <v>63.96 HKD</v>
       </c>
       <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
@@ -5105,7 +5121,7 @@
       </c>
       <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
-        <v>59.43 HKD</v>
+        <v>59.48 HKD</v>
       </c>
       <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
@@ -5127,7 +5143,7 @@
       </c>
       <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
-        <v>57.34 HKD</v>
+        <v>57.39 HKD</v>
       </c>
       <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
@@ -5140,7 +5156,7 @@
       </c>
       <c r="C122" s="241">
         <f>Scenarios!C60</f>
-        <v>65.117037542048564</v>
+        <v>65.172461488868507</v>
       </c>
       <c r="D122" s="236" t="str">
         <f>Market_currency</f>
@@ -5213,7 +5229,7 @@
       </c>
       <c r="C133" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="D133" s="236" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5265,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>8.0629572157434382</v>
+        <v>8.070186807580173</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5259,7 +5275,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>23.73069881269992</v>
+        <v>23.750897044048294</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5268,7 +5284,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>31.793656028443358</v>
+        <v>31.821083851628465</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5294,7 +5310,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51174596958725316</v>
+        <v>0.5117403405568236</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5311,40 +5327,40 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="2:4">
       <c r="B145" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C145" s="240">
         <f>Scenarios!C91</f>
-        <v>10.689308680555555</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6">
+        <v>10.698893171296296</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C146" s="240">
         <f>Scenarios!C92</f>
-        <v>37.683470799796623</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6">
+        <v>37.715544843095202</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
       <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C147" s="239">
         <f>Scenarios!C93</f>
-        <v>48.372779480352179</v>
+        <v>48.4144380143915</v>
       </c>
       <c r="D147" s="342" t="str">
         <f>IF($D$11="","",C147*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="2:4">
       <c r="B148" s="290" t="s">
         <v>425</v>
       </c>
@@ -5357,21 +5373,21 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="2:4">
       <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C149" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25714096792078378</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6">
+        <v>0.2571335053431929</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="2:4">
       <c r="B152" s="1" t="s">
         <v>419</v>
       </c>
@@ -5380,40 +5396,40 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="2:4">
       <c r="B153" s="236" t="str">
         <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C153" s="240">
         <f>Scenarios!C97</f>
-        <v>13.077440005334559</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6">
+        <v>13.089165796626538</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C154" s="240">
         <f>Scenarios!C98</f>
-        <v>51.692003840598929</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
+        <v>51.736001156509182</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
       <c r="B155" s="80" t="s">
         <v>409</v>
       </c>
       <c r="C155" s="239">
         <f>Scenarios!C99</f>
-        <v>64.769443845933495</v>
+        <v>64.825166953135721</v>
       </c>
       <c r="D155" s="342" t="str">
         <f>IF($D$11="","",C155*$E$22)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="2:4">
       <c r="B156" s="290" t="s">
         <v>425</v>
       </c>
@@ -5426,127 +5442,196 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="2:4">
       <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3379838708205174E-3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="13.9">
-      <c r="A159" s="247" t="s">
+        <v>5.3288540558208419E-3</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
+      <c r="B160" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C160" s="92">
+        <f>E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C161" s="240">
+        <f>Scenarios!C103</f>
+        <v>12.253695717751807</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="B162" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C162" s="240">
+        <f>Scenarios!C104</f>
+        <v>46.71303911050348</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="B163" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C163" s="239">
+        <f>Scenarios!C105</f>
+        <v>58.966734828255284</v>
+      </c>
+      <c r="D163" s="342" t="str">
+        <f>IF($D$11="","",C163*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="B164" s="290" t="s">
+        <v>425</v>
+      </c>
+      <c r="C164" s="340" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="D164" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="238" t="s">
+        <v>263</v>
+      </c>
+      <c r="C165" s="92">
+        <f>Scenarios!F105</f>
+        <v>9.5216378389229028E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" ht="13.9">
+      <c r="A167" s="247" t="s">
         <v>382</v>
       </c>
-      <c r="B159" s="36"/>
-      <c r="C159" s="36"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="36"/>
-      <c r="F159" s="36"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B167" s="36"/>
+      <c r="C167" s="36"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="36"/>
+      <c r="F167" s="36"/>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
-    </row>
-    <row r="163" spans="2:6">
-      <c r="B163" s="234" t="s">
+      <c r="C169" s="343"/>
+      <c r="D169" s="343"/>
+      <c r="E169" s="343"/>
+      <c r="F169" s="343"/>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="B171" s="234" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="164" spans="2:6">
-      <c r="B164" s="347" t="s">
+    <row r="172" spans="1:6">
+      <c r="B172" s="347" t="s">
         <v>388</v>
       </c>
-      <c r="C164" s="347"/>
-      <c r="D164" s="347"/>
-      <c r="E164" s="347"/>
-      <c r="F164" s="347"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="238" t="s">
+      <c r="C172" s="347"/>
+      <c r="D172" s="347"/>
+      <c r="E172" s="347"/>
+      <c r="F172" s="347"/>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="B173" s="238" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
-      <c r="B166" s="238" t="s">
+    <row r="174" spans="1:6">
+      <c r="B174" s="238" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
-      <c r="B167" s="238" t="s">
+    <row r="175" spans="1:6">
+      <c r="B175" s="238" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="169" spans="2:6">
-      <c r="B169" s="1" t="s">
+    <row r="177" spans="2:6">
+      <c r="B177" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+    <row r="178" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B178" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
-    </row>
-    <row r="172" spans="2:6">
-      <c r="B172" s="1" t="s">
+      <c r="C178" s="344"/>
+      <c r="D178" s="344"/>
+      <c r="E178" s="344"/>
+      <c r="F178" s="344"/>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="1" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+    <row r="181" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B181" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
-    </row>
-    <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="C181" s="349"/>
+      <c r="D181" s="349"/>
+      <c r="E181" s="349"/>
+      <c r="F181" s="349"/>
+    </row>
+    <row r="182" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B182" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
-    </row>
-    <row r="176" spans="2:6">
-      <c r="B176" s="1" t="s">
+      <c r="C182" s="349"/>
+      <c r="D182" s="349"/>
+      <c r="E182" s="349"/>
+      <c r="F182" s="349"/>
+    </row>
+    <row r="184" spans="2:6">
+      <c r="B184" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="177" spans="2:2">
-      <c r="B177" s="238" t="s">
+    <row r="185" spans="2:6">
+      <c r="B185" s="238" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="178" spans="2:2">
-      <c r="B178" s="238" t="s">
+    <row r="186" spans="2:6">
+      <c r="B186" s="238" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="179" spans="2:2">
-      <c r="B179" s="238" t="s">
+    <row r="187" spans="2:6">
+      <c r="B187" s="238" t="s">
         <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B169:F169"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B172:F172"/>
     <mergeCell ref="B69:F69"/>
     <mergeCell ref="B113:F113"/>
     <mergeCell ref="B78:F78"/>
@@ -6238,11 +6323,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.606071</v>
+        <v>4.610201</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -6259,7 +6344,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7591,11 +7676,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.606071</v>
+        <v>4.610201</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -8941,11 +9026,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.33919271099553</v>
+        <v>19.356533057224759</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6601414280060807</v>
+        <v>-2.6625266244343737</v>
       </c>
       <c r="F47" s="283"/>
     </row>
@@ -9136,7 +9221,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-129.52268106402835</v>
+        <v>-129.61865161029084</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9203,11 +9288,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-269.43320823095877</v>
+        <v>-269.52917877722126</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.72268106402834</v>
+        <v>-279.81865161029083</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>359</v>
@@ -9219,11 +9304,11 @@
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
-        <v>0.55746654611056035</v>
+        <v>0.55726805046271988</v>
       </c>
       <c r="D74" s="289">
         <f>-$C$66/D73</f>
-        <v>0.53696039030034648</v>
+        <v>0.53677622680130199</v>
       </c>
       <c r="F74" s="283" t="s">
         <v>327</v>
@@ -9236,7 +9321,7 @@
       <c r="C75" s="293"/>
       <c r="D75" s="292">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.72268106402834</v>
+        <v>279.81865161029083</v>
       </c>
       <c r="F75" s="283" t="s">
         <v>360</v>
@@ -9351,11 +9436,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1212.41157</v>
+        <v>-1213.4986700000002</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7900743668542374</v>
+        <v>-4.7943693521323869</v>
       </c>
       <c r="E86" s="269" t="str">
         <f>Market_currency</f>
@@ -9368,11 +9453,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-1011.1706187987629</v>
+        <v>-1012.8271818176516</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-3.994998547913966</v>
+        <v>-4.001543404669051</v>
       </c>
       <c r="E87" s="269" t="str">
         <f>Market_currency</f>
@@ -9385,11 +9470,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0446909999999998</v>
+        <v>3.0474210000000004</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2029162930284306E-2</v>
+        <v>1.2039948791575215E-2</v>
       </c>
       <c r="E88" s="269" t="str">
         <f>Market_currency</f>
@@ -9402,11 +9487,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2220.5374977987631</v>
+        <v>-2223.2784308176515</v>
       </c>
       <c r="D89" s="271">
         <f>SUM(D86:D88)</f>
-        <v>-8.7730437518379194</v>
+        <v>-8.783872808009864</v>
       </c>
       <c r="E89" s="269" t="str">
         <f>Market_currency</f>
@@ -12070,7 +12155,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12402,7 +12487,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12919,16 +13004,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="E90" s="302"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.606071</v>
+        <v>4.610201</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -12975,16 +13060,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1284.398498771505</v>
+        <v>1285.5501453266552</v>
       </c>
       <c r="E91" s="302"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1284.398498771505</v>
+        <v>1285.5501453266552</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1165.838637346443</v>
+        <v>1166.8839780657329</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13030,16 +13115,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4896743206528482</v>
+        <v>7.496389882558927</v>
       </c>
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4316399537882054</v>
+        <v>6.4374068368886057</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.480481586139212</v>
+        <v>6.4862922627333761</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13085,16 +13170,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.7119330143540669E-2</v>
+        <v>9.814560386473431E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.7119330143540669E-2</v>
+        <v>9.814560386473431E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.8154468899521526E-2</v>
+        <v>8.9086009661835747E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14227,46 +14312,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2894151668595937</v>
+        <v>5.2941578824276201</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="299"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1595483004558371</v>
+        <v>6.1650712145578748</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5488369516875489</v>
+        <v>5.5538122759086628</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1903923079693781</v>
+        <v>6.195942878126008</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.3124600249015934</v>
+        <v>8.319913331614158</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.4087306047545889</v>
+        <v>7.4153735890676051</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.129358449503286</v>
+        <v>5.133957651381948</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2428271207424171</v>
+        <v>6.2484247061918534</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5179929441740097</v>
+        <v>5.5229406123405314</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5704277569470388</v>
+        <v>5.5754224404063679</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14284,46 +14369,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10123282615999223</v>
+        <v>0.10230256777637912</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11788609187475287</v>
+        <v>0.11913181090933091</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10619783639593396</v>
+        <v>0.10732004397891136</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11847640780802637</v>
+        <v>0.11972836479470547</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.15909014401725538</v>
+        <v>0.16077127210848616</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14179388717233662</v>
+        <v>0.14329224326700687</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.8169539703412176E-2</v>
+        <v>9.9206911137815421E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.11947994489459171</v>
+        <v>0.12074250639984258</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10560752046266048</v>
+        <v>0.10672349009353684</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10661105754922562</v>
+        <v>0.10773763169867377</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -14341,39 +14426,39 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2597399029498801E-2</v>
+        <v>1.2719113029783815E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1281704292924497E-2</v>
+        <v>1.1390706266769178E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.305864833370014E-2</v>
+        <v>1.3184818849001589E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.745942038362109E-2</v>
+        <v>1.7628110435636751E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4419711854294246E-2</v>
+        <v>1.4559032741775351E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.2952787837653931E-2</v>
+        <v>1.3077935546230298E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5599300238809141E-2</v>
+        <v>1.5750018115512611E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3535020565908077E-2</v>
+        <v>1.3665793711472406E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3716495701987292E-2</v>
+        <v>1.3849022230508908E-2</v>
       </c>
       <c r="P126" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15193,7 +15278,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-129.52268106402835</v>
+        <v>-129.61865161029084</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15225,7 +15310,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.1827215940084</v>
+        <v>1859.0867510477458</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15239,7 +15324,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8068999999999997</v>
+        <v>7.8139000000000003</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15253,7 +15338,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15306,7 +15391,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>65.116771521408964</v>
+        <v>65.172195229703433</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16242,23 +16327,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16269,23 +16354,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.344645833906995</v>
+        <v>57.393100722335362</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.403482667225695</v>
+        <v>58.452886953985441</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.568386086358387</v>
+        <v>60.619731517994339</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.798572109974408</v>
+        <v>62.851917221658169</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>66.272507725911723</v>
+        <v>66.328967716652684</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16296,23 +16381,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.344645833906995</v>
+        <v>57.393100722335362</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.428443586465868</v>
+        <v>59.478766896965489</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.904863416898536</v>
+        <v>63.95920047662166</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.834028331482827</v>
+        <v>68.892785091010253</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>77.196413841145343</v>
+        <v>77.262668672707449</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16323,23 +16408,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.344645833906995</v>
+        <v>57.393100722335362</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.665579872934103</v>
+        <v>60.717012452670573</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>68.142082802763454</v>
+        <v>68.200219134374407</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.914303180800687</v>
+        <v>76.980305059894789</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>93.078681199944924</v>
+        <v>93.159176750808129</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16350,23 +16435,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.344645833906981</v>
+        <v>57.393100722335348</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.893504844439491</v>
+        <v>61.946038434154403</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.577372641837798</v>
+        <v>72.6394858437652</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.864304420569653</v>
+        <v>85.938331253061179</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>112.33552590593894</v>
+        <v>112.4332879662927</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16377,23 +16462,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.344645833906981</v>
+        <v>57.393100722335348</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>63.005280471383735</v>
+        <v>63.058810926613575</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.820070173752455</v>
+        <v>76.885987559507413</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>94.952859064678591</v>
+        <v>95.035035083467974</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>133.88905125152414</v>
+        <v>134.00613912332921</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16403,23 +16488,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.344645833906981</v>
+        <v>57.393100722335348</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>63.959409467124061</v>
+        <v>64.013795435165676</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.673383130926453</v>
+        <v>80.742755561667281</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.7419084317973</v>
+        <v>103.83196508766028</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>157.00565884936802</v>
+        <v>157.14347405893642</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16454,7 +16539,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>93.078681199944924</v>
+        <v>93.159176750808129</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16476,7 +16561,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.834028331482827</v>
+        <v>68.892785091010253</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16499,7 +16584,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.904863416898536</v>
+        <v>63.95920047662166</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16522,7 +16607,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.428443586465868</v>
+        <v>59.478766896965489</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16545,7 +16630,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.344645833906995</v>
+        <v>57.393100722335362</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16613,7 +16698,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
-  <dimension ref="B2:I104"/>
+  <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -16646,7 +16731,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-52.25</v>
+        <v>-51.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16666,7 +16751,7 @@
       </c>
       <c r="I4" s="264">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16675,7 +16760,7 @@
       </c>
       <c r="I5" s="264">
         <f t="shared" si="0"/>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16695,7 +16780,7 @@
       </c>
       <c r="I6" s="264">
         <f t="shared" si="0"/>
-        <v>70.19152254204856</v>
+        <v>70.251496488868511</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -16886,7 +16971,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>52.25</v>
+        <v>51.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -16901,7 +16986,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.344645833907009</v>
+        <v>57.393100722335376</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -16948,7 +17033,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.904863416898536</v>
+        <v>63.95920047662166</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17006,7 +17091,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.428443586465868</v>
+        <v>59.478766896965489</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17064,7 +17149,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.834028331482827</v>
+        <v>68.892785091010253</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17091,7 +17176,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>63.995412433728859</v>
+        <v>64.049830683568146</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17165,7 +17250,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.344645833906995</v>
+        <v>57.393100722335362</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17223,7 +17308,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>93.078681199944924</v>
+        <v>93.159176750808129</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17249,7 +17334,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>65.117037542048564</v>
+        <v>65.172461488868507</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17311,7 +17396,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>65.116771521408964</v>
+        <v>65.172195229703433</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17374,7 +17459,7 @@
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
-        <v>-0.13472731688957484</v>
+        <v>-0.13477890212126106</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17407,7 +17492,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0744850000000001</v>
+        <v>5.0790350000000002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17434,7 +17519,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.0629572157434382</v>
+        <v>8.070186807580173</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17446,7 +17531,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>23.73069881269992</v>
+        <v>23.750897044048294</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17456,7 +17541,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>31.793656028443358</v>
+        <v>31.821083851628465</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17467,7 +17552,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.51174596958725316</v>
+        <v>0.5117403405568236</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17484,7 +17569,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>52.25</v>
+        <v>51.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17497,7 +17582,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16690907088940898</v>
+        <v>0.17134418888864666</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17523,7 +17608,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.689308680555555</v>
+        <v>10.698893171296296</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17535,7 +17620,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.683470799796623</v>
+        <v>37.715544843095202</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17545,7 +17630,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.372779480352179</v>
+        <v>48.4144380143915</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17556,7 +17641,7 @@
       </c>
       <c r="F93" s="329">
         <f>(1-C93/C60)</f>
-        <v>0.25714096792078378</v>
+        <v>0.2571335053431929</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17583,7 +17668,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.077440005334559</v>
+        <v>13.089165796626538</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17595,7 +17680,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.692003840598929</v>
+        <v>51.736001156509182</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17607,7 +17692,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.769443845933495</v>
+        <v>64.825166953135721</v>
       </c>
       <c r="D99" t="s">
         <v>404</v>
@@ -17617,39 +17702,95 @@
       </c>
       <c r="F99" s="329">
         <f>(1-C99/C60)</f>
-        <v>5.3379838708205174E-3</v>
+        <v>5.3288540558208419E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="14.65">
-      <c r="E101" s="320" t="s">
+    <row r="101" spans="2:8" ht="13.15">
+      <c r="B101" s="109" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
+      <c r="B102" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="C102" s="135">
+        <f>Thesis!E26</f>
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
+      <c r="B103" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C103" s="117">
+        <f>PV(C102, C76, -C77, 0)</f>
+        <v>12.253695717751807</v>
+      </c>
+      <c r="D103" s="117"/>
+    </row>
+    <row r="104" spans="2:8">
+      <c r="B104" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" s="117">
+        <f>C60/(1+C102)^C76</f>
+        <v>46.71303911050348</v>
+      </c>
+      <c r="D104" s="117"/>
+    </row>
+    <row r="105" spans="2:8" ht="13.15">
+      <c r="B105" s="111" t="s">
+        <v>406</v>
+      </c>
+      <c r="C105" s="112">
+        <f>C103+C104</f>
+        <v>58.966734828255284</v>
+      </c>
+      <c r="D105" t="s">
+        <v>404</v>
+      </c>
+      <c r="E105" s="147" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" s="329">
+        <f>(1-C105/C66)</f>
+        <v>9.5216378389229028E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
+      <c r="B106" s="100"/>
+    </row>
+    <row r="107" spans="2:8" ht="14.65">
+      <c r="E107" s="320" t="s">
         <v>332</v>
       </c>
-      <c r="F101" s="317"/>
-    </row>
-    <row r="102" spans="2:8" ht="13.9">
-      <c r="E102" s="313" t="s">
+      <c r="F107" s="317"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="313" t="s">
         <v>333</v>
       </c>
-      <c r="F102" s="318" t="s">
+      <c r="F108" s="318" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="103" spans="2:8" ht="13.9">
-      <c r="E103" s="314" t="s">
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="314" t="s">
         <v>333</v>
       </c>
-      <c r="F103" s="318" t="s">
+      <c r="F109" s="318" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="104" spans="2:8" ht="13.9">
-      <c r="E104" s="315" t="s">
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="315" t="s">
         <v>333</v>
       </c>
-      <c r="F104" s="319" t="s">
+      <c r="F110" s="319" t="s">
         <v>336</v>
       </c>
     </row>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868E5562-9E61-49BF-AF84-3CB59C126471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC04106B-15AE-41C8-B1EA-D9035BA1B001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2379,15 +2356,63 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
   </si>
   <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
     <t>Y</t>
   </si>
   <si>
@@ -2400,13 +2425,13 @@
     <t/>
   </si>
   <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>USD</t>
-  </si>
-  <si>
-    <t>CNS_02</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -3089,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3603,14 +3628,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3668,9 +3687,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3678,7 +3694,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3770,9 +3785,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3787,9 +3799,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3797,6 +3806,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4109,10 +4145,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4127,11 +4163,11 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>434</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4150,7 +4186,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4159,10 +4195,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>435</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4176,9 +4212,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4199,20 +4235,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4228,17 +4264,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4252,14 +4288,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>USD/HKD</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4274,29 +4310,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4304,286 +4340,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D22" s="32" t="str">
+      <c r="C24" s="291" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>450</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (HKD):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>31.821083851628465</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (HKD) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>65.172461488868507</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>0.17134418888864666</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>0303.HK (HKD)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>432</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>31.821083851628465</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>48.4144380143915</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>64.825166953135721</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>439</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>58.966734828255284</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>210.2763260031652</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>0</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>-4.9000000000000004</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-33.887093790522258</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4591,20 +4679,16 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
       <c r="D56" s="1" t="str">
@@ -4612,1059 +4696,1092 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>199.70000000000005</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-33.887093790522258</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>171.48923221264295</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>199.70000000000005</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>171.48923221264295</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.10230256777637912</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>9.814560386473431E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>66.176973530345236</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>155.30000000000001</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>4.794369352132386</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>150.19999999999999</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>-129.61865161029084</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>USD</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.001543404669051</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>0.39</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2039948791575213E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>-129.61865161029084</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>-4.001543404669051</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>57.393100722335376</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>0.39</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
-        <v>HKD</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-2.6625266244343737</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>1.2039948791575213E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>57.393100722335376</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-2.6625266244343737</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>93.16 HKD</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.05</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>68.89 HKD</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.03</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>63.96 HKD</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.01</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>59.48 HKD</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.39 HKD</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>65.172461488868507</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>5.0790350000000002</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>0303.HK</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>8.070186807580173</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>23.750897044048294</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>31.821083851628465</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C140" s="340" t="str">
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.5117403405568236</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>10.698893171296296</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>37.715544843095202</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>48.4144380143915</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C148" s="340" t="str">
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.2571335053431929</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>13.089165796626538</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>51.736001156509182</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>64.825166953135721</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C156" s="340" t="str">
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>5.3288540558208419E-3</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>12.253695717751807</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>46.71303911050348</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>58.966734828255284</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>425</v>
-      </c>
-      <c r="C164" s="340" t="str">
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>419</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>9.5216378389229028E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5678,17 +5795,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="104">
@@ -6216,7 +6333,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>355.2</v>
@@ -6250,7 +6367,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-54.4</v>
@@ -6284,7 +6401,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-171.1</v>
@@ -6344,7 +6461,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7623,7 +7740,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8071,11 +8188,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8105,11 +8222,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8241,15 +8358,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8306,7 +8423,7 @@
       <c r="C4" s="19">
         <v>547.9</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8316,7 +8433,7 @@
       <c r="G4" s="19">
         <v>150.19999999999999</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8327,7 +8444,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8337,7 +8454,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8348,7 +8465,7 @@
       <c r="C6" s="19">
         <v>425.2</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8358,7 +8475,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8369,7 +8486,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8379,7 +8496,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8390,7 +8507,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8400,7 +8517,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8411,7 +8528,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8421,7 +8538,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8432,10 +8549,10 @@
       <c r="C10" s="19">
         <v>5.9</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8444,10 +8561,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8505,7 +8622,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8514,7 +8631,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8526,7 +8643,7 @@
         <f>1.2+6.2</f>
         <v>7.4</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8535,7 +8652,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8546,7 +8663,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8555,7 +8672,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8566,7 +8683,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8575,7 +8692,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8587,7 +8704,7 @@
         <f>97.3+136.4+14.3</f>
         <v>248</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8596,7 +8713,7 @@
       <c r="G19" s="19">
         <v>3.9</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8607,7 +8724,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8616,7 +8733,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8627,7 +8744,7 @@
       <c r="C21" s="19">
         <v>36.1</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8636,7 +8753,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8647,10 +8764,10 @@
       <c r="C22" s="19">
         <v>11.7</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8659,10 +8776,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -8995,13 +9112,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9017,7 +9134,7 @@
         <f>H29</f>
         <v>-86.245000000000118</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9032,23 +9149,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-2.6625266244343737</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9062,7 +9179,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.78872524123920762</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9073,22 +9190,22 @@
         <f>G29/G32</f>
         <v>0.43653832764742734</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9102,7 +9219,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.15356418655435974</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9116,22 +9233,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9153,22 +9270,22 @@
         <f>G39/G32</f>
         <v>0.17266587760217228</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9182,7 +9299,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9201,13 +9318,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9235,7 +9352,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9245,7 +9362,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9255,7 +9372,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9265,26 +9382,26 @@
         <f>SUM(C66:C69)</f>
         <v>150.19999999999999</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9295,65 +9412,65 @@
         <v>-279.81865161029083</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>0.55726805046271988</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>0.53677622680130199</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>279.81865161029083</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9367,7 +9484,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9381,7 +9498,7 @@
         <f>G19*H19</f>
         <v>0.39</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9395,7 +9512,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9409,11 +9526,11 @@
         <f>SUM(D79:D81)</f>
         <v>0.39</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9424,15 +9541,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9442,14 +9559,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-4.7943693521323869</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9459,13 +9576,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-4.001543404669051</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9476,24 +9593,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.2039948791575215E-2</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-2223.2784308176515</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>-8.783872808009864</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9512,22 +9629,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>USD</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9614,7 +9731,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9628,7 +9745,7 @@
         <v>2282.5500000000002</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9684,7 +9801,7 @@
         <f>C25</f>
         <v>-1909.898673996835</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1789.1999999999998</v>
@@ -9739,7 +9856,7 @@
         <f>C4+C5</f>
         <v>372.6513260031652</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>356.5</v>
@@ -9794,7 +9911,7 @@
         <f>C35</f>
         <v>-162.375</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-159.59999999999997</v>
@@ -9850,7 +9967,7 @@
         <v>210.2763260031652</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9906,7 +10023,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -9961,7 +10078,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>32.4</v>
@@ -10017,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10073,7 +10190,7 @@
         <f>C50</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-4.9000000000000004</v>
@@ -10128,7 +10245,7 @@
         <f>SUM(C8:C12)</f>
         <v>205.37632600316519</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>224.40000000000003</v>
@@ -10183,7 +10300,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-33.887093790522258</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-24.7</v>
@@ -10239,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10296,7 +10413,7 @@
         <v>171.48923221264295</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10353,8 +10470,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10378,8 +10495,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10404,7 +10521,7 @@
         <v>171.48923221264295</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10500,7 +10617,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10524,7 +10641,7 @@
         <v>-1616.5432662254061</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10581,7 +10698,7 @@
         <v>-293.35540777142882</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10638,7 +10755,7 @@
         <v>-1909.898673996835</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10687,14 +10804,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10706,8 +10823,8 @@
         <v>0.70821811843131843</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10766,8 +10883,8 @@
         <v>0.12852091203760216</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10824,7 +10941,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.83673903046892062</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.83385375401966721</v>
@@ -10872,14 +10989,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10890,8 +11007,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-78.45</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10948,8 +11065,8 @@
         <v>-83.925000000000011</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11007,7 +11124,7 @@
         <v>-162.375</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11056,14 +11173,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11076,7 +11193,7 @@
         <v>3.4369455214562659E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11134,7 +11251,7 @@
         <v>3.6768088322271145E-2</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11190,7 +11307,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>7.1137543536833797E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>7.4381320781097063E-2</v>
@@ -11238,26 +11355,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.16500000000000001</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11336,7 +11453,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11347,7 +11464,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-4.9000000000000004</v>
@@ -11396,111 +11513,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328" t="str">
+      <c r="P48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324" t="str">
+      <c r="P49" s="320" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11514,7 +11631,7 @@
         <f>C47+C48</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-4.9000000000000004</v>
@@ -11562,14 +11679,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11583,8 +11700,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11610,8 +11727,8 @@
         <f>G54</f>
         <v>3.1551835157759174E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11637,7 +11754,7 @@
         <f>-C8/C47</f>
         <v>42.913535919013299</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>40.183673469387756</v>
@@ -11685,14 +11802,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11706,7 +11823,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11761,7 +11878,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11816,7 +11933,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11871,7 +11988,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11922,11 +12039,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11982,7 +12099,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-0.69999999999993179</v>
@@ -12030,14 +12147,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12051,7 +12168,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12076,7 +12193,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12101,7 +12218,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12127,7 +12244,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12155,7 +12272,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12177,7 +12294,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12201,7 +12318,7 @@
         <v>0.83673903046892062</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12258,7 +12375,7 @@
         <v>0.16326096953107935</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12315,7 +12432,7 @@
         <v>7.1137543536833797E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12372,7 +12489,7 @@
         <v>9.2123425994245556E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12429,7 +12546,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12486,8 +12603,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>443</v>
+      <c r="E78" s="296" t="s">
+        <v>453</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12545,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12602,7 +12719,7 @@
         <v>2.1467218680861319E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12659,7 +12776,7 @@
         <v>8.9976704126159421E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12716,7 +12833,7 @@
         <v>1.4846156180816304E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12769,12 +12886,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12831,7 +12948,7 @@
         <v>7.5130547945343115E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12883,26 +13000,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12912,7 +13029,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12938,7 +13055,7 @@
         <v>7.5130547945343115E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -12987,14 +13104,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13006,7 +13123,7 @@
         <f>G90</f>
         <v>5.0790350000000002</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>5.0790350000000002</v>
@@ -13062,7 +13179,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1285.5501453266552</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1285.5501453266552</v>
@@ -13117,7 +13234,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>7.496389882558927</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>6.4374068368886057</v>
@@ -13166,13 +13283,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>9.814560386473431E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>9.814560386473431E-2</v>
@@ -13220,7 +13337,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13229,7 +13346,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13253,7 +13370,7 @@
         <v>6.3778720231160158E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13310,7 +13427,7 @@
         <v>-8.4775730823684725E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13388,7 +13505,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13403,7 +13520,7 @@
         <v>1436.2999999999997</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13460,7 +13577,7 @@
         <v>547.9</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13517,7 +13634,7 @@
         <v>425.2</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13574,7 +13691,7 @@
         <v>809.3</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13631,7 +13748,7 @@
         <v>626.99999999999977</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13680,7 +13797,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13689,7 +13806,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13715,7 +13832,7 @@
         <v>0.24003855337232477</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13772,7 +13889,7 @@
         <v>0.1862828853694333</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13829,7 +13946,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13848,63 +13965,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.1320528211284513</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6005361930294908</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.80833815865663006</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.2139454309224773</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.24278972207656</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.4553415061295971</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.85167232186136688</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.035195530726257</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.1945975744211685</v>
       </c>
-      <c r="P113" s="334" t="str">
+      <c r="P113" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13912,58 +14029,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7786680020030041</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.327404113396333</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.695565520677629</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.0400742115027826</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.98667776852622835</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.4990980156343947</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.86808300395256932</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.035774175517048</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.199889258028793</v>
       </c>
-      <c r="P114" s="334" t="str">
+      <c r="P114" s="329" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13972,7 +14089,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14028,7 +14145,7 @@
         <f>C81</f>
         <v>8.9976704126159421E-2</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.10458125553432449</v>
@@ -14082,7 +14199,7 @@
         <f>C4/C101</f>
         <v>1.5891874956485419</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.4939079579475041</v>
@@ -14137,7 +14254,7 @@
         <v>2.2907496012759174</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14194,7 +14311,7 @@
         <v>0.33536894099388398</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14290,7 +14407,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14315,7 +14432,7 @@
         <v>5.2941578824276201</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14372,7 +14489,7 @@
         <v>0.10230256777637912</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14421,7 +14538,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15172,13 +15289,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15222,7 +15339,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15232,7 +15349,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15250,10 +15367,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15268,8 +15385,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15284,8 +15401,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15300,8 +15417,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15365,7 +15482,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15375,7 +15492,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15385,7 +15502,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16646,7 +16763,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16699,12 +16816,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16717,19 +16834,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-51.75</v>
       </c>
@@ -16746,19 +16863,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>5.0790350000000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>5.0790350000000002</v>
       </c>
@@ -16772,13 +16889,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>70.251496488868511</v>
       </c>
@@ -16795,15 +16912,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16820,12 +16937,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16842,37 +16959,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16886,12 +17003,12 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16904,12 +17021,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16922,8 +17039,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16939,7 +17056,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16949,25 +17066,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -16977,12 +17094,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -16992,8 +17109,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17013,8 +17130,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17024,8 +17141,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17039,8 +17156,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17050,8 +17167,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17071,8 +17188,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17082,8 +17199,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17097,8 +17214,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17108,8 +17225,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17129,8 +17246,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17140,8 +17257,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17155,8 +17272,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17167,8 +17284,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17230,8 +17347,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17241,8 +17358,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17256,8 +17373,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17267,12 +17384,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17288,8 +17405,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17299,8 +17416,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17314,8 +17431,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17325,8 +17442,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17341,16 +17458,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17359,10 +17476,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17374,8 +17491,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17386,8 +17503,8 @@
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17402,23 +17519,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17426,38 +17543,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>-0.13477890212126106</v>
       </c>
@@ -17477,10 +17594,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17501,15 +17618,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17550,7 +17667,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.5117403405568236</v>
       </c>
@@ -17560,14 +17677,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>51.75</v>
       </c>
@@ -17578,9 +17695,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.17134418888864666</v>
       </c>
@@ -17590,15 +17707,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17639,28 +17756,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.2571335053431929</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17672,7 +17789,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17684,23 +17801,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>64.825166953135721</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>5.3288540558208419E-3</v>
       </c>
@@ -17710,15 +17827,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17744,19 +17861,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>58.966734828255284</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>9.5216378389229028E-2</v>
       </c>
@@ -17765,33 +17882,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC04106B-15AE-41C8-B1EA-D9035BA1B001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBF960C-4F9C-4959-AA16-255BA4708BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3833,29 +3833,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8139000000000003</v>
+        <v>7.8137999999999996</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4315,13 +4315,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4393,14 +4393,14 @@
       </c>
       <c r="C26" s="341">
         <f>C127</f>
-        <v>65.172461488868507</v>
+        <v>65.171669755574641</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17134418888864666</v>
+        <v>0.17133897517982155</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="C29" s="339">
         <f>C144</f>
-        <v>31.821083851628465</v>
+        <v>31.820692039203585</v>
       </c>
       <c r="D29" s="339" t="str">
         <f>D144</f>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>48.4144380143915</v>
+        <v>46.53485696680815</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4461,7 +4461,7 @@
         <v>440</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C31" s="148">
         <f>C160</f>
-        <v>64.825166953135721</v>
+        <v>64.824370938416592</v>
       </c>
       <c r="D31" s="148" t="str">
         <f>D160</f>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C32" s="148">
         <f>C168</f>
-        <v>58.966734828255284</v>
+        <v>58.966010525985226</v>
       </c>
       <c r="D32" s="148" t="str">
         <f>D168</f>
@@ -4517,22 +4517,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4544,13 +4544,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4570,13 +4570,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4605,13 +4605,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4697,13 +4697,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4719,7 +4719,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4741,22 +4741,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10230256777637912</v>
+        <v>0.10230125853812708</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.814560386473431E-2</v>
+        <v>9.8144347826086956E-2</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4817,22 +4817,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4876,22 +4876,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>66.176973530345236</v>
+        <v>66.176126616850951</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4928,13 +4928,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4947,13 +4947,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C97" s="248">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.794369352132386</v>
+        <v>4.7943079951998415</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="C104" s="188">
         <f>Valuation_Model!C8</f>
-        <v>-129.61865161029084</v>
+        <v>-129.61728060248709</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="C105" s="248">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.001543404669051</v>
+        <v>-4.0014498693404068</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="C109" s="248">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2039948791575213E-2</v>
+        <v>1.2039794707842486E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5084,13 +5084,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C113" s="248">
         <f>Valuation_Model!C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C114" s="248">
         <f>BS!D47</f>
-        <v>-2.6625266244343737</v>
+        <v>-2.6624925501996839</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5129,13 +5129,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C127" s="241">
         <f>Scenarios!C60</f>
-        <v>65.172461488868507</v>
+        <v>65.171669755574641</v>
       </c>
       <c r="D127" s="236" t="str">
         <f>Market_currency</f>
@@ -5278,13 +5278,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,22 +5297,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C138" s="237">
         <f>Scenarios!C77</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="D138" s="236" t="str">
         <f>Market_currency</f>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="C142" s="240">
         <f>Scenarios!C81</f>
-        <v>8.070186807580173</v>
+        <v>8.0700835276967897</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="C143" s="240">
         <f>Scenarios!C82</f>
-        <v>23.750897044048294</v>
+        <v>23.750608511506798</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="C144" s="239">
         <f>Scenarios!C83</f>
-        <v>31.821083851628465</v>
+        <v>31.820692039203585</v>
       </c>
       <c r="D144" s="336" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.5117403405568236</v>
+        <v>0.51174042097514749</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>10.698893171296296</v>
+        <v>10.413924272385298</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5458,7 +5458,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>37.715544843095202</v>
+        <v>36.120932694422855</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>48.4144380143915</v>
+        <v>46.53485696680815</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.2571335053431929</v>
+        <v>0.28596494241537118</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C158" s="240">
         <f>Scenarios!C97</f>
-        <v>13.089165796626538</v>
+        <v>13.088998285322367</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C159" s="240">
         <f>Scenarios!C98</f>
-        <v>51.736001156509182</v>
+        <v>51.735372653094224</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
-        <v>64.825166953135721</v>
+        <v>64.824370938416592</v>
       </c>
       <c r="D160" s="336" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3288540558208419E-3</v>
+        <v>5.3289844875938908E-3</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C166" s="240">
         <f>Scenarios!C103</f>
-        <v>12.253695717751807</v>
+        <v>12.253538898548621</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C167" s="240">
         <f>Scenarios!C104</f>
-        <v>46.71303911050348</v>
+        <v>46.712471627436607</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
-        <v>58.966734828255284</v>
+        <v>58.966010525985226</v>
       </c>
       <c r="D168" s="336" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>9.5216378389229028E-2</v>
+        <v>9.5216500498555012E-2</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5645,13 +5645,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5688,13 +5688,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5702,22 +5702,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,17 +5741,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5768,6 +5757,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6440,11 +6440,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.610201</v>
+        <v>4.6101419999999997</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7793,11 +7793,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.610201</v>
+        <v>4.6101419999999997</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -9143,11 +9143,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.356533057224759</v>
+        <v>19.356285337992912</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6625266244343737</v>
+        <v>-2.6624925501996839</v>
       </c>
       <c r="F47" s="280"/>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D66" s="188">
         <f>C66-D75</f>
-        <v>-129.61865161029084</v>
+        <v>-129.61728060248709</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9405,11 +9405,11 @@
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-269.52917877722126</v>
+        <v>-269.52780776941751</v>
       </c>
       <c r="D73" s="188">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.81865161029083</v>
+        <v>-279.81728060248707</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>354</v>
@@ -9421,11 +9421,11 @@
       </c>
       <c r="C74" s="285">
         <f>-$C$66/C73</f>
-        <v>0.55726805046271988</v>
+        <v>0.55727088511956768</v>
       </c>
       <c r="D74" s="285">
         <f>-$C$66/D73</f>
-        <v>0.53677622680130199</v>
+        <v>0.53677885681898441</v>
       </c>
       <c r="F74" s="280" t="s">
         <v>322</v>
@@ -9438,7 +9438,7 @@
       <c r="C75" s="289"/>
       <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.81865161029083</v>
+        <v>279.81728060248707</v>
       </c>
       <c r="F75" s="280" t="s">
         <v>355</v>
@@ -9553,11 +9553,11 @@
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
-        <v>-1213.4986700000002</v>
+        <v>-1213.48314</v>
       </c>
       <c r="D86" s="248">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7943693521323869</v>
+        <v>-4.7943079951998415</v>
       </c>
       <c r="E86" s="267" t="str">
         <f>Market_currency</f>
@@ -9570,11 +9570,11 @@
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
-        <v>-1012.8271818176516</v>
+        <v>-1012.8035071717136</v>
       </c>
       <c r="D87" s="248">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-4.001543404669051</v>
+        <v>-4.0014498693404068</v>
       </c>
       <c r="E87" s="267" t="str">
         <f>Market_currency</f>
@@ -9587,11 +9587,11 @@
       </c>
       <c r="C88" s="188">
         <f>Valuation_Model!C9*Exchange_Rate</f>
-        <v>3.0474210000000004</v>
+        <v>3.0473819999999998</v>
       </c>
       <c r="D88" s="248">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2039948791575215E-2</v>
+        <v>1.2039794707842486E-2</v>
       </c>
       <c r="E88" s="267" t="str">
         <f>Market_currency</f>
@@ -9604,11 +9604,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2223.2784308176515</v>
+        <v>-2223.2392651717132</v>
       </c>
       <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
-        <v>-8.783872808009864</v>
+        <v>-8.7837180698324069</v>
       </c>
       <c r="E89" s="267" t="str">
         <f>Market_currency</f>
@@ -13121,16 +13121,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.610201</v>
+        <v>4.6101419999999997</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -13177,16 +13177,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1285.5501453266552</v>
+        <v>1285.5336932330101</v>
       </c>
       <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1285.5501453266552</v>
+        <v>1285.5336932330101</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1166.8839780657329</v>
+        <v>1166.8690446268859</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13232,16 +13232,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.496389882558927</v>
+        <v>7.4962939459602689</v>
       </c>
       <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4374068368886057</v>
+        <v>6.4373244528443143</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4862922627333761</v>
+        <v>6.4862092530677442</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13287,16 +13287,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.814560386473431E-2</v>
+        <v>9.8144347826086956E-2</v>
       </c>
       <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.814560386473431E-2</v>
+        <v>9.8144347826086956E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.9086009661835747E-2</v>
+        <v>8.9084869565217384E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14429,46 +14429,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.2941578824276201</v>
+        <v>5.294090129348076</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1650712145578748</v>
+        <v>6.1649923157849873</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5538122759086628</v>
+        <v>5.5537411998483606</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.195942878126008</v>
+        <v>6.1958635842666263</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.319913331614158</v>
+        <v>8.3198068558039768</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.4153735890676051</v>
+        <v>7.4152786892917044</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.133957651381948</v>
+        <v>5.1338919484979666</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2484247061918534</v>
+        <v>6.2483447406854324</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5229406123405314</v>
+        <v>5.5228699313667233</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5754224404063679</v>
+        <v>5.5753510877855197</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14486,46 +14486,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10230256777637912</v>
+        <v>0.10230125853812708</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11913181090933091</v>
+        <v>0.11913028629536207</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10732004397891136</v>
+        <v>0.10731867052847073</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.11972836479470547</v>
+        <v>0.119726832546215</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16077127210848616</v>
+        <v>0.16076921460490776</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.14329224326700687</v>
+        <v>0.14329040945491217</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>9.9206911137815421E-2</v>
+        <v>9.920564151686892E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.12074250639984258</v>
+        <v>0.12074096117266536</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>0.10672349009353684</v>
+        <v>0.10672212427761785</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>0.10773763169867377</v>
+        <v>0.10773625290406802</v>
       </c>
       <c r="P125" s="77" t="str">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="C8" s="201">
         <f>BS!D66</f>
-        <v>-129.61865161029084</v>
+        <v>-129.61728060248709</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="C10" s="232">
         <f>C6-C7+C8+C9</f>
-        <v>1859.0867510477458</v>
+        <v>1859.0881220555495</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15441,7 +15441,7 @@
       </c>
       <c r="C11" s="231">
         <f>Exchange_Rate</f>
-        <v>7.8139000000000003</v>
+        <v>7.8137999999999996</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>65.172195229703433</v>
+        <v>65.171403499817089</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16444,23 +16444,23 @@
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="H65" s="121"/>
     </row>
@@ -16471,23 +16471,23 @@
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.393100722335362</v>
+        <v>57.392408547018526</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.452886953985441</v>
+        <v>58.452181215835303</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.619731517994339</v>
+        <v>60.618998049203114</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.851917221658169</v>
+        <v>62.851155186009102</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>66.328967716652684</v>
+        <v>66.328161182731378</v>
       </c>
       <c r="H66" s="121"/>
     </row>
@@ -16498,23 +16498,23 @@
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.393100722335362</v>
+        <v>57.392408547018526</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.478766896965489</v>
+        <v>59.47804802990477</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.95920047662166</v>
+        <v>63.958424270286322</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.892785091010253</v>
+        <v>68.891945746106288</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>77.262668672707449</v>
+        <v>77.261722212488678</v>
       </c>
       <c r="H67" s="121"/>
     </row>
@@ -16525,23 +16525,23 @@
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.393100722335362</v>
+        <v>57.392408547018526</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.717012452670573</v>
+        <v>60.716277738906477</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>68.200219134374407</v>
+        <v>68.199388652726384</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.980305059894789</v>
+        <v>76.979362213282741</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>93.159176750808129</v>
+        <v>93.158026851742221</v>
       </c>
       <c r="H68" s="121"/>
     </row>
@@ -16552,23 +16552,23 @@
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.393100722335348</v>
+        <v>57.392408547018512</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.946038434154403</v>
+        <v>61.945287991676324</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.6394858437652</v>
+        <v>72.63859854968409</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.938331253061179</v>
+        <v>85.937273764257711</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>112.4332879662927</v>
+        <v>112.43189140280549</v>
       </c>
       <c r="H69" s="121"/>
     </row>
@@ -16579,23 +16579,23 @@
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.393100722335348</v>
+        <v>57.392408547018512</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>63.058810926613575</v>
+        <v>63.058046243199584</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.885987559507413</v>
+        <v>76.885045919943039</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>95.035035083467974</v>
+        <v>95.033861177717426</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>134.00613912332921</v>
+        <v>134.00446647682128</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16605,23 +16605,23 @@
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.393100722335348</v>
+        <v>57.392408547018512</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>64.013795435165676</v>
+        <v>64.013018530140087</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.742755561667281</v>
+        <v>80.741764564317407</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.83196508766028</v>
+        <v>103.8306786013801</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>157.14347405893642</v>
+        <v>157.1415053076033</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>93.159176750808129</v>
+        <v>93.158026851742221</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
@@ -16678,7 +16678,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.892785091010253</v>
+        <v>68.891945746106288</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16701,7 +16701,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.95920047662166</v>
+        <v>63.958424270286322</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16724,7 +16724,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.478766896965489</v>
+        <v>59.47804802990477</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.393100722335362</v>
+        <v>57.392408547018526</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="I5" s="262">
         <f t="shared" si="0"/>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="I6" s="262">
         <f t="shared" si="0"/>
-        <v>70.251496488868511</v>
+        <v>70.250639755574639</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
-        <v>57.393100722335376</v>
+        <v>57.39240854701854</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C27" s="161">
         <f>Valuation_Model!E76</f>
-        <v>63.95920047662166</v>
+        <v>63.958424270286322</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="C33" s="161">
         <f>Valuation_Model!E77</f>
-        <v>59.478766896965489</v>
+        <v>59.47804802990477</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="C39" s="161">
         <f>Valuation_Model!E75</f>
-        <v>68.892785091010253</v>
+        <v>68.891945746106288</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>64.049830683568146</v>
+        <v>64.049053317374003</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -17367,7 +17367,7 @@
       </c>
       <c r="C51" s="161">
         <f>Valuation_Model!E78</f>
-        <v>57.393100722335362</v>
+        <v>57.392408547018526</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="C57" s="161">
         <f>Valuation_Model!E74</f>
-        <v>93.159176750808129</v>
+        <v>93.158026851742221</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>65.172461488868507</v>
+        <v>65.171669755574641</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -17513,7 +17513,7 @@
       </c>
       <c r="C66" s="161">
         <f>Valuation_Model!C18</f>
-        <v>65.172195229703433</v>
+        <v>65.171403499817089</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -17576,7 +17576,7 @@
       </c>
       <c r="F72" s="325">
         <f>BS!D89/C60</f>
-        <v>-0.13477890212126106</v>
+        <v>-0.13477816515635718</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="C77" s="174">
         <f>Normalized_FCF!C90</f>
-        <v>5.0790350000000002</v>
+        <v>5.07897</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.070186807580173</v>
+        <v>8.0700835276967897</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>23.750897044048294</v>
+        <v>23.750608511506798</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17658,7 +17658,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>31.821083851628465</v>
+        <v>31.820692039203585</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="F83" s="325">
         <f>(1-C83/C60)</f>
-        <v>0.5117403405568236</v>
+        <v>0.51174042097514749</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17134418888864666</v>
+        <v>0.17133897517982155</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -17716,7 +17716,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>10.698893171296296</v>
+        <v>10.413924272385298</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>37.715544843095202</v>
+        <v>36.120932694422855</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>48.4144380143915</v>
+        <v>46.53485696680815</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17758,7 +17758,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.2571335053431929</v>
+        <v>0.28596494241537118</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -17785,7 +17785,7 @@
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.089165796626538</v>
+        <v>13.088998285322367</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.736001156509182</v>
+        <v>51.735372653094224</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
@@ -17809,7 +17809,7 @@
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.825166953135721</v>
+        <v>64.824370938416592</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -17819,7 +17819,7 @@
       </c>
       <c r="F99" s="325">
         <f>(1-C99/C60)</f>
-        <v>5.3288540558208419E-3</v>
+        <v>5.3289844875938908E-3</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -17845,7 +17845,7 @@
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>12.253695717751807</v>
+        <v>12.253538898548621</v>
       </c>
       <c r="D103" s="117"/>
     </row>
@@ -17855,7 +17855,7 @@
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>46.71303911050348</v>
+        <v>46.712471627436607</v>
       </c>
       <c r="D104" s="117"/>
     </row>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>58.966734828255284</v>
+        <v>58.966010525985226</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -17875,7 +17875,7 @@
       </c>
       <c r="F105" s="325">
         <f>(1-C105/C66)</f>
-        <v>9.5216378389229028E-2</v>
+        <v>9.5216500498555012E-2</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBF960C-4F9C-4959-AA16-255BA4708BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C93508-099F-4A89-BFE6-154519C2A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3114,7 +3114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3748,7 +3748,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3812,9 +3811,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3833,29 +3829,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4163,7 +4169,7 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4197,7 +4203,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>445</v>
       </c>
     </row>
@@ -4350,7 +4356,7 @@
       <c r="D22" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>442</v>
       </c>
     </row>
@@ -4381,7 +4387,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4391,14 +4397,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>65.171669755574641</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>0.17133897517982155</v>
       </c>
@@ -4411,18 +4417,18 @@
       <c r="B28" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0303.HK (HKD)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4430,18 +4436,18 @@
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>31.820692039203585</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>427</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4449,18 +4455,18 @@
       <c r="B30" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>46.53485696680815</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4468,18 +4474,18 @@
       <c r="B31" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>64.824370938416592</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>439</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4487,18 +4493,18 @@
       <c r="B32" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>58.966010525985226</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4526,13 +4532,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4639,7 +4645,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4647,14 +4653,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-4.9000000000000004</v>
       </c>
@@ -4662,8 +4668,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4722,10 +4728,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4826,13 +4832,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4870,7 +4876,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4982,28 +4988,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
@@ -5106,7 +5112,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5278,13 +5284,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5297,13 +5303,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5367,7 +5373,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5400,7 +5406,7 @@
         <f>Scenarios!C83</f>
         <v>31.820692039203585</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5409,11 +5415,11 @@
       <c r="B145" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5436,7 +5442,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5469,7 +5475,7 @@
         <f>Scenarios!C93</f>
         <v>46.53485696680815</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5478,11 +5484,11 @@
       <c r="B153" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5538,7 +5544,7 @@
         <f>Scenarios!C99</f>
         <v>64.824370938416592</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5547,11 +5553,11 @@
       <c r="B161" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5607,7 +5613,7 @@
         <f>Scenarios!C105</f>
         <v>58.966010525985226</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5616,11 +5622,11 @@
       <c r="B169" s="286" t="s">
         <v>419</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5645,7 +5651,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5659,13 +5665,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5702,22 +5708,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5741,6 +5747,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5757,17 +5774,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8188,11 +8194,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8222,11 +8228,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9449,7 +9455,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -11520,104 +11526,104 @@
         <v>0</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324" t="str">
+      <c r="P48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320" t="str">
+      <c r="P49" s="319" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -13981,47 +13987,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.1320528211284513</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6005361930294908</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.80833815865663006</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.2139454309224773</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.24278972207656</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.4553415061295971</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.85167232186136688</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.035195530726257</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.1945975744211685</v>
       </c>
-      <c r="P113" s="329" t="str">
+      <c r="P113" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14033,47 +14039,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7786680020030041</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.327404113396333</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.695565520677629</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.0400742115027826</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.98667776852622835</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.4990980156343947</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.86808300395256932</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.035774175517048</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.199889258028793</v>
       </c>
-      <c r="P114" s="329" t="str">
+      <c r="P114" s="328" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15367,10 +15373,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15385,8 +15391,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15401,8 +15407,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15417,8 +15423,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16912,11 +16918,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16937,8 +16943,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16959,8 +16965,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16970,8 +16976,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -16984,8 +16990,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17003,8 +17009,8 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17021,8 +17027,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17039,8 +17045,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17066,21 +17072,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17094,8 +17100,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17109,8 +17115,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17130,8 +17136,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17141,8 +17147,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17156,8 +17162,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17167,8 +17173,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17188,8 +17194,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17199,8 +17205,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17214,8 +17220,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17225,8 +17231,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17246,8 +17252,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17257,8 +17263,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17272,8 +17278,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17284,8 +17290,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17347,8 +17353,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17358,8 +17364,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17373,8 +17379,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17384,8 +17390,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17405,8 +17411,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17416,8 +17422,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17431,8 +17437,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17442,8 +17448,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17460,7 +17466,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17574,7 +17580,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-0.13477816515635718</v>
       </c>
@@ -17667,7 +17673,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.51174042097514749</v>
       </c>
@@ -17756,7 +17762,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.28596494241537118</v>
       </c>
@@ -17766,7 +17772,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17777,7 +17783,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17789,7 +17795,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17801,7 +17807,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17817,7 +17823,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>5.3289844875938908E-3</v>
       </c>
@@ -17873,7 +17879,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>9.5216500498555012E-2</v>
       </c>
@@ -17882,32 +17888,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C93508-099F-4A89-BFE6-154519C2A2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7AD53-7610-4438-AB9C-EED3CC9DEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4912,7 +4912,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>66.176126616850951</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4966,7 +4966,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>155.30000000000001</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5037,7 +5037,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>-129.61728060248709</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5068,7 +5068,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>0.39</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5103,7 +5103,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>57.39240854701854</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5162,111 +5162,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.08</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>93.16 HKD</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.05</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>68.89 HKD</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.03</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>63.96 HKD</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.01</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>59.48 HKD</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.39 HKD</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-1213.48314</v>
       </c>
       <c r="D86" s="248">
@@ -9575,7 +9575,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>-1012.8035071717136</v>
       </c>
       <c r="D87" s="248">
@@ -9592,7 +9592,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>3.0473819999999998</v>
       </c>
       <c r="D88" s="248">
@@ -15552,7 +15552,7 @@
         <v>177.50852070282099</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15574,7 +15574,7 @@
         <v>183.73908679603281</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15596,7 +15596,7 @@
         <v>190.18834635639865</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15618,7 +15618,7 @@
         <v>196.86397554558027</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15640,7 +15640,7 @@
         <v>203.77391995924967</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15662,7 +15662,7 @@
         <v>210.92640408424856</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15684,7 +15684,7 @@
         <v>218.3299410876952</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15706,7 +15706,7 @@
         <v>225.99334294968995</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15728,7 +15728,7 @@
         <v>233.9257309516793</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15750,7 +15750,7 @@
         <v>242.13654653296291</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15772,7 +15772,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15794,7 +15794,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15816,7 +15816,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15838,7 +15838,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15860,7 +15860,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15882,7 +15882,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15904,7 +15904,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15926,7 +15926,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15948,7 +15948,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -15992,7 +15992,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16014,7 +16014,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16036,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16058,7 +16058,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16080,7 +16080,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16102,7 +16102,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16124,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16146,7 +16146,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16168,7 +16168,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16190,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16891,7 +16891,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17108,7 +17108,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>57.39240854701854</v>
       </c>
       <c r="D22" t="str">
@@ -17155,7 +17155,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>63.958424270286322</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17213,7 +17213,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>59.47804802990477</v>
       </c>
       <c r="D33" t="str">
@@ -17271,7 +17271,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>68.891945746106288</v>
       </c>
       <c r="D39" t="str">
@@ -17372,7 +17372,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>57.392408547018526</v>
       </c>
       <c r="D51" t="str">
@@ -17430,7 +17430,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>93.158026851742221</v>
       </c>
       <c r="D57" t="str">
@@ -17518,7 +17518,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>65.171403499817089</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B7AD53-7610-4438-AB9C-EED3CC9DEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2F1050-5518-41B4-B4BE-7657107324F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2F1050-5518-41B4-B4BE-7657107324F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54F9C7D-659E-49B4-9622-4A20736E342D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="462">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2407,31 +2402,61 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>偉易達</t>
+  </si>
+  <si>
+    <t>0303.HK</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_02</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>偉易達</t>
-  </si>
-  <si>
-    <t>0303.HK</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_02</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>USD</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2447,7 +2472,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2466,6 +2491,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3114,7 +3140,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3620,9 +3646,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3839,29 +3862,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3880,7 +3910,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3927,8 +3971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4169,15 +4213,15 @@
         <v>45754</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>444</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4192,7 +4236,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4201,10 +4245,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>445</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4218,9 +4262,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4241,20 +4285,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4270,17 +4314,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4294,7 +4338,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4321,73 +4365,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>448</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>442</v>
-      </c>
+        <v>455</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>449</v>
+        <v>435</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>449</v>
+        <v>436</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4397,14 +4445,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>65.171669755574641</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>0.17133897517982155</v>
       </c>
@@ -4415,96 +4463,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>436</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>434</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>0303.HK (HKD)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>432</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>430</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C29" s="345">
+        <v>426</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>31.820692039203585</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>427</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>425</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C30" s="346">
+        <v>427</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>46.53485696680815</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C31" s="346">
+        <v>428</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>64.824370938416592</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>437</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C32" s="346">
+        <v>429</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>58.966010525985226</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4513,8 +4561,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4523,22 +4571,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4550,13 +4598,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4576,13 +4624,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4611,13 +4659,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4633,19 +4681,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>0</v>
       </c>
@@ -4653,14 +4701,14 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-4.9000000000000004</v>
       </c>
@@ -4668,8 +4716,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4703,13 +4751,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4725,13 +4773,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4747,22 +4795,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4791,26 +4839,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>0.10230125853812708</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>9.8144347826086956E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>449</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>7.4962939459602689</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4823,22 +4879,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4847,7 +4903,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4856,7 +4912,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4867,7 +4923,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4876,42 +4932,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>66.176126616850951</v>
       </c>
@@ -4921,8 +4977,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4934,13 +4990,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4953,13 +5009,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4976,9 +5032,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>4.7943079951998415</v>
       </c>
@@ -4988,28 +5044,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>1.2907496012759174</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>0.24768740031897937</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>0.73855199466278643</v>
       </c>
@@ -5047,9 +5103,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>-4.0014498693404068</v>
       </c>
@@ -5078,9 +5134,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>1.2039794707842486E-2</v>
       </c>
@@ -5090,20 +5146,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>450</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>57.39240854701854</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5112,10 +5168,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-2.6624925501996839</v>
       </c>
@@ -5125,8 +5181,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5135,49 +5191,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.08</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>93.16 HKD</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5195,11 +5251,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>68.89 HKD</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5217,11 +5273,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>63.96 HKD</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5239,11 +5295,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>59.48 HKD</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5261,11 +5317,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>57.39 HKD</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5284,17 +5340,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5303,22 +5359,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5329,7 +5385,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5338,7 +5394,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5358,22 +5414,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>0303.HK</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5406,20 +5462,20 @@
         <f>Scenarios!C83</f>
         <v>31.820692039203585</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5435,14 +5491,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5475,20 +5531,20 @@
         <f>Scenarios!C93</f>
         <v>46.53485696680815</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5504,12 +5560,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5538,26 +5594,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>64.824370938416592</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5573,12 +5629,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5607,26 +5663,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>58.966010525985226</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>419</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5641,8 +5697,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5651,113 +5707,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5774,6 +5819,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5786,7 +5842,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6339,7 +6395,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>355.2</v>
@@ -6373,7 +6429,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-54.4</v>
@@ -6407,7 +6463,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-171.1</v>
@@ -6467,7 +6523,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7746,7 +7802,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8194,11 +8250,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8228,11 +8284,11 @@
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8335,17 +8391,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8429,7 +8485,7 @@
       <c r="C4" s="19">
         <v>547.9</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8439,7 +8495,7 @@
       <c r="G4" s="19">
         <v>150.19999999999999</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8450,7 +8506,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8460,7 +8516,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8471,7 +8527,7 @@
       <c r="C6" s="19">
         <v>425.2</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8481,7 +8537,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8492,7 +8548,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8502,7 +8558,7 @@
       <c r="G7" s="19">
         <v>0</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8513,7 +8569,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8523,7 +8579,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8534,7 +8590,7 @@
       <c r="C9" s="19">
         <v>0</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8544,7 +8600,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8555,10 +8611,10 @@
       <c r="C10" s="19">
         <v>5.9</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8567,10 +8623,10 @@
       <c r="C11" s="19">
         <v>0</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8628,7 +8684,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8637,7 +8693,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8649,7 +8705,7 @@
         <f>1.2+6.2</f>
         <v>7.4</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8658,7 +8714,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8669,7 +8725,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8678,7 +8734,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8689,7 +8745,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8698,7 +8754,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8710,7 +8766,7 @@
         <f>97.3+136.4+14.3</f>
         <v>248</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8719,7 +8775,7 @@
       <c r="G19" s="19">
         <v>3.9</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8730,7 +8786,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8739,7 +8795,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8750,7 +8806,7 @@
       <c r="C21" s="19">
         <v>36.1</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8759,7 +8815,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8770,10 +8826,10 @@
       <c r="C22" s="19">
         <v>11.7</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8782,10 +8838,10 @@
       <c r="C23" s="19">
         <v>0</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9118,13 +9174,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9140,7 +9196,7 @@
         <f>H29</f>
         <v>-86.245000000000118</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9155,23 +9211,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-2.6624925501996839</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9185,7 +9241,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>0.78872524123920762</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9196,22 +9252,22 @@
         <f>G29/G32</f>
         <v>0.43653832764742734</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9225,7 +9281,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.15356418655435974</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9239,22 +9295,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9276,22 +9332,22 @@
         <f>G39/G32</f>
         <v>0.17266587760217228</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9305,7 +9361,7 @@
         <f>G28/G29</f>
         <v>0</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9324,13 +9380,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9358,7 +9414,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9368,7 +9424,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9378,7 +9434,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9388,26 +9444,26 @@
         <f>SUM(C66:C69)</f>
         <v>150.19999999999999</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9418,65 +9474,65 @@
         <v>-279.81728060248707</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>0.55727088511956768</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>0.53677885681898441</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>279.81728060248707</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9490,7 +9546,7 @@
         <f>G7*H7+G17*H17</f>
         <v>0</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9504,7 +9560,7 @@
         <f>G19*H19</f>
         <v>0.39</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9518,7 +9574,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9532,11 +9588,11 @@
         <f>SUM(D79:D81)</f>
         <v>0.39</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9547,76 +9603,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-1213.48314</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-4.7943079951998415</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>-1012.8035071717136</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>-4.0014498693404068</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>3.0473819999999998</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>1.2039794707842486E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-2223.2392651717132</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-8.7837180698324069</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
@@ -9737,7 +9793,7 @@
         <v>1000000</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9751,7 +9807,7 @@
         <v>2282.5500000000002</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9807,7 +9863,7 @@
         <f>C25</f>
         <v>-1909.898673996835</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1789.1999999999998</v>
@@ -9862,7 +9918,7 @@
         <f>C4+C5</f>
         <v>372.6513260031652</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>356.5</v>
@@ -9917,7 +9973,7 @@
         <f>C35</f>
         <v>-162.375</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-159.59999999999997</v>
@@ -9973,7 +10029,7 @@
         <v>210.2763260031652</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10029,7 +10085,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>0</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>0</v>
@@ -10084,7 +10140,7 @@
         <f>-C4*C78</f>
         <v>0</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>32.4</v>
@@ -10140,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10196,7 +10252,7 @@
         <f>C50</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>-4.9000000000000004</v>
@@ -10251,7 +10307,7 @@
         <f>SUM(C8:C12)</f>
         <v>205.37632600316519</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>224.40000000000003</v>
@@ -10306,7 +10362,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-33.887093790522258</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-24.7</v>
@@ -10362,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10419,7 +10475,7 @@
         <v>171.48923221264295</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10476,8 +10532,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10501,8 +10557,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10527,7 +10583,7 @@
         <v>171.48923221264295</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10623,7 +10679,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10647,7 +10703,7 @@
         <v>-1616.5432662254061</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10704,7 +10760,7 @@
         <v>-293.35540777142882</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10761,7 +10817,7 @@
         <v>-1909.898673996835</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10810,14 +10866,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10829,8 +10885,8 @@
         <v>0.70821811843131843</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10889,8 +10945,8 @@
         <v>0.12852091203760216</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10947,7 +11003,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.83673903046892062</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.83385375401966721</v>
@@ -10995,14 +11051,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11013,8 +11069,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-78.45</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11071,8 +11127,8 @@
         <v>-83.925000000000011</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11130,7 +11186,7 @@
         <v>-162.375</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11179,14 +11235,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11199,7 +11255,7 @@
         <v>3.4369455214562659E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11257,7 +11313,7 @@
         <v>3.6768088322271145E-2</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11313,7 +11369,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>7.1137543536833797E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>7.4381320781097063E-2</v>
@@ -11361,26 +11417,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.16500000000000001</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11459,7 +11515,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11470,7 +11526,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-4.9000000000000004</v>
@@ -11519,111 +11575,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>0</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323" t="str">
+      <c r="P48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>0</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>0</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>0</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>0</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>0</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>0</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>0</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>0</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319" t="str">
+      <c r="P49" s="318" t="str">
         <f>Data!L52</f>
         <v/>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11637,7 +11693,7 @@
         <f>C47+C48</f>
         <v>-4.9000000000000004</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>-4.9000000000000004</v>
@@ -11685,14 +11741,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11706,8 +11762,8 @@
         <f>G53</f>
         <v>0</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11733,8 +11789,8 @@
         <f>G54</f>
         <v>3.1551835157759174E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11760,7 +11816,7 @@
         <f>-C8/C47</f>
         <v>42.913535919013299</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>40.183673469387756</v>
@@ -11808,14 +11864,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11829,7 +11885,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11884,7 +11940,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11939,7 +11995,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11994,7 +12050,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -12045,11 +12101,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12105,7 +12161,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-0.69999999999993179</v>
@@ -12153,14 +12209,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12174,7 +12230,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12199,7 +12255,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12224,7 +12280,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12250,7 +12306,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12278,7 +12334,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12300,7 +12356,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12324,7 +12380,7 @@
         <v>0.83673903046892062</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12381,7 +12437,7 @@
         <v>0.16326096953107935</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12438,7 +12494,7 @@
         <v>7.1137543536833797E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12495,7 +12551,7 @@
         <v>9.2123425994245556E-2</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12552,7 +12608,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12609,8 +12665,8 @@
         <v>0</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>453</v>
+      <c r="E78" s="295" t="s">
+        <v>461</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12668,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12725,7 +12781,7 @@
         <v>2.1467218680861319E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12782,7 +12838,7 @@
         <v>8.9976704126159421E-2</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12839,7 +12895,7 @@
         <v>1.4846156180816304E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12892,12 +12948,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>0</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12954,7 +13010,7 @@
         <v>7.5130547945343115E-2</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13006,26 +13062,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13035,7 +13091,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13061,7 +13117,7 @@
         <v>7.5130547945343115E-2</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13110,14 +13166,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13129,7 +13185,7 @@
         <f>G90</f>
         <v>5.07897</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>5.07897</v>
@@ -13185,7 +13241,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1285.5336932330101</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1285.5336932330101</v>
@@ -13240,7 +13296,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>7.4962939459602689</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>6.4373244528443143</v>
@@ -13289,13 +13345,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>9.8144347826086956E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>9.8144347826086956E-2</v>
@@ -13343,7 +13399,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13352,7 +13408,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13376,7 +13432,7 @@
         <v>6.3778720231160158E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13433,7 +13489,7 @@
         <v>-8.4775730823684725E-2</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13511,7 +13567,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13526,7 +13582,7 @@
         <v>1436.2999999999997</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13583,7 +13639,7 @@
         <v>547.9</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13640,7 +13696,7 @@
         <v>425.2</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13697,7 +13753,7 @@
         <v>809.3</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13754,7 +13810,7 @@
         <v>626.99999999999977</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13803,7 +13859,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13812,7 +13868,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13838,7 +13894,7 @@
         <v>0.24003855337232477</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13895,7 +13951,7 @@
         <v>0.1862828853694333</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13952,7 +14008,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13971,63 +14027,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>2.1320528211284513</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.6005361930294908</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>0.80833815865663006</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.2139454309224773</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>1.24278972207656</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>1.4553415061295971</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>0.85167232186136688</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>1.035195530726257</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>1.1945975744211685</v>
       </c>
-      <c r="P113" s="328" t="str">
+      <c r="P113" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v/>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14035,58 +14091,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.7786680020030041</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.327404113396333</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.695565520677629</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.0400742115027826</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.98667776852622835</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.4990980156343947</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.86808300395256932</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>1.035774175517048</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.199889258028793</v>
       </c>
-      <c r="P114" s="328" t="str">
+      <c r="P114" s="327" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14095,7 +14151,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14151,7 +14207,7 @@
         <f>C81</f>
         <v>8.9976704126159421E-2</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.10458125553432449</v>
@@ -14205,7 +14261,7 @@
         <f>C4/C101</f>
         <v>1.5891874956485419</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.4939079579475041</v>
@@ -14260,7 +14316,7 @@
         <v>2.2907496012759174</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14317,7 +14373,7 @@
         <v>0.33536894099388398</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14413,7 +14469,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14438,7 +14494,7 @@
         <v>5.294090129348076</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14495,7 +14551,7 @@
         <v>0.10230125853812708</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14544,7 +14600,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15277,7 +15333,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15345,7 +15401,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15355,7 +15411,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15373,10 +15429,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15391,8 +15447,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15407,8 +15463,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15423,8 +15479,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16769,7 +16825,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16800,12 +16856,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16820,6 +16876,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>443</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1000000</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>441</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>1285.5336932330101</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>442</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>16069.171165412627</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>USD</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>70.950028167513793</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>HKD</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>447</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>446</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>1330.6560491009202</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>1232.0889343527037</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>1377.3622039853694</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>1180.8660870930808</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>1425.7077493836662</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>1131.7727777330581</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>1475.750228060004</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>1084.720472895277</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>1527.5492025351159</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>1039.6243198877091</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>1581.166325979922</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>996.40299368289664</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>1636.6654155975521</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>954.9785502588802</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>1694.1125285810838</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>915.27628603732364</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>1753.5760407374044</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>877.22460316535989</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>1815.1267278707771</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>3.5100095863245001E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>840.7548803982047</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>16633.200613761503</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>7704.3902103005012</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>17958.100115804995</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>17958.100115804995</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.01</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.03</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.05</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.08</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>16069.171165412623</v>
+      </c>
+      <c r="C51" s="124">
+        <v>16326.509714558026</v>
+      </c>
+      <c r="D51" s="124">
+        <v>16852.665480383981</v>
+      </c>
+      <c r="E51" s="124">
+        <v>17394.68745920284</v>
+      </c>
+      <c r="F51" s="124">
+        <v>18238.988982439303</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>16069.171165412619</v>
+      </c>
+      <c r="C52" s="124">
+        <v>16575.615098492679</v>
+      </c>
+      <c r="D52" s="124">
+        <v>17663.559291856909</v>
+      </c>
+      <c r="E52" s="124">
+        <v>18861.538156685227</v>
+      </c>
+      <c r="F52" s="124">
+        <v>20893.923210486391</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>16069.171165412616</v>
+      </c>
+      <c r="C53" s="124">
+        <v>16876.287352268573</v>
+      </c>
+      <c r="D53" s="124">
+        <v>18693.36847005826</v>
+      </c>
+      <c r="E53" s="124">
+        <v>20825.359343281278</v>
+      </c>
+      <c r="F53" s="124">
+        <v>24753.932147314415</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>16069.171165412617</v>
+      </c>
+      <c r="C54" s="124">
+        <v>17174.720898102252</v>
+      </c>
+      <c r="D54" s="124">
+        <v>19771.316475181346</v>
+      </c>
+      <c r="E54" s="124">
+        <v>23000.557883242211</v>
+      </c>
+      <c r="F54" s="124">
+        <v>29434.094682109095</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>16069.171165412617</v>
+      </c>
+      <c r="C55" s="124">
+        <v>17444.925633912513</v>
+      </c>
+      <c r="D55" s="124">
+        <v>20802.457056023864</v>
+      </c>
+      <c r="E55" s="124">
+        <v>25209.430291480145</v>
+      </c>
+      <c r="F55" s="124">
+        <v>34672.439974666646</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>16069.171165412619</v>
+      </c>
+      <c r="C56" s="124">
+        <v>17676.816104412868</v>
+      </c>
+      <c r="D56" s="124">
+        <v>21738.962034505166</v>
+      </c>
+      <c r="E56" s="124">
+        <v>27345.511263854925</v>
+      </c>
+      <c r="F56" s="124">
+        <v>40290.675073031583</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.01</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.03</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.05</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.08</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>496.07569732500002</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>496.07569732499985</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>504.02006476634534</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>520.26316067632513</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>536.99606670739593</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>563.06072571069262</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>496.07569732499974</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>511.71026395401583</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>545.29648124041228</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>582.27960841186643</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>645.0219130658495</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>496.07569732499962</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>520.99239782531345</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>577.08799686553084</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>642.90525951322047</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>764.18528529622574</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>496.07569732499974</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>530.20541994267489</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>610.36561914094182</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>710.05639764124192</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>908.66783944561985</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>496.07569732499974</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>538.5469828868861</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>642.19823685445306</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>778.24709079765819</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>1070.3822033717379</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>496.07569732499974</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>545.7057358600382</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>671.1093334795487</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>844.19061999437861</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>1243.8242474863764</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.08</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>764.18528529622574</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.05</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>582.27960841186643</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.03</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>545.29648124041228</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.01</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>511.71026395401583</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>496.07569732499962</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16840,19 +18347,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-51.75</v>
       </c>
@@ -16869,19 +18376,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>5.07897</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>5.07897</v>
       </c>
@@ -16895,13 +18402,13 @@
         <v>1000000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>70.250639755574639</v>
       </c>
@@ -16918,15 +18425,15 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16943,12 +18450,12 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16965,37 +18472,37 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>448</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17009,12 +18516,12 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17027,12 +18534,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17045,8 +18552,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17062,7 +18569,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17072,25 +18579,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17100,23 +18607,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>57.39240854701854</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17136,8 +18643,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17147,23 +18654,23 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>63.958424270286322</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17173,8 +18680,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17194,8 +18701,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17205,23 +18712,23 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>59.47804802990477</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17231,8 +18738,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17252,8 +18759,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17263,23 +18770,23 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>68.891945746106288</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17290,8 +18797,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17353,8 +18860,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17364,23 +18871,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>57.392408547018526</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17390,12 +18897,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17411,8 +18918,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17422,23 +18929,23 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>93.158026851742221</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17448,8 +18955,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17464,16 +18971,16 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17482,10 +18989,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17497,8 +19004,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17509,8 +19016,8 @@
         <v>3.5100095863245001E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17518,30 +19025,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>65.171403499817089</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17549,38 +19056,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>-0.13477816515635718</v>
       </c>
@@ -17600,10 +19107,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17624,12 +19131,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17673,7 +19180,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.51174042097514749</v>
       </c>
@@ -17683,14 +19190,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>51.75</v>
       </c>
@@ -17701,9 +19208,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>0.17133897517982155</v>
       </c>
@@ -17713,12 +19220,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17762,28 +19269,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.28596494241537118</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17795,7 +19302,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17807,23 +19314,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>64.824370938416592</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>5.3289844875938908E-3</v>
       </c>
@@ -17833,12 +19340,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17867,19 +19374,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>58.966010525985226</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>9.5216500498555012E-2</v>
       </c>
@@ -17888,33 +19395,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26102915-77DD-5C45-ADC6-F88E6D57D66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E61DEB-7244-E04A-88B5-886F8D00E16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="1480" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3877,6 +3877,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3912,9 +3915,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4223,7 +4223,7 @@
       <c r="C1" s="44">
         <v>45754</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>462</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4378,13 +4378,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4584,22 +4584,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4611,13 +4611,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4637,13 +4637,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4672,13 +4672,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4764,13 +4764,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4786,13 +4786,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4808,22 +4808,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4892,22 +4892,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4951,22 +4951,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5003,13 +5003,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5022,13 +5022,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5159,13 +5159,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5204,13 +5204,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5353,13 +5353,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5372,22 +5372,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5720,13 +5720,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5763,13 +5763,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5777,22 +5777,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15442,10 +15442,10 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15460,8 +15460,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15476,8 +15476,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15492,8 +15492,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16972,8 +16972,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18438,11 +18438,11 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 偉易達(0303.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18463,8 +18463,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18485,8 +18485,8 @@
         <f>Reporting_currency</f>
         <v>USD</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18496,8 +18496,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18510,8 +18510,8 @@
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18529,8 +18529,8 @@
         <v>-3.2910954099016121E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18547,8 +18547,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.0823625892916704E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18565,8 +18565,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-9.5087824202677584E-2</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18592,21 +18592,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18620,8 +18620,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18635,8 +18635,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18656,8 +18656,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18667,8 +18667,8 @@
         <v>0.03</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18682,8 +18682,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18693,8 +18693,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18714,8 +18714,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18725,8 +18725,8 @@
         <v>0.01</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18740,8 +18740,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18751,8 +18751,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18772,8 +18772,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18783,8 +18783,8 @@
         <v>0.05</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18798,8 +18798,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18810,8 +18810,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18873,8 +18873,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18884,8 +18884,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18899,8 +18899,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18910,8 +18910,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18931,8 +18931,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18942,8 +18942,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18957,8 +18957,8 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18968,8 +18968,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E61DEB-7244-E04A-88B5-886F8D00E16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F899AD9-6C97-4869-913C-D31B8B40B7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="1480" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2505,7 +2494,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3918,7 +3907,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4207,7 +4196,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4216,7 +4205,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4233,7 +4222,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4247,7 +4236,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>416</v>
       </c>
@@ -4256,7 +4245,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4264,7 +4253,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4273,7 +4262,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4283,7 +4272,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4293,17 +4282,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>419</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>418</v>
       </c>
@@ -4315,7 +4304,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4325,7 +4314,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>417</v>
       </c>
@@ -4335,7 +4324,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>421</v>
       </c>
@@ -4349,7 +4338,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>420</v>
       </c>
@@ -4363,7 +4352,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4373,11 +4362,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4386,14 +4375,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4408,7 +4397,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4421,7 +4410,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>435</v>
       </c>
@@ -4429,7 +4418,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>436</v>
       </c>
@@ -4437,7 +4426,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4453,28 +4442,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>65.171669755574641</v>
+        <v>69.934431264803422</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17133897517982155</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.19512134426713557</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>434</v>
       </c>
@@ -4493,13 +4482,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>426</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>31.820692039203585</v>
+        <v>35.770129754280603</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4509,16 +4498,16 @@
         <v>425</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>46.53485696680815</v>
+        <v>49.174583531428283</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4531,13 +4520,13 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>64.824370938416592</v>
+        <v>69.502451836283839</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4547,16 +4536,16 @@
         <v>437</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>58.966010525985226</v>
+        <v>62.379769337175816</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4569,11 +4558,11 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4583,7 +4572,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4592,7 +4581,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4601,7 +4590,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4610,7 +4599,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4619,7 +4608,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4632,11 +4621,11 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4645,7 +4634,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4658,7 +4647,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4671,7 +4660,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4680,7 +4669,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4693,7 +4682,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4702,7 +4691,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4717,7 +4706,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4732,7 +4721,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4745,12 +4734,12 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4763,7 +4752,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4772,7 +4761,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4785,7 +4774,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4794,7 +4783,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4807,7 +4796,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4816,7 +4805,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4825,7 +4814,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4838,7 +4827,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4851,7 +4840,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4861,7 +4850,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4877,7 +4866,7 @@
         <v>7.4962939459602689</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4887,10 +4876,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4900,7 +4889,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4909,21 +4898,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>432</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>431</v>
       </c>
@@ -4932,25 +4921,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4959,7 +4948,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4968,7 +4957,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4976,20 +4965,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>66.176126616850951</v>
+        <v>70.587868391307694</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4999,10 +4988,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5011,17 +5000,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5030,7 +5019,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5043,7 +5032,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5056,7 +5045,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5065,7 +5054,7 @@
         <v>1.2907496012759174</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5074,7 +5063,7 @@
         <v>0.24768740031897937</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5083,12 +5072,12 @@
         <v>0.73855199466278643</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5101,7 +5090,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5114,7 +5103,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5127,12 +5116,12 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5145,7 +5134,7 @@
         <v>USD</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5158,7 +5147,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5167,20 +5156,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>450</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5203,7 +5192,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5212,7 +5201,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5229,7 +5218,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5244,14 +5233,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>93.16 HKD</v>
+        <v>99.41 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5266,14 +5255,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>68.89 HKD</v>
+        <v>73.8 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5288,14 +5277,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>63.96 HKD</v>
+        <v>68.65 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5310,14 +5299,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>59.48 HKD</v>
+        <v>63.98 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5332,27 +5321,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>57.39 HKD</v>
+        <v>61.8 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>65.171669755574641</v>
+        <v>69.934431264803422</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5361,7 +5350,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5371,7 +5360,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5380,7 +5369,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5389,12 +5378,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5403,16 +5392,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5425,7 +5414,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5438,49 +5427,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>8.0700835276967897</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.4171703652745364</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>23.750608511506798</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>27.35295938900607</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>31.820692039203585</v>
+        <v>35.770129754280603</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>417</v>
       </c>
@@ -5493,21 +5482,21 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51174042097514749</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.4885190440909043</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
@@ -5516,7 +5505,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5526,30 +5515,30 @@
         <v>10.413924272385298</v>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>36.120932694422855</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>38.760659259042988</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>46.53485696680815</v>
+        <v>49.174583531428283</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>417</v>
       </c>
@@ -5562,63 +5551,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.28596494241537118</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.29684730908540535</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>13.088998285322367</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>13.207992217037489</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>51.735372653094224</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>56.294459619246346</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>64.824370938416592</v>
+        <v>69.502451836283839</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>417</v>
       </c>
@@ -5631,21 +5620,21 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>5.3289844875938908E-3</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>6.1769205912880487E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>424</v>
       </c>
@@ -5654,7 +5643,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5664,30 +5653,30 @@
         <v>12.253538898548621</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>46.712471627436607</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>50.126230438627196</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>58.966010525985226</v>
+        <v>62.379769337175816</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>417</v>
       </c>
@@ -5700,16 +5689,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>9.5216500498555012E-2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.10783243247054153</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5719,7 +5708,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5728,12 +5717,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5742,27 +5731,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5771,12 +5760,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5785,7 +5774,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5794,22 +5783,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5870,15 +5859,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>USD</v>
@@ -5927,7 +5916,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5943,7 +5932,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5951,7 +5940,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5985,7 +5974,7 @@
       <c r="L4" s="181"/>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6019,7 +6008,7 @@
       <c r="L5" s="181"/>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6062,7 +6051,7 @@
       <c r="L6" s="181"/>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6096,7 +6085,7 @@
       <c r="L7" s="188"/>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6130,7 +6119,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6146,7 +6135,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6162,7 +6151,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6178,7 +6167,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6212,7 +6201,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6228,7 +6217,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6262,7 +6251,7 @@
       <c r="L14" s="181"/>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6296,7 +6285,7 @@
       <c r="L15" s="182"/>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6330,13 +6319,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6352,7 +6341,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6378,7 +6367,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6406,7 +6395,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6440,7 +6429,7 @@
       <c r="L22" s="181"/>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6474,7 +6463,7 @@
       <c r="L23" s="181"/>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6508,7 +6497,7 @@
       <c r="L24" s="181"/>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -6531,7 +6520,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6539,7 +6528,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6566,7 +6555,7 @@
       <c r="L28" s="181"/>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6593,7 +6582,7 @@
       <c r="L29" s="181"/>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6628,7 +6617,7 @@
       <c r="L30" s="182"/>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6663,7 +6652,7 @@
       <c r="L31" s="182"/>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6698,7 +6687,7 @@
       <c r="L32" s="182"/>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6714,12 +6703,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6768,7 +6757,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6817,7 +6806,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6866,7 +6855,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6915,7 +6904,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6964,7 +6953,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7013,7 +7002,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7062,7 +7051,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7111,7 +7100,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7160,7 +7149,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7209,7 +7198,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7258,7 +7247,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7307,7 +7296,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7356,12 +7345,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7410,7 +7399,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7459,12 +7448,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7513,7 +7502,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7562,7 +7551,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7611,7 +7600,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7660,13 +7649,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7715,7 +7704,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7764,7 +7753,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7813,7 +7802,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7862,7 +7851,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7911,12 +7900,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7966,7 +7955,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8015,7 +8004,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8065,7 +8054,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8114,7 +8103,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8164,7 +8153,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8180,13 +8169,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8235,7 +8224,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8269,7 +8258,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8303,7 +8292,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8352,7 +8341,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8433,7 +8422,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8444,7 +8433,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8460,7 +8449,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8471,7 +8460,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8491,7 +8480,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8512,7 +8501,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8533,7 +8522,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8554,7 +8543,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8575,7 +8564,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8596,7 +8585,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8617,7 +8606,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8629,7 +8618,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8641,7 +8630,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8665,12 +8654,12 @@
         <v>135.18</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8690,7 +8679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8710,7 +8699,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8731,7 +8720,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8751,7 +8740,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8771,7 +8760,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8792,7 +8781,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8812,7 +8801,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8832,7 +8821,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8844,7 +8833,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8856,7 +8845,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8897,7 +8886,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8916,7 +8905,7 @@
         <v>-86.245000000000118</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8931,7 +8920,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8950,7 +8939,7 @@
         <v>-86.245000000000118</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8966,7 +8955,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -8983,7 +8972,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9003,7 +8992,7 @@
         <v>723.05499999999984</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9014,7 +9003,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9027,7 +9016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9046,7 +9035,7 @@
         <v>587.4849999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9062,7 +9051,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9078,7 +9067,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9094,7 +9083,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9113,7 +9102,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9133,7 +9122,7 @@
         <v>135.57</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9153,7 +9142,7 @@
         <v>135.18</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9172,7 +9161,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9183,7 +9172,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9197,7 +9186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9211,7 +9200,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
@@ -9226,10 +9215,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9242,7 +9231,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9256,7 +9245,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9267,10 +9256,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9282,7 +9271,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9296,7 +9285,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9310,10 +9299,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9325,7 +9314,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9336,7 +9325,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9347,10 +9336,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9362,7 +9351,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9378,7 +9367,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9389,7 +9378,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9403,7 +9392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9419,7 +9408,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9429,7 +9418,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9439,7 +9428,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9449,7 +9438,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9459,10 +9448,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9474,7 +9463,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9490,7 +9479,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9506,7 +9495,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9519,7 +9508,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9532,10 +9521,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9547,7 +9536,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9561,7 +9550,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9575,7 +9564,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9589,7 +9578,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9603,7 +9592,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9614,7 +9603,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9622,7 +9611,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9639,7 +9628,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9656,7 +9645,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9673,7 +9662,7 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9704,19 +9693,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9773,7 +9762,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9796,7 +9785,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9810,7 +9799,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9867,7 +9856,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9922,7 +9911,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -9977,7 +9966,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10032,7 +10021,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10089,7 +10078,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10144,7 +10133,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10199,7 +10188,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10256,7 +10245,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10311,7 +10300,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10366,7 +10355,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10421,7 +10410,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10478,7 +10467,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10535,7 +10524,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10561,7 +10550,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10586,7 +10575,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10643,7 +10632,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10662,7 +10651,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10685,7 +10674,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10706,7 +10695,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10763,7 +10752,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10820,7 +10809,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10877,18 +10866,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10947,7 +10936,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11007,7 +10996,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11062,18 +11051,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11130,7 +11119,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11189,7 +11178,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11246,18 +11235,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11315,7 +11304,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11373,7 +11362,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11428,18 +11417,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11497,10 +11486,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11523,14 +11512,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11585,7 +11574,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11640,7 +11629,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11697,7 +11686,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11752,11 +11741,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11766,7 +11755,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11793,7 +11782,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11820,7 +11809,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11875,11 +11864,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11889,7 +11878,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11944,7 +11933,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -11999,7 +11988,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12054,7 +12043,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12109,7 +12098,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12165,7 +12154,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12220,11 +12209,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12234,7 +12223,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12259,7 +12248,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12284,7 +12273,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12309,7 +12298,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12336,10 +12325,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12362,7 +12351,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12383,7 +12372,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12440,7 +12429,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12497,7 +12486,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12554,7 +12543,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12611,7 +12600,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12668,7 +12657,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12727,7 +12716,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12784,7 +12773,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12841,7 +12830,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12898,7 +12887,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12955,7 +12944,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13013,7 +13002,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13070,7 +13059,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13096,7 +13085,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13120,7 +13109,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13177,18 +13166,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13244,7 +13233,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13300,7 +13289,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13355,7 +13344,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13410,11 +13399,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13435,7 +13424,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13492,7 +13481,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13549,10 +13538,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13575,7 +13564,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13585,7 +13574,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13642,7 +13631,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13699,7 +13688,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13756,7 +13745,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13813,7 +13802,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13870,11 +13859,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13897,7 +13886,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13954,7 +13943,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14011,7 +14000,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14038,18 +14027,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14101,7 +14090,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14153,11 +14142,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14211,7 +14200,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14266,7 +14255,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14320,7 +14309,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14376,7 +14365,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14433,7 +14422,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14452,7 +14441,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14475,7 +14464,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14496,7 +14485,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14554,7 +14543,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14611,7 +14600,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14661,688 +14650,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15364,16 +15353,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15385,7 +15374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15398,7 +15387,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15419,24 +15408,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2143.6154026580366</v>
+        <v>2286.5230961685729</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15448,7 +15437,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15464,7 +15453,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15480,7 +15469,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15496,13 +15485,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>1859.0881220555495</v>
+        <v>2001.9958155660859</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15510,7 +15499,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15524,13 +15513,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15538,10 +15527,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15551,13 +15540,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15567,7 +15556,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15577,13 +15566,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>65.171403499817089</v>
+        <v>69.919342069242049</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15591,10 +15580,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15612,7 +15601,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15626,15 +15615,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>164.3597413915009</v>
+        <v>165.12420530494975</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15648,15 +15637,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>157.52665191703773</v>
+        <v>158.99542394464711</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15670,15 +15659,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>150.97764120402016</v>
+        <v>153.09411959713628</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15692,15 +15681,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>144.70089896619245</v>
+        <v>147.41184918241382</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15714,15 +15703,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>138.68510591796624</v>
+        <v>141.94048299543698</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15736,15 +15725,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>132.91941336156586</v>
+        <v>136.67219307483921</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15758,15 +15747,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>127.39342362281768</v>
+        <v>131.5994420033544</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15780,15 +15769,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>122.09717130030143</v>
+        <v>126.71497212392714</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15802,15 +15791,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>117.02110529404915</v>
+        <v>122.01179515607947</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15824,15 +15813,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>112.15607158138255</v>
+        <v>117.4831821976786</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15854,7 +15843,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15876,7 +15865,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15898,7 +15887,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15920,7 +15909,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15942,7 +15931,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15964,7 +15953,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -15986,7 +15975,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16008,7 +15997,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16030,7 +16019,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16052,7 +16041,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16074,7 +16063,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16096,7 +16085,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16118,7 +16107,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16140,7 +16129,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16162,7 +16151,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16184,7 +16173,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16206,7 +16195,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16228,7 +16217,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16250,7 +16239,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16272,13 +16261,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>2218.8565087852621</v>
+        <v>2366.7802760376135</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16286,30 +16275,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>1027.7598858636504</v>
+        <v>1148.3474195571139</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>2395.5971104204846</v>
+        <v>2549.3950851375766</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16319,10 +16308,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>2395.5971104204846</v>
+        <v>2549.3950851375766</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16346,141 +16335,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>2143.6154026580361</v>
+        <v>2286.5230961685729</v>
       </c>
       <c r="C56" s="124">
-        <v>2177.944172447551</v>
+        <v>2322.5181544876964</v>
       </c>
       <c r="D56" s="124">
-        <v>2248.1329576818198</v>
+        <v>2396.0696561704076</v>
       </c>
       <c r="E56" s="124">
-        <v>2320.4382838504866</v>
+        <v>2471.7794931152084</v>
       </c>
       <c r="F56" s="124">
-        <v>2433.0674749311615</v>
+        <v>2589.5981757852073</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>2143.6154026580361</v>
+        <v>2286.5230961685734</v>
       </c>
       <c r="C57" s="124">
-        <v>2211.1746441620298</v>
+        <v>2357.02955929581</v>
       </c>
       <c r="D57" s="124">
-        <v>2356.3055850252176</v>
+        <v>2508.4224580809523</v>
       </c>
       <c r="E57" s="124">
-        <v>2516.1150686799911</v>
+        <v>2675.0372314135711</v>
       </c>
       <c r="F57" s="124">
-        <v>2787.2337132331991</v>
+        <v>2957.5392154274923</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>2143.6154026580361</v>
+        <v>2286.5230961685738</v>
       </c>
       <c r="C58" s="124">
-        <v>2251.284097705794</v>
+        <v>2399.63876214725</v>
       </c>
       <c r="D58" s="124">
-        <v>2493.6813583907101</v>
+        <v>2654.3741787150057</v>
       </c>
       <c r="E58" s="124">
-        <v>2778.0873446810347</v>
+        <v>2953.392165522383</v>
       </c>
       <c r="F58" s="124">
-        <v>3302.1560154607114</v>
+        <v>3504.7511719097461</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>2143.6154026580357</v>
+        <v>2286.5230961685734</v>
       </c>
       <c r="C59" s="124">
-        <v>2291.0949092861629</v>
+        <v>2442.91347348722</v>
       </c>
       <c r="D59" s="124">
-        <v>2637.4788152265623</v>
+        <v>2810.6990804571815</v>
       </c>
       <c r="E59" s="124">
-        <v>3068.257201365102</v>
+        <v>3268.8754610450337</v>
       </c>
       <c r="F59" s="124">
-        <v>3926.486193617186</v>
+        <v>4183.6646305569257</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>2143.6154026580357</v>
+        <v>2286.5230961685734</v>
       </c>
       <c r="C60" s="124">
-        <v>2327.1400187439999</v>
+        <v>2483.0095416463528</v>
       </c>
       <c r="D60" s="124">
-        <v>2775.0321967075802</v>
+        <v>2963.7274033635958</v>
       </c>
       <c r="E60" s="124">
-        <v>3362.9191268660743</v>
+        <v>3596.7246411158512</v>
       </c>
       <c r="F60" s="124">
-        <v>4625.2775337540652</v>
+        <v>4961.3049983681531</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>2143.6154026580357</v>
+        <v>2286.5230961685734</v>
       </c>
       <c r="C61" s="124">
-        <v>2358.0740338949558</v>
+        <v>2518.2250733235915</v>
       </c>
       <c r="D61" s="124">
-        <v>2899.9612596862244</v>
+        <v>3105.9628390006328</v>
       </c>
       <c r="E61" s="124">
-        <v>3647.8707293210327</v>
+        <v>3921.1891998160045</v>
       </c>
       <c r="F61" s="124">
-        <v>5374.7458895664186</v>
+        <v>5814.8675939598643</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16490,7 +16479,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16513,193 +16502,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.392408547018526</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>58.452181215835303</v>
+        <v>62.915363430857504</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>60.618998049203114</v>
+        <v>65.185991586532822</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>62.851155186009102</v>
+        <v>67.52325028955751</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>66.328161182731378</v>
+        <v>71.160462474417074</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.392408547018526</v>
+        <v>61.804150321475298</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>59.47804802990477</v>
+        <v>63.980774274367597</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>63.958424270286322</v>
+        <v>68.654465098978591</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>68.891945746106288</v>
+        <v>73.7980744995387</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>77.261722212488678</v>
+        <v>82.519269094630516</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.392408547018526</v>
+        <v>61.804150321475312</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>60.716277738906477</v>
+        <v>65.296174415383362</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>68.199388652726384</v>
+        <v>73.160179852030836</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>76.979362213282741</v>
+        <v>82.391244403603096</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>93.158026851742221</v>
+        <v>99.412396319561722</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.392408547018512</v>
+        <v>61.804150321475298</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>61.945287991676324</v>
+        <v>66.632119647625359</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>72.63859854968409</v>
+        <v>77.9861278640807</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>85.937273764257711</v>
+        <v>92.130613921157746</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>112.43189140280549</v>
+        <v>120.3713159772626</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.392408547018512</v>
+        <v>61.804150321475298</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>63.058046243199584</v>
+        <v>67.869936132824392</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>76.885045919943039</v>
+        <v>82.710306305820851</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>95.033861177717426</v>
+        <v>102.25173398061192</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>134.00446647682128</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>144.37806055413006</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.392408547018512</v>
+        <v>61.804150321475298</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>64.013018530140087</v>
+        <v>68.957084265956397</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>80.741764564317407</v>
+        <v>87.1012946269759</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>103.8306786013801</v>
+        <v>112.26836648502359</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>157.1415053076033</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>170.72862060853359</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16716,7 +16705,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16731,14 +16720,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>93.158026851742221</v>
+        <v>99.412396319561722</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16753,7 +16742,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>68.891945746106288</v>
+        <v>73.7980744995387</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16761,7 +16750,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16776,7 +16765,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>63.958424270286322</v>
+        <v>68.654465098978591</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16784,7 +16773,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16799,7 +16788,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>59.47804802990477</v>
+        <v>63.980774274367597</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16807,7 +16796,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16822,21 +16811,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.392408547018526</v>
+        <v>61.804150321475312</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16844,23 +16833,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16894,16 +16883,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>444</v>
       </c>
@@ -16915,7 +16904,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>443</v>
       </c>
@@ -16928,7 +16917,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>441</v>
       </c>
@@ -16949,24 +16938,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>442</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>16069.171165412627</v>
+        <v>17140.449243106803</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16976,13 +16965,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>445</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -16990,10 +16979,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17003,13 +16992,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17019,7 +17008,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17029,13 +17018,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>70.950028167513793</v>
+        <v>75.50503893740445</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17043,10 +17032,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17064,7 +17053,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17078,15 +17067,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1232.0889343527037</v>
+        <v>1237.8195805589955</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17100,15 +17089,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>1180.8660870930808</v>
+        <v>1191.8764339516449</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17122,15 +17111,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>1131.7727777330581</v>
+        <v>1147.6385218981304</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17144,15 +17133,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>1084.720472895277</v>
+        <v>1105.042552588937</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17166,15 +17155,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>1039.6243198877091</v>
+        <v>1064.0275833653709</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17188,15 +17177,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.64796151846522443</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>996.40299368289664</v>
+        <v>1024.5349335280303</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17210,15 +17199,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.60275490089788319</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>954.9785502588802</v>
+        <v>986.5081003814953</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17232,15 +17221,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.56070223339337966</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>915.27628603732364</v>
+        <v>949.89267839511945</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17254,15 +17243,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.52158347292407414</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>877.22460316535989</v>
+        <v>914.63628136426303</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17276,15 +17265,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>840.7548803982047</v>
+        <v>880.68846746060558</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17306,7 +17295,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17328,7 +17317,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17350,7 +17339,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17372,7 +17361,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17394,7 +17383,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17416,7 +17405,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17438,7 +17427,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17460,7 +17449,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17482,7 +17471,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17504,7 +17493,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17526,7 +17515,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17548,7 +17537,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17570,7 +17559,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17592,7 +17581,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17614,7 +17603,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17636,7 +17625,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17658,7 +17647,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17680,7 +17669,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17702,7 +17691,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17724,13 +17713,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>16633.200613761503</v>
+        <v>17742.080654678935</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17738,30 +17727,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.48519392830146441</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>7704.3902103005012</v>
+        <v>8608.3498090850899</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>17958.100115804995</v>
+        <v>19111.014942577684</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17771,10 +17760,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>17958.100115804995</v>
+        <v>19111.014942577684</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17798,141 +17787,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>16069.171165412623</v>
+        <v>17140.449243106803</v>
       </c>
       <c r="C51" s="124">
-        <v>16326.509714558026</v>
+        <v>17410.278780868939</v>
       </c>
       <c r="D51" s="124">
-        <v>16852.665480383981</v>
+        <v>17961.642457649334</v>
       </c>
       <c r="E51" s="124">
-        <v>17394.68745920284</v>
+        <v>18529.185649988282</v>
       </c>
       <c r="F51" s="124">
-        <v>18238.988982439303</v>
+        <v>19412.38912760841</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>16069.171165412619</v>
+        <v>17140.449243106807</v>
       </c>
       <c r="C52" s="124">
-        <v>16575.615098492679</v>
+        <v>17668.986415798587</v>
       </c>
       <c r="D52" s="124">
-        <v>17663.559291856909</v>
+        <v>18803.87208642302</v>
       </c>
       <c r="E52" s="124">
-        <v>18861.538156685227</v>
+        <v>20052.865403063872</v>
       </c>
       <c r="F52" s="124">
-        <v>20893.923210486391</v>
+        <v>22170.583315549196</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>16069.171165412616</v>
+        <v>17140.449243106807</v>
       </c>
       <c r="C53" s="124">
-        <v>16876.287352268573</v>
+        <v>17988.397525176028</v>
       </c>
       <c r="D53" s="124">
-        <v>18693.36847005826</v>
+        <v>19897.969086214558</v>
       </c>
       <c r="E53" s="124">
-        <v>20825.359343281278</v>
+        <v>22139.495810451932</v>
       </c>
       <c r="F53" s="124">
-        <v>24753.932147314415</v>
+        <v>26272.644992084188</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>16069.171165412617</v>
+        <v>17140.44924310681</v>
       </c>
       <c r="C54" s="124">
-        <v>17174.720898102252</v>
+        <v>18312.797481807022</v>
       </c>
       <c r="D54" s="124">
-        <v>19771.316475181346</v>
+        <v>21069.826500747269</v>
       </c>
       <c r="E54" s="124">
-        <v>23000.557883242211</v>
+        <v>24504.451328729981</v>
       </c>
       <c r="F54" s="124">
-        <v>29434.094682109095</v>
+        <v>31361.979841971988</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>16069.171165412617</v>
+        <v>17140.44924310681</v>
       </c>
       <c r="C55" s="124">
-        <v>17444.925633912513</v>
+        <v>18613.369394805137</v>
       </c>
       <c r="D55" s="124">
-        <v>20802.457056023864</v>
+        <v>22216.971791311073</v>
       </c>
       <c r="E55" s="124">
-        <v>25209.430291480145</v>
+        <v>26962.105152482887</v>
       </c>
       <c r="F55" s="124">
-        <v>34672.439974666646</v>
+        <v>37191.400623329617</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>16069.171165412619</v>
+        <v>17140.44924310681</v>
       </c>
       <c r="C56" s="124">
-        <v>17676.816104412868</v>
+        <v>18877.355371720994</v>
       </c>
       <c r="D56" s="124">
-        <v>21738.962034505166</v>
+        <v>23283.210426378017</v>
       </c>
       <c r="E56" s="124">
-        <v>27345.511263854925</v>
+        <v>29394.386859545517</v>
       </c>
       <c r="F56" s="124">
-        <v>40290.675073031583</v>
+        <v>43589.956741161892</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17942,7 +17931,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17965,193 +17954,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>496.07569732500002</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>496.07569732499985</v>
+        <v>529.14741048000008</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>504.02006476634534</v>
+        <v>537.47739058453374</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>520.26316067632513</v>
+        <v>554.4986866814495</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>536.99606670739593</v>
+        <v>572.01946494707659</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>563.06072571069262</v>
+        <v>599.28507662861216</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>496.07569732499974</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>511.71026395401583</v>
+        <v>545.46402344069895</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>545.29648124041228</v>
+        <v>580.49938367452023</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>582.27960841186643</v>
+        <v>619.05739168432319</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>645.0219130658495</v>
+        <v>684.43402992905169</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>496.07569732499962</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>520.99239782531345</v>
+        <v>555.32464955431078</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>577.08799686553084</v>
+        <v>614.27554590004979</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>642.90525951322047</v>
+        <v>683.4743192127695</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>764.18528529622574</v>
+        <v>811.06987727363992</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>496.07569732499974</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>530.20541994267489</v>
+        <v>565.33928771090086</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>610.36561914094182</v>
+        <v>650.45227076629828</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>710.05639764124192</v>
+        <v>756.48349596468461</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>908.66783944561985</v>
+        <v>968.18409981753086</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>496.07569732499974</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>538.5469828868861</v>
+        <v>574.61832393510815</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>642.19823685445306</v>
+        <v>685.8661010187509</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>778.24709079765819</v>
+        <v>832.35438699270787</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>1070.3822033717379</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>1148.1457138513172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>496.07569732499974</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>545.7057358600382</v>
+        <v>582.76790590386759</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>671.1093334795487</v>
+        <v>718.78224018740775</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>844.19061999437861</v>
+        <v>907.44200859443811</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>1243.8242474863764</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>1345.6772576598046</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18168,7 +18157,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18183,14 +18172,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>764.18528529622574</v>
+        <v>811.06987727363992</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18205,7 +18194,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>582.27960841186643</v>
+        <v>619.05739168432319</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18213,7 +18202,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18228,7 +18217,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>545.29648124041228</v>
+        <v>580.49938367452023</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18236,7 +18225,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18251,7 +18240,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>511.71026395401583</v>
+        <v>545.46402344069895</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18259,7 +18248,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18274,21 +18263,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>496.07569732499962</v>
+        <v>529.14741048000019</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18296,23 +18285,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18342,7 +18331,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18352,7 +18341,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18365,7 +18354,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18377,7 +18366,7 @@
         <v>-51.75</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18397,7 +18386,7 @@
         <v>5.07897</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18406,7 +18395,7 @@
         <v>5.07897</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18423,10 +18412,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>70.250639755574639</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>75.01340126480342</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18451,7 +18440,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18473,7 +18462,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18495,7 +18484,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18506,7 +18495,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>448</v>
       </c>
@@ -18520,7 +18509,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18539,7 +18528,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18557,7 +18546,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18568,7 +18557,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18577,7 +18566,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18585,7 +18574,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18597,18 +18586,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18623,13 +18612,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>57.39240854701854</v>
+        <v>61.804150321475284</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18638,7 +18627,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18647,7 +18636,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18659,7 +18648,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18670,13 +18659,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>63.958424270286322</v>
+        <v>68.654465098978591</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18685,7 +18674,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18696,7 +18685,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18705,7 +18694,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18717,7 +18706,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18728,13 +18717,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>59.47804802990477</v>
+        <v>63.980774274367597</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18743,7 +18732,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18754,7 +18743,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18763,7 +18752,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18775,7 +18764,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18786,13 +18775,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>68.891945746106288</v>
+        <v>73.7980744995387</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18801,7 +18790,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18813,20 +18802,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>64.049053317374003</v>
+        <v>68.748448814168412</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18835,12 +18824,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18850,12 +18839,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18864,7 +18853,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18876,7 +18865,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18887,13 +18876,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>57.392408547018526</v>
+        <v>61.804150321475312</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18902,7 +18891,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18913,7 +18902,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18922,7 +18911,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18934,7 +18923,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18945,13 +18934,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>93.158026851742221</v>
+        <v>99.412396319561722</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18960,7 +18949,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18971,13 +18960,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>65.171669755574641</v>
+        <v>69.934431264803422</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -18991,7 +18980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -19000,7 +18989,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19008,7 +18997,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19021,7 +19010,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19033,13 +19022,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>65.171403499817089</v>
+        <v>69.919342069242049</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19049,7 +19038,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19057,7 +19046,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19067,7 +19056,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19079,7 +19068,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19089,7 +19078,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19102,10 +19091,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>-0.13477816515635718</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>-0.12559933513398105</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19114,12 +19103,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19129,7 +19118,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19142,49 +19131,49 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.3674</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>8.0700835276967897</v>
+        <v>8.4171703652745364</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>23.750608511506798</v>
+        <v>27.35295938900607</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>31.820692039203585</v>
+        <v>35.770129754280603</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19195,18 +19184,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.51174042097514749</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.4885190440909043</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19219,24 +19208,24 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17133897517982155</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.19512134426713557</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
@@ -19245,7 +19234,7 @@
         <v>0.21740000000000001</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
@@ -19257,23 +19246,23 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>36.120932694422855</v>
+        <v>38.760659259042988</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>46.53485696680815</v>
+        <v>49.174583531428283</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19284,58 +19273,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.28596494241537118</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.29684730908540535</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>13.088998285322367</v>
+        <v>13.207992217037489</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>51.735372653094224</v>
+        <v>56.294459619246346</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>64.824370938416592</v>
+        <v>69.502451836283839</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19345,18 +19334,18 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>5.3289844875938908E-3</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>6.1769205912880487E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>422</v>
       </c>
@@ -19365,7 +19354,7 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
@@ -19375,23 +19364,23 @@
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>46.712471627436607</v>
+        <v>50.126230438627196</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>58.966010525985226</v>
+        <v>62.379769337175816</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19401,19 +19390,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>9.5216500498555012E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.10783243247054153</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19421,7 +19410,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19429,7 +19418,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/0303.HK_Valuation.xlsx
+++ b/financial_models/opportunities/0303.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F899AD9-6C97-4869-913C-D31B8B40B7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2612B644-7AE3-4739-B272-54AFFC59804B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3869,29 +3869,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4309,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>51.75</v>
+        <v>52.95</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>13098.39763275</v>
+        <v>13402.12859235</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4357,7 +4357,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>7.8137999999999996</v>
+        <v>7.8289</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4367,13 +4367,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4449,14 +4449,14 @@
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>69.934431264803422</v>
+        <v>70.063174657336106</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19512134426713557</v>
+        <v>0.1860616757315392</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>35.770129754280603</v>
+        <v>35.836750246899136</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>49.174583531428283</v>
+        <v>49.26606332171275</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>69.502451836283839</v>
+        <v>69.631609350994381</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>62.379769337175816</v>
+        <v>62.495727201486694</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4573,22 +4573,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
@@ -4600,13 +4600,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4626,13 +4626,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4661,13 +4661,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4753,13 +4753,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4775,7 +4775,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4797,22 +4797,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>0.10230125853812708</v>
+        <v>0.10017603105494056</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>9.8144347826086956E-2</v>
+        <v>9.6105476864966954E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
       </c>
       <c r="F70" s="345">
         <f>Normalized_FCF!C92</f>
-        <v>7.4962939459602689</v>
+        <v>7.5107803723576687</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4881,22 +4881,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
@@ -4940,22 +4940,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>70.587868391307694</v>
+        <v>70.724277924788041</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4992,13 +4992,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5011,13 +5011,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="C97" s="245">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>4.7943079951998415</v>
+        <v>4.8035728920141336</v>
       </c>
       <c r="D97" s="1" t="str">
         <f>Market_currency</f>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="C104" s="76">
         <f>DCF!C8</f>
-        <v>-129.61728060248709</v>
+        <v>-129.82430278085337</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C105" s="245">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-4.0014498693404068</v>
+        <v>-4.0155859727156624</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="C109" s="245">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.2039794707842486E-2</v>
+        <v>1.2063061351484302E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
@@ -5148,13 +5148,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>61.804150321475284</v>
+        <v>61.917182121409724</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="C114" s="245">
         <f>BS!D47</f>
-        <v>-2.6624925501996839</v>
+        <v>-2.6676377596378593</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5193,13 +5193,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>99.41 HKD</v>
+        <v>99.6 HKD</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>73.8 HKD</v>
+        <v>73.93 HKD</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>68.65 HKD</v>
+        <v>68.78 HKD</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>63.98 HKD</v>
+        <v>64.1 HKD</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>61.8 HKD</v>
+        <v>61.92 HKD</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>69.934431264803422</v>
+        <v>70.063174657336106</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
@@ -5342,13 +5342,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
@@ -5361,22 +5361,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C138" s="235">
         <f>Scenarios!C77</f>
-        <v>5.07897</v>
+        <v>5.0887850000000006</v>
       </c>
       <c r="D138" s="234" t="str">
         <f>Market_currency</f>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>8.4171703652745364</v>
+        <v>8.4334363654941047</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>27.35295938900607</v>
+        <v>27.403313881405033</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>35.770129754280603</v>
+        <v>35.836750246899136</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4885190440909043</v>
+        <v>0.48850804403070569</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>10.413924272385298</v>
+        <v>10.434048956471534</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>38.760659259042988</v>
+        <v>38.832014365241214</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>49.174583531428283</v>
+        <v>49.26606332171275</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.29684730908540535</v>
+        <v>0.29683369954812278</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>13.207992217037489</v>
+        <v>13.233516377174332</v>
       </c>
     </row>
     <row r="159" spans="2:4">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>56.294459619246346</v>
+        <v>56.398092973820056</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>69.502451836283839</v>
+        <v>69.631609350994381</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>6.1769205912880487E-3</v>
+        <v>6.1596595993889114E-3</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>12.253538898548621</v>
+        <v>12.277218598229711</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>50.126230438627196</v>
+        <v>50.218508603256986</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>62.379769337175816</v>
+        <v>62.495727201486694</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.10783243247054153</v>
+        <v>0.10781639776209762</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5709,13 +5709,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
@@ -5752,13 +5752,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5766,22 +5766,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5805,17 +5805,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5832,6 +5821,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6504,11 +6504,11 @@
       </c>
       <c r="C25" s="39">
         <f>(0.17+0.48)*Exchange_Rate</f>
-        <v>5.07897</v>
+        <v>5.0887850000000006</v>
       </c>
       <c r="D25" s="39">
         <f>(0.17+0.42)*Exchange_Rate</f>
-        <v>4.6101419999999997</v>
+        <v>4.6190509999999998</v>
       </c>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
@@ -7857,11 +7857,11 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>5.07897</v>
+        <v>5.0887850000000006</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>4.6101419999999997</v>
+        <v>4.6190509999999998</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
@@ -9207,11 +9207,11 @@
       </c>
       <c r="C47" s="148">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>19.356285337992912</v>
+        <v>19.39369094200168</v>
       </c>
       <c r="D47" s="148">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-2.6624925501996839</v>
+        <v>-2.6676377596378593</v>
       </c>
       <c r="F47" s="275"/>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>-129.61728060248709</v>
+        <v>-129.82430278085337</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9469,11 +9469,11 @@
       </c>
       <c r="C73" s="76">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-269.52780776941751</v>
+        <v>-269.73482994778374</v>
       </c>
       <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-279.81728060248707</v>
+        <v>-280.02430278085336</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>352</v>
@@ -9485,11 +9485,11 @@
       </c>
       <c r="C74" s="280">
         <f>-$C$66/C73</f>
-        <v>0.55727088511956768</v>
+        <v>0.55684317827651797</v>
       </c>
       <c r="D74" s="280">
         <f>-$C$66/D73</f>
-        <v>0.53677885681898441</v>
+        <v>0.53638201580505784</v>
       </c>
       <c r="F74" s="275" t="s">
         <v>320</v>
@@ -9502,7 +9502,7 @@
       <c r="C75" s="284"/>
       <c r="D75" s="283">
         <f>MAX(-D73*D76,G5)</f>
-        <v>279.81728060248707</v>
+        <v>280.02430278085336</v>
       </c>
       <c r="F75" s="275" t="s">
         <v>353</v>
@@ -9617,11 +9617,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-1213.48314</v>
+        <v>-1215.82817</v>
       </c>
       <c r="D86" s="245">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-4.7943079951998415</v>
+        <v>-4.8035728920141336</v>
       </c>
       <c r="E86" s="262" t="str">
         <f>Market_currency</f>
@@ -9634,11 +9634,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>-1012.8035071717136</v>
+        <v>-1016.381484041023</v>
       </c>
       <c r="D87" s="245">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-4.0014498693404068</v>
+        <v>-4.0155859727156624</v>
       </c>
       <c r="E87" s="262" t="str">
         <f>Market_currency</f>
@@ -9651,11 +9651,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>3.0473819999999998</v>
+        <v>3.0532710000000001</v>
       </c>
       <c r="D88" s="245">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.2039794707842486E-2</v>
+        <v>1.2063061351484302E-2</v>
       </c>
       <c r="E88" s="262" t="str">
         <f>Market_currency</f>
@@ -9668,11 +9668,11 @@
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
-        <v>-2223.2392651717132</v>
+        <v>-2229.1563830410228</v>
       </c>
       <c r="D89" s="264">
         <f>SUM(D86:D88)</f>
-        <v>-8.7837180698324069</v>
+        <v>-8.8070958033783118</v>
       </c>
       <c r="E89" s="262" t="str">
         <f>Market_currency</f>
@@ -13185,16 +13185,16 @@
       </c>
       <c r="C90" s="114">
         <f>G90</f>
-        <v>5.07897</v>
+        <v>5.0887850000000006</v>
       </c>
       <c r="E90" s="293"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
-        <v>5.07897</v>
+        <v>5.0887850000000006</v>
       </c>
       <c r="H90" s="113">
         <f>Data!D65</f>
-        <v>4.6101419999999997</v>
+        <v>4.6190509999999998</v>
       </c>
       <c r="I90" s="113">
         <f>Data!E65</f>
@@ -13241,16 +13241,16 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>1285.5336932330101</v>
+        <v>1288.0179593734051</v>
       </c>
       <c r="E91" s="293"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>1285.5336932330101</v>
+        <v>1288.0179593734051</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>1166.8690446268859</v>
+        <v>1169.1239938927829</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
@@ -13296,16 +13296,16 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>7.4962939459602689</v>
+        <v>7.5107803723576687</v>
       </c>
       <c r="E92" s="293"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>6.4373244528443143</v>
+        <v>6.449764443532322</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
-        <v>6.4862092530677442</v>
+        <v>6.4987437125780119</v>
       </c>
       <c r="I92" s="171">
         <f t="shared" si="38"/>
@@ -13351,16 +13351,16 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>9.8144347826086956E-2</v>
+        <v>9.6105476864966954E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>9.8144347826086956E-2</v>
+        <v>9.6105476864966954E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>8.9084869565217384E-2</v>
+        <v>8.723420207743153E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
@@ -14493,46 +14493,46 @@
       </c>
       <c r="C124" s="178">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>5.294090129348076</v>
+        <v>5.3043208443591023</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="290"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>6.1649923157849873</v>
+        <v>6.1769060304908106</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5537411998483606</v>
+        <v>5.5644736849539065</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.1958635842666263</v>
+        <v>6.2078369570330691</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>8.3198068558039768</v>
+        <v>8.3358847031410779</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>7.4152786892917044</v>
+        <v>7.4296085554526385</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>5.1338919484979666</v>
+        <v>5.1438130839790794</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2483447406854324</v>
+        <v>6.2604195321549287</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5228699313667233</v>
+        <v>5.5335427584116497</v>
       </c>
       <c r="O124" s="178">
         <f t="shared" si="49"/>
-        <v>5.5753510877855197</v>
+        <v>5.5861253335334995</v>
       </c>
       <c r="P124" s="178" t="str">
         <f t="shared" si="49"/>
@@ -14550,46 +14550,46 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>0.10230125853812708</v>
+        <v>0.10017603105494056</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.11913028629536207</v>
+        <v>0.11665544911219661</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.10731867052847073</v>
+        <v>0.10508921029185847</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.119726832546215</v>
+        <v>0.11723960258797109</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.16076921460490776</v>
+        <v>0.15742936172126681</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market